--- a/deliverables/qc_register/PP_QC_eCoA_Master_Register.xlsx
+++ b/deliverables/qc_register/PP_QC_eCoA_Master_Register.xlsx
@@ -58468,7 +58468,7 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>ППК25117 printed THC total 1.58 vs own components 15.38 — VERIFY ON PAPER; ППК25154 printed 1.87 same class; BSS052501 sheet 20.47 — probably the NGP result but the NGP scan parses as garbage, read off paper; GP062501 PP cert prints 24.89 vs tranche sheet 22.89 — QC decision; J31112501 sheet 25.00 and J31122501 sheet 21.77 match no certificate in the ingestion folder — source unknown, QC review.</t>
+          <t>ППК25117 printed THC total 1.58 vs own components 15.38 — VERIFY ON PAPER; ППК25154 printed 1.87 same class; BSS052501 sheet 20.47 — probably the NGP result but the NGP scan parses as garbage, read off paper; GP062501 PP cert prints 24.89 vs tranche sheet 22.89 — QC decision; J31112501 sheet 25.00 = the March 051-5-K-26 result (25.27, CF-77/26), stale — superseded by the April retest 100-1-K-26 (20.21); J31122501 sheet 21.77 ≈ the 100-3-K-26 trimmed-sample result (21.84, CF-153/26) while the register carries the hand-trimmed 100-2-K-26 (19.84, CF-151/26) — same-day dual-preparation results: QC to decide which preparation is CoQ-forming.</t>
         </is>
       </c>
     </row>

--- a/deliverables/qc_register/PP_QC_eCoA_Master_Register.xlsx
+++ b/deliverables/qc_register/PP_QC_eCoA_Master_Register.xlsx
@@ -32912,7 +32912,7 @@
       </c>
       <c r="B236" s="6" t="inlineStr">
         <is>
-          <t>J31122501</t>
+          <t>J31122501 (hand-trimmed)</t>
         </is>
       </c>
       <c r="C236" s="7" t="inlineStr">
@@ -33063,22 +33063,22 @@
       <c r="D237" s="10" t="inlineStr"/>
       <c r="E237" s="9" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>19.84</t>
         </is>
       </c>
       <c r="F237" s="9" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>18.84–24.25%</t>
         </is>
       </c>
       <c r="G237" s="9" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>&lt;LOQ</t>
         </is>
       </c>
       <c r="H237" s="9" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>&lt;LOQ</t>
         </is>
       </c>
       <c r="I237" s="9" t="inlineStr">
@@ -33108,12 +33108,12 @@
       </c>
       <c r="N237" s="9" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>/</t>
         </is>
       </c>
       <c r="O237" s="9" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>/</t>
         </is>
       </c>
       <c r="P237" s="9" t="inlineStr">
@@ -33123,12 +33123,12 @@
       </c>
       <c r="Q237" s="9" t="inlineStr">
         <is>
-          <t>Одговара</t>
+          <t>/</t>
         </is>
       </c>
       <c r="R237" s="9" t="inlineStr">
         <is>
-          <t>Одговара</t>
+          <t>/</t>
         </is>
       </c>
       <c r="S237" s="9" t="inlineStr">
@@ -33173,17 +33173,17 @@
       </c>
       <c r="AA237" s="9" t="inlineStr">
         <is>
-          <t>230-0393-26</t>
+          <t>100-2-K-26</t>
         </is>
       </c>
       <c r="AB237" s="9" t="inlineStr">
         <is>
-          <t>07.04.2026</t>
+          <t>09.04.2026</t>
         </is>
       </c>
       <c r="AC237" s="10" t="inlineStr">
         <is>
-          <t>IPH — Institute of Public Health (microbiology)</t>
+          <t>Farmahem</t>
         </is>
       </c>
       <c r="AD237" s="11" t="inlineStr">
@@ -33199,7 +33199,7 @@
       <c r="D238" s="10" t="inlineStr"/>
       <c r="E238" s="9" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F238" s="9" t="inlineStr">
@@ -33209,12 +33209,12 @@
       </c>
       <c r="G238" s="9" t="inlineStr">
         <is>
-          <t>&lt;LOQ</t>
+          <t>/</t>
         </is>
       </c>
       <c r="H238" s="9" t="inlineStr">
         <is>
-          <t>&lt;LOQ</t>
+          <t>/</t>
         </is>
       </c>
       <c r="I238" s="9" t="inlineStr">
@@ -33269,57 +33269,57 @@
       </c>
       <c r="S238" s="9" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>2,5</t>
         </is>
       </c>
       <c r="T238" s="9" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>н.д.</t>
         </is>
       </c>
       <c r="U238" s="9" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>н.д.</t>
         </is>
       </c>
       <c r="V238" s="9" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>н.д.</t>
         </is>
       </c>
       <c r="W238" s="9" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>н.д.</t>
         </is>
       </c>
       <c r="X238" s="9" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>н.д.</t>
         </is>
       </c>
       <c r="Y238" s="9" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>н.д.</t>
         </is>
       </c>
       <c r="Z238" s="9" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>н.д.</t>
         </is>
       </c>
       <c r="AA238" s="9" t="inlineStr">
         <is>
-          <t>100-3-K-26</t>
+          <t>1628-2026</t>
         </is>
       </c>
       <c r="AB238" s="9" t="inlineStr">
         <is>
-          <t>09.04.2026</t>
+          <t>23.04.2026</t>
         </is>
       </c>
       <c r="AC238" s="10" t="inlineStr">
         <is>
-          <t>Farmahem</t>
+          <t>IPH — Institute of Public Health (chemistry)</t>
         </is>
       </c>
       <c r="AD238" s="11" t="inlineStr">
@@ -33329,13 +33329,27 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="9" t="inlineStr"/>
-      <c r="B239" s="12" t="inlineStr"/>
-      <c r="C239" s="9" t="inlineStr"/>
-      <c r="D239" s="10" t="inlineStr"/>
+      <c r="A239" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="B239" s="6" t="inlineStr">
+        <is>
+          <t>J31122501 (machine-trimmed)</t>
+        </is>
+      </c>
+      <c r="C239" s="7" t="inlineStr">
+        <is>
+          <t>P060262</t>
+        </is>
+      </c>
+      <c r="D239" s="8" t="inlineStr">
+        <is>
+          <t>Jokerz 31</t>
+        </is>
+      </c>
       <c r="E239" s="9" t="inlineStr">
         <is>
-          <t>19.84</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F239" s="9" t="inlineStr">
@@ -33345,12 +33359,12 @@
       </c>
       <c r="G239" s="9" t="inlineStr">
         <is>
-          <t>&lt;LOQ</t>
+          <t>/</t>
         </is>
       </c>
       <c r="H239" s="9" t="inlineStr">
         <is>
-          <t>&lt;LOQ</t>
+          <t>/</t>
         </is>
       </c>
       <c r="I239" s="9" t="inlineStr">
@@ -33380,12 +33394,12 @@
       </c>
       <c r="N239" s="9" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="O239" s="9" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>840</t>
         </is>
       </c>
       <c r="P239" s="9" t="inlineStr">
@@ -33395,12 +33409,12 @@
       </c>
       <c r="Q239" s="9" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>Одговара</t>
         </is>
       </c>
       <c r="R239" s="9" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>Одговара</t>
         </is>
       </c>
       <c r="S239" s="9" t="inlineStr">
@@ -33445,17 +33459,17 @@
       </c>
       <c r="AA239" s="9" t="inlineStr">
         <is>
-          <t>100-2-K-26</t>
+          <t>230-0393-26</t>
         </is>
       </c>
       <c r="AB239" s="9" t="inlineStr">
         <is>
-          <t>09.04.2026</t>
+          <t>07.04.2026</t>
         </is>
       </c>
       <c r="AC239" s="10" t="inlineStr">
         <is>
-          <t>Farmahem</t>
+          <t>IPH — Institute of Public Health (microbiology)</t>
         </is>
       </c>
       <c r="AD239" s="11" t="inlineStr">
@@ -33471,22 +33485,22 @@
       <c r="D240" s="10" t="inlineStr"/>
       <c r="E240" s="9" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="F240" s="9" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>18.84–24.25%</t>
         </is>
       </c>
       <c r="G240" s="9" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>&lt;LOQ</t>
         </is>
       </c>
       <c r="H240" s="9" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>&lt;LOQ</t>
         </is>
       </c>
       <c r="I240" s="9" t="inlineStr">
@@ -33541,57 +33555,57 @@
       </c>
       <c r="S240" s="9" t="inlineStr">
         <is>
-          <t>2,5</t>
+          <t>/</t>
         </is>
       </c>
       <c r="T240" s="9" t="inlineStr">
         <is>
-          <t>н.д.</t>
+          <t>/</t>
         </is>
       </c>
       <c r="U240" s="9" t="inlineStr">
         <is>
-          <t>н.д.</t>
+          <t>/</t>
         </is>
       </c>
       <c r="V240" s="9" t="inlineStr">
         <is>
-          <t>н.д.</t>
+          <t>/</t>
         </is>
       </c>
       <c r="W240" s="9" t="inlineStr">
         <is>
-          <t>н.д.</t>
+          <t>/</t>
         </is>
       </c>
       <c r="X240" s="9" t="inlineStr">
         <is>
-          <t>н.д.</t>
+          <t>/</t>
         </is>
       </c>
       <c r="Y240" s="9" t="inlineStr">
         <is>
-          <t>н.д.</t>
+          <t>/</t>
         </is>
       </c>
       <c r="Z240" s="9" t="inlineStr">
         <is>
-          <t>н.д.</t>
+          <t>/</t>
         </is>
       </c>
       <c r="AA240" s="9" t="inlineStr">
         <is>
-          <t>1628-2026</t>
+          <t>100-3-K-26</t>
         </is>
       </c>
       <c r="AB240" s="9" t="inlineStr">
         <is>
-          <t>23.04.2026</t>
+          <t>09.04.2026</t>
         </is>
       </c>
       <c r="AC240" s="10" t="inlineStr">
         <is>
-          <t>IPH — Institute of Public Health (chemistry)</t>
+          <t>Farmahem</t>
         </is>
       </c>
       <c r="AD240" s="11" t="inlineStr">
@@ -33738,7 +33752,7 @@
     </row>
     <row r="242">
       <c r="A242" s="5" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B242" s="6" t="inlineStr">
         <is>
@@ -34568,7 +34582,7 @@
     </row>
     <row r="248">
       <c r="A248" s="5" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B248" s="6" t="inlineStr">
         <is>
@@ -34990,7 +35004,7 @@
     </row>
     <row r="251">
       <c r="A251" s="13" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B251" s="14" t="inlineStr">
         <is>
@@ -35412,7 +35426,7 @@
     </row>
     <row r="254">
       <c r="A254" s="5" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B254" s="6" t="inlineStr">
         <is>
@@ -35834,7 +35848,7 @@
     </row>
     <row r="257">
       <c r="A257" s="13" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B257" s="14" t="inlineStr">
         <is>
@@ -36248,7 +36262,7 @@
     </row>
     <row r="260">
       <c r="A260" s="5" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B260" s="6" t="inlineStr">
         <is>
@@ -36670,7 +36684,7 @@
     </row>
     <row r="263">
       <c r="A263" s="13" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B263" s="14" t="inlineStr">
         <is>
@@ -37084,7 +37098,7 @@
     </row>
     <row r="266">
       <c r="A266" s="5" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B266" s="6" t="inlineStr">
         <is>
@@ -37774,7 +37788,7 @@
     </row>
     <row r="271">
       <c r="A271" s="13" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B271" s="14" t="inlineStr">
         <is>
@@ -38188,7 +38202,7 @@
     </row>
     <row r="274">
       <c r="A274" s="5" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B274" s="6" t="inlineStr">
         <is>
@@ -38610,7 +38624,7 @@
     </row>
     <row r="277">
       <c r="A277" s="5" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B277" s="6" t="inlineStr">
         <is>
@@ -38756,7 +38770,7 @@
     </row>
     <row r="278">
       <c r="A278" s="5" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B278" s="6" t="inlineStr">
         <is>
@@ -38906,7 +38920,7 @@
     </row>
     <row r="279">
       <c r="A279" s="5" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B279" s="6" t="inlineStr">
         <is>
@@ -39328,7 +39342,7 @@
     </row>
     <row r="282">
       <c r="A282" s="5" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B282" s="6" t="inlineStr">
         <is>
@@ -39474,7 +39488,7 @@
     </row>
     <row r="283">
       <c r="A283" s="5" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B283" s="6" t="inlineStr">
         <is>
@@ -39620,7 +39634,7 @@
     </row>
     <row r="284">
       <c r="A284" s="5" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B284" s="6" t="inlineStr">
         <is>
@@ -39766,7 +39780,7 @@
     </row>
     <row r="285">
       <c r="A285" s="5" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B285" s="6" t="inlineStr">
         <is>
@@ -39916,7 +39930,7 @@
     </row>
     <row r="286">
       <c r="A286" s="5" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B286" s="6" t="inlineStr">
         <is>
@@ -40066,7 +40080,7 @@
     </row>
     <row r="287">
       <c r="A287" s="5" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B287" s="6" t="inlineStr">
         <is>
@@ -40216,7 +40230,7 @@
     </row>
     <row r="288">
       <c r="A288" s="5" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B288" s="6" t="inlineStr">
         <is>
@@ -40362,7 +40376,7 @@
     </row>
     <row r="289">
       <c r="A289" s="5" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B289" s="6" t="inlineStr">
         <is>
@@ -40508,7 +40522,7 @@
     </row>
     <row r="290">
       <c r="A290" s="5" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B290" s="6" t="inlineStr">
         <is>
@@ -40654,7 +40668,7 @@
     </row>
     <row r="291">
       <c r="A291" s="5" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B291" s="6" t="inlineStr">
         <is>
@@ -40940,7 +40954,7 @@
     </row>
     <row r="293">
       <c r="A293" s="5" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B293" s="6" t="inlineStr">
         <is>
@@ -41226,7 +41240,7 @@
     </row>
     <row r="295">
       <c r="A295" s="5" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B295" s="6" t="inlineStr">
         <is>
@@ -46319,7 +46333,7 @@
     <row r="108">
       <c r="A108" s="6" t="inlineStr">
         <is>
-          <t>Jokerz 31      3 batch(es)</t>
+          <t>Jokerz 31      4 batch(es)</t>
         </is>
       </c>
       <c r="B108" s="7" t="inlineStr"/>
@@ -46516,7 +46530,7 @@
       </c>
       <c r="B114" s="12" t="inlineStr">
         <is>
-          <t>J31122501</t>
+          <t>J31122501 (hand-trimmed)</t>
         </is>
       </c>
       <c r="C114" s="9" t="inlineStr">
@@ -46526,48 +46540,62 @@
       </c>
       <c r="D114" s="9" t="inlineStr">
         <is>
+          <t>19.84</t>
+        </is>
+      </c>
+      <c r="E114" s="9" t="inlineStr">
+        <is>
+          <t>18.84–24.25%</t>
+        </is>
+      </c>
+      <c r="F114" s="9" t="inlineStr">
+        <is>
+          <t>100-2-K-26</t>
+        </is>
+      </c>
+      <c r="G114" s="9" t="inlineStr">
+        <is>
+          <t>09.04.2026</t>
+        </is>
+      </c>
+      <c r="H114" s="10" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I114" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="9" t="n">
+        <v>54</v>
+      </c>
+      <c r="B115" s="12" t="inlineStr">
+        <is>
+          <t>J31122501 (machine-trimmed)</t>
+        </is>
+      </c>
+      <c r="C115" s="9" t="inlineStr">
+        <is>
+          <t>P060262</t>
+        </is>
+      </c>
+      <c r="D115" s="9" t="inlineStr">
+        <is>
           <t>21.84</t>
         </is>
       </c>
-      <c r="E114" s="9" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="F114" s="9" t="inlineStr">
+      <c r="E115" s="9" t="inlineStr">
+        <is>
+          <t>18.84–24.25%</t>
+        </is>
+      </c>
+      <c r="F115" s="9" t="inlineStr">
         <is>
           <t>100-3-K-26</t>
-        </is>
-      </c>
-      <c r="G114" s="9" t="inlineStr">
-        <is>
-          <t>09.04.2026</t>
-        </is>
-      </c>
-      <c r="H114" s="10" t="inlineStr">
-        <is>
-          <t>Farmahem</t>
-        </is>
-      </c>
-      <c r="I114" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="9" t="inlineStr"/>
-      <c r="B115" s="10" t="inlineStr"/>
-      <c r="C115" s="9" t="inlineStr"/>
-      <c r="D115" s="9" t="inlineStr">
-        <is>
-          <t>19.84</t>
-        </is>
-      </c>
-      <c r="E115" s="9" t="inlineStr"/>
-      <c r="F115" s="9" t="inlineStr">
-        <is>
-          <t>100-2-K-26</t>
         </is>
       </c>
       <c r="G115" s="9" t="inlineStr">
@@ -46603,7 +46631,7 @@
     </row>
     <row r="117">
       <c r="A117" s="9" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B117" s="12" t="inlineStr">
         <is>
@@ -46663,7 +46691,7 @@
     </row>
     <row r="119">
       <c r="A119" s="9" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B119" s="12" t="inlineStr">
         <is>
@@ -46739,7 +46767,7 @@
     </row>
     <row r="121">
       <c r="A121" s="9" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B121" s="12" t="inlineStr">
         <is>
@@ -46830,7 +46858,7 @@
     </row>
     <row r="124">
       <c r="A124" s="9" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B124" s="12" t="inlineStr">
         <is>
@@ -46902,7 +46930,7 @@
     </row>
     <row r="126">
       <c r="A126" s="9" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B126" s="12" t="inlineStr">
         <is>
@@ -46978,7 +47006,7 @@
     </row>
     <row r="128">
       <c r="A128" s="9" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B128" s="12" t="inlineStr">
         <is>
@@ -47085,7 +47113,7 @@
     </row>
     <row r="131">
       <c r="A131" s="9" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B131" s="12" t="inlineStr">
         <is>
@@ -47161,7 +47189,7 @@
     </row>
     <row r="133">
       <c r="A133" s="9" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B133" s="12" t="inlineStr">
         <is>
@@ -47237,7 +47265,7 @@
     </row>
     <row r="135">
       <c r="A135" s="9" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B135" s="12" t="inlineStr">
         <is>
@@ -47313,7 +47341,7 @@
     </row>
     <row r="137">
       <c r="A137" s="9" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B137" s="12" t="inlineStr">
         <is>
@@ -47358,7 +47386,7 @@
     </row>
     <row r="138">
       <c r="A138" s="9" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B138" s="12" t="inlineStr">
         <is>
@@ -47449,7 +47477,7 @@
     </row>
     <row r="141">
       <c r="A141" s="9" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B141" s="12" t="inlineStr">
         <is>
@@ -47525,7 +47553,7 @@
     </row>
     <row r="143">
       <c r="A143" s="9" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B143" s="12" t="inlineStr">
         <is>
@@ -47585,7 +47613,7 @@
     </row>
     <row r="145">
       <c r="A145" s="9" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B145" s="12" t="inlineStr">
         <is>
@@ -47707,7 +47735,7 @@
     </row>
     <row r="149">
       <c r="A149" s="9" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B149" s="12" t="inlineStr">
         <is>
@@ -47752,7 +47780,7 @@
     </row>
     <row r="150">
       <c r="A150" s="9" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B150" s="12" t="inlineStr">
         <is>
@@ -47793,7 +47821,7 @@
     </row>
     <row r="151">
       <c r="A151" s="9" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B151" s="12" t="inlineStr">
         <is>
@@ -47853,7 +47881,7 @@
     </row>
     <row r="153">
       <c r="A153" s="9" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B153" s="12" t="inlineStr">
         <is>
@@ -47929,7 +47957,7 @@
     </row>
     <row r="155">
       <c r="A155" s="9" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B155" s="12" t="inlineStr">
         <is>
@@ -47974,7 +48002,7 @@
     </row>
     <row r="156">
       <c r="A156" s="9" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B156" s="12" t="inlineStr">
         <is>
@@ -48034,7 +48062,7 @@
     </row>
     <row r="158">
       <c r="A158" s="9" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B158" s="12" t="inlineStr">
         <is>
@@ -48079,7 +48107,7 @@
     </row>
     <row r="159">
       <c r="A159" s="9" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B159" s="12" t="inlineStr">
         <is>
@@ -48170,7 +48198,7 @@
     </row>
     <row r="162">
       <c r="A162" s="9" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B162" s="12" t="inlineStr">
         <is>
@@ -48211,7 +48239,7 @@
     </row>
     <row r="163">
       <c r="A163" s="9" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B163" s="12" t="inlineStr">
         <is>
@@ -48252,7 +48280,7 @@
     </row>
     <row r="164">
       <c r="A164" s="9" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B164" s="12" t="inlineStr">
         <is>
@@ -48440,7 +48468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M82"/>
+  <dimension ref="A1:M83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -51753,7 +51781,7 @@
       </c>
       <c r="B57" s="10" t="inlineStr">
         <is>
-          <t>J31122501</t>
+          <t>J31122501 (hand-trimmed)</t>
         </is>
       </c>
       <c r="C57" s="9" t="inlineStr">
@@ -51818,57 +51846,57 @@
       </c>
       <c r="B58" s="10" t="inlineStr">
         <is>
-          <t>OPM122501</t>
+          <t>J31122501 (machine-trimmed)</t>
         </is>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>P060242</t>
+          <t>P060262</t>
         </is>
       </c>
       <c r="D58" s="10" t="inlineStr">
         <is>
-          <t>Orange Punch Mimosa</t>
+          <t>Jokerz 31</t>
         </is>
       </c>
       <c r="E58" s="9" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="F58" s="10" t="inlineStr">
         <is>
-          <t>197-19-K-26, 07.08.2026, FHM</t>
+          <t>100-3-K-26, 09.04.2026, FHM</t>
         </is>
       </c>
       <c r="G58" s="9" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="H58" s="9" t="inlineStr">
         <is>
-          <t>8.00%</t>
+          <t>21.00%</t>
         </is>
       </c>
       <c r="I58" s="9" t="inlineStr">
         <is>
-          <t>± 0.54%</t>
+          <t>± 2.10%</t>
         </is>
       </c>
       <c r="J58" s="9" t="inlineStr">
         <is>
-          <t>7.46% – 8.54%</t>
+          <t>18.90% – 23.10%</t>
         </is>
       </c>
       <c r="K58" s="10" t="inlineStr">
         <is>
-          <t>Citrus Bloom</t>
+          <t>Jokerz 31</t>
         </is>
       </c>
       <c r="L58" s="9" t="inlineStr">
         <is>
-          <t>STEADY</t>
+          <t>CAYN</t>
         </is>
       </c>
       <c r="M58" s="9" t="inlineStr">
@@ -51883,27 +51911,27 @@
       </c>
       <c r="B59" s="10" t="inlineStr">
         <is>
-          <t>CC112501</t>
+          <t>OPM122501</t>
         </is>
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>P060272</t>
+          <t>P060242</t>
         </is>
       </c>
       <c r="D59" s="10" t="inlineStr">
         <is>
-          <t>Cash Cow</t>
+          <t>Orange Punch Mimosa</t>
         </is>
       </c>
       <c r="E59" s="9" t="inlineStr">
         <is>
-          <t>13.35</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="F59" s="10" t="inlineStr">
         <is>
-          <t>ППК26068, 11.05.2026, CNP</t>
+          <t>197-19-K-26, 07.08.2026, FHM</t>
         </is>
       </c>
       <c r="G59" s="9" t="inlineStr">
@@ -51913,22 +51941,22 @@
       </c>
       <c r="H59" s="9" t="inlineStr">
         <is>
-          <t>13.50%</t>
+          <t>8.00%</t>
         </is>
       </c>
       <c r="I59" s="9" t="inlineStr">
         <is>
-          <t>± 1.34%</t>
+          <t>± 0.54%</t>
         </is>
       </c>
       <c r="J59" s="9" t="inlineStr">
         <is>
-          <t>12.16% – 14.84%</t>
+          <t>7.46% – 8.54%</t>
         </is>
       </c>
       <c r="K59" s="10" t="inlineStr">
         <is>
-          <t>Payday</t>
+          <t>Citrus Bloom</t>
         </is>
       </c>
       <c r="L59" s="9" t="inlineStr">
@@ -51948,47 +51976,59 @@
       </c>
       <c r="B60" s="10" t="inlineStr">
         <is>
-          <t>FB012601_1</t>
+          <t>CC112501</t>
         </is>
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>P060322</t>
+          <t>P060272</t>
         </is>
       </c>
       <c r="D60" s="10" t="inlineStr">
         <is>
-          <t>Fat Bastard</t>
+          <t>Cash Cow</t>
         </is>
       </c>
       <c r="E60" s="9" t="inlineStr">
         <is>
-          <t>14.68</t>
+          <t>13.35</t>
         </is>
       </c>
       <c r="F60" s="10" t="inlineStr">
         <is>
-          <t>ППК26067, 11.05.2026, CNP</t>
+          <t>ППК26068, 11.05.2026, CNP</t>
         </is>
       </c>
       <c r="G60" s="9" t="inlineStr">
         <is>
-          <t>Spec III</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="H60" s="9" t="inlineStr">
         <is>
-          <t>16.5%</t>
-        </is>
-      </c>
-      <c r="I60" s="9" t="inlineStr"/>
+          <t>13.50%</t>
+        </is>
+      </c>
+      <c r="I60" s="9" t="inlineStr">
+        <is>
+          <t>± 1.34%</t>
+        </is>
+      </c>
       <c r="J60" s="9" t="inlineStr">
         <is>
-          <t>13.68–19.25%</t>
-        </is>
-      </c>
-      <c r="K60" s="10" t="inlineStr"/>
-      <c r="L60" s="9" t="inlineStr"/>
+          <t>12.16% – 14.84%</t>
+        </is>
+      </c>
+      <c r="K60" s="10" t="inlineStr">
+        <is>
+          <t>Payday</t>
+        </is>
+      </c>
+      <c r="L60" s="9" t="inlineStr">
+        <is>
+          <t>STEADY</t>
+        </is>
+      </c>
       <c r="M60" s="9" t="inlineStr">
         <is>
           <t>ДА | YES</t>
@@ -52001,12 +52041,12 @@
       </c>
       <c r="B61" s="10" t="inlineStr">
         <is>
-          <t>FB112501</t>
+          <t>FB012601_1</t>
         </is>
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>P060292</t>
+          <t>P060322</t>
         </is>
       </c>
       <c r="D61" s="10" t="inlineStr">
@@ -52016,44 +52056,32 @@
       </c>
       <c r="E61" s="9" t="inlineStr">
         <is>
-          <t>16.69</t>
+          <t>14.68</t>
         </is>
       </c>
       <c r="F61" s="10" t="inlineStr">
         <is>
-          <t>ППК26066, 11.05.2026, CNP</t>
+          <t>ППК26067, 11.05.2026, CNP</t>
         </is>
       </c>
       <c r="G61" s="9" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Spec III</t>
         </is>
       </c>
       <c r="H61" s="9" t="inlineStr">
         <is>
-          <t>16.00%</t>
-        </is>
-      </c>
-      <c r="I61" s="9" t="inlineStr">
-        <is>
-          <t>± 1.54%</t>
-        </is>
-      </c>
+          <t>16.5%</t>
+        </is>
+      </c>
+      <c r="I61" s="9" t="inlineStr"/>
       <c r="J61" s="9" t="inlineStr">
         <is>
-          <t>14.46% – 17.54%</t>
-        </is>
-      </c>
-      <c r="K61" s="10" t="inlineStr">
-        <is>
-          <t>Fat Sofa</t>
-        </is>
-      </c>
-      <c r="L61" s="9" t="inlineStr">
-        <is>
-          <t>CAYN</t>
-        </is>
-      </c>
+          <t>13.68–19.25%</t>
+        </is>
+      </c>
+      <c r="K61" s="10" t="inlineStr"/>
+      <c r="L61" s="9" t="inlineStr"/>
       <c r="M61" s="9" t="inlineStr">
         <is>
           <t>ДА | YES</t>
@@ -52066,28 +52094,64 @@
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t>GG012601*</t>
-        </is>
-      </c>
-      <c r="C62" s="9" t="inlineStr"/>
-      <c r="D62" s="10" t="inlineStr"/>
+          <t>FB112501</t>
+        </is>
+      </c>
+      <c r="C62" s="9" t="inlineStr">
+        <is>
+          <t>P060292</t>
+        </is>
+      </c>
+      <c r="D62" s="10" t="inlineStr">
+        <is>
+          <t>Fat Bastard</t>
+        </is>
+      </c>
       <c r="E62" s="9" t="inlineStr">
         <is>
-          <t>15.35</t>
+          <t>16.69</t>
         </is>
       </c>
       <c r="F62" s="10" t="inlineStr">
         <is>
-          <t>ППК26062, 11.05.2026, CNP</t>
-        </is>
-      </c>
-      <c r="G62" s="9" t="inlineStr"/>
-      <c r="H62" s="9" t="inlineStr"/>
-      <c r="I62" s="9" t="inlineStr"/>
-      <c r="J62" s="9" t="inlineStr"/>
-      <c r="K62" s="10" t="inlineStr"/>
-      <c r="L62" s="9" t="inlineStr"/>
-      <c r="M62" s="9" t="inlineStr"/>
+          <t>ППК26066, 11.05.2026, CNP</t>
+        </is>
+      </c>
+      <c r="G62" s="9" t="inlineStr">
+        <is>
+          <t>Pot.-1</t>
+        </is>
+      </c>
+      <c r="H62" s="9" t="inlineStr">
+        <is>
+          <t>16.00%</t>
+        </is>
+      </c>
+      <c r="I62" s="9" t="inlineStr">
+        <is>
+          <t>± 1.54%</t>
+        </is>
+      </c>
+      <c r="J62" s="9" t="inlineStr">
+        <is>
+          <t>14.46% – 17.54%</t>
+        </is>
+      </c>
+      <c r="K62" s="10" t="inlineStr">
+        <is>
+          <t>Fat Sofa</t>
+        </is>
+      </c>
+      <c r="L62" s="9" t="inlineStr">
+        <is>
+          <t>CAYN</t>
+        </is>
+      </c>
+      <c r="M62" s="9" t="inlineStr">
+        <is>
+          <t>ДА | YES</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="9" t="n">
@@ -52095,64 +52159,28 @@
       </c>
       <c r="B63" s="10" t="inlineStr">
         <is>
-          <t>GG112501</t>
-        </is>
-      </c>
-      <c r="C63" s="9" t="inlineStr">
-        <is>
-          <t>P060252</t>
-        </is>
-      </c>
-      <c r="D63" s="10" t="inlineStr">
-        <is>
-          <t>Gorilla Glue</t>
-        </is>
-      </c>
+          <t>GG012601*</t>
+        </is>
+      </c>
+      <c r="C63" s="9" t="inlineStr"/>
+      <c r="D63" s="10" t="inlineStr"/>
       <c r="E63" s="9" t="inlineStr">
         <is>
-          <t>17.94</t>
+          <t>15.35</t>
         </is>
       </c>
       <c r="F63" s="10" t="inlineStr">
         <is>
-          <t>ППК26061, 11.05.2026, CNP</t>
-        </is>
-      </c>
-      <c r="G63" s="9" t="inlineStr">
-        <is>
-          <t>Pot.-2</t>
-        </is>
-      </c>
-      <c r="H63" s="9" t="inlineStr">
-        <is>
-          <t>17.50%</t>
-        </is>
-      </c>
-      <c r="I63" s="9" t="inlineStr">
-        <is>
-          <t>± 1.75%</t>
-        </is>
-      </c>
-      <c r="J63" s="9" t="inlineStr">
-        <is>
-          <t>15.75% – 19.25%</t>
-        </is>
-      </c>
-      <c r="K63" s="10" t="inlineStr">
-        <is>
-          <t>Cherry Chocolate</t>
-        </is>
-      </c>
-      <c r="L63" s="9" t="inlineStr">
-        <is>
-          <t>CAYN</t>
-        </is>
-      </c>
-      <c r="M63" s="9" t="inlineStr">
-        <is>
-          <t>ДА | YES</t>
-        </is>
-      </c>
+          <t>ППК26062, 11.05.2026, CNP</t>
+        </is>
+      </c>
+      <c r="G63" s="9" t="inlineStr"/>
+      <c r="H63" s="9" t="inlineStr"/>
+      <c r="I63" s="9" t="inlineStr"/>
+      <c r="J63" s="9" t="inlineStr"/>
+      <c r="K63" s="10" t="inlineStr"/>
+      <c r="L63" s="9" t="inlineStr"/>
+      <c r="M63" s="9" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="9" t="n">
@@ -52160,28 +52188,64 @@
       </c>
       <c r="B64" s="10" t="inlineStr">
         <is>
-          <t>JD012601*</t>
-        </is>
-      </c>
-      <c r="C64" s="9" t="inlineStr"/>
-      <c r="D64" s="10" t="inlineStr"/>
+          <t>GG112501</t>
+        </is>
+      </c>
+      <c r="C64" s="9" t="inlineStr">
+        <is>
+          <t>P060252</t>
+        </is>
+      </c>
+      <c r="D64" s="10" t="inlineStr">
+        <is>
+          <t>Gorilla Glue</t>
+        </is>
+      </c>
       <c r="E64" s="9" t="inlineStr">
         <is>
-          <t>18.16</t>
+          <t>17.94</t>
         </is>
       </c>
       <c r="F64" s="10" t="inlineStr">
         <is>
-          <t>ППК26064, 11.05.2026, CNP</t>
-        </is>
-      </c>
-      <c r="G64" s="9" t="inlineStr"/>
-      <c r="H64" s="9" t="inlineStr"/>
-      <c r="I64" s="9" t="inlineStr"/>
-      <c r="J64" s="9" t="inlineStr"/>
-      <c r="K64" s="10" t="inlineStr"/>
-      <c r="L64" s="9" t="inlineStr"/>
-      <c r="M64" s="9" t="inlineStr"/>
+          <t>ППК26061, 11.05.2026, CNP</t>
+        </is>
+      </c>
+      <c r="G64" s="9" t="inlineStr">
+        <is>
+          <t>Pot.-2</t>
+        </is>
+      </c>
+      <c r="H64" s="9" t="inlineStr">
+        <is>
+          <t>17.50%</t>
+        </is>
+      </c>
+      <c r="I64" s="9" t="inlineStr">
+        <is>
+          <t>± 1.75%</t>
+        </is>
+      </c>
+      <c r="J64" s="9" t="inlineStr">
+        <is>
+          <t>15.75% – 19.25%</t>
+        </is>
+      </c>
+      <c r="K64" s="10" t="inlineStr">
+        <is>
+          <t>Cherry Chocolate</t>
+        </is>
+      </c>
+      <c r="L64" s="9" t="inlineStr">
+        <is>
+          <t>CAYN</t>
+        </is>
+      </c>
+      <c r="M64" s="9" t="inlineStr">
+        <is>
+          <t>ДА | YES</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="9" t="n">
@@ -52189,60 +52253,28 @@
       </c>
       <c r="B65" s="10" t="inlineStr">
         <is>
-          <t>JD112501</t>
+          <t>JD012601*</t>
         </is>
       </c>
       <c r="C65" s="9" t="inlineStr"/>
-      <c r="D65" s="10" t="inlineStr">
-        <is>
-          <t>Jelly Donutz</t>
-        </is>
-      </c>
+      <c r="D65" s="10" t="inlineStr"/>
       <c r="E65" s="9" t="inlineStr">
         <is>
-          <t>20.32</t>
+          <t>18.16</t>
         </is>
       </c>
       <c r="F65" s="10" t="inlineStr">
         <is>
-          <t>197-15-K-26, 07.08.2026, FHM</t>
-        </is>
-      </c>
-      <c r="G65" s="9" t="inlineStr">
-        <is>
-          <t>Pot.-2</t>
-        </is>
-      </c>
-      <c r="H65" s="9" t="inlineStr">
-        <is>
-          <t>20.00%</t>
-        </is>
-      </c>
-      <c r="I65" s="9" t="inlineStr">
-        <is>
-          <t>± 2.00%</t>
-        </is>
-      </c>
-      <c r="J65" s="9" t="inlineStr">
-        <is>
-          <t>18.00% – 22.00%</t>
-        </is>
-      </c>
-      <c r="K65" s="10" t="inlineStr">
-        <is>
-          <t>Jelly Donuts</t>
-        </is>
-      </c>
-      <c r="L65" s="9" t="inlineStr">
-        <is>
-          <t>CAYN</t>
-        </is>
-      </c>
-      <c r="M65" s="9" t="inlineStr">
-        <is>
-          <t>ДА | YES</t>
-        </is>
-      </c>
+          <t>ППК26064, 11.05.2026, CNP</t>
+        </is>
+      </c>
+      <c r="G65" s="9" t="inlineStr"/>
+      <c r="H65" s="9" t="inlineStr"/>
+      <c r="I65" s="9" t="inlineStr"/>
+      <c r="J65" s="9" t="inlineStr"/>
+      <c r="K65" s="10" t="inlineStr"/>
+      <c r="L65" s="9" t="inlineStr"/>
+      <c r="M65" s="9" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="9" t="n">
@@ -52250,28 +52282,60 @@
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
-          <t>JD112501*</t>
+          <t>JD112501</t>
         </is>
       </c>
       <c r="C66" s="9" t="inlineStr"/>
-      <c r="D66" s="10" t="inlineStr"/>
+      <c r="D66" s="10" t="inlineStr">
+        <is>
+          <t>Jelly Donutz</t>
+        </is>
+      </c>
       <c r="E66" s="9" t="inlineStr">
         <is>
-          <t>13.93</t>
+          <t>20.32</t>
         </is>
       </c>
       <c r="F66" s="10" t="inlineStr">
         <is>
-          <t>ППК26065, 11.05.2026, CNP</t>
-        </is>
-      </c>
-      <c r="G66" s="9" t="inlineStr"/>
-      <c r="H66" s="9" t="inlineStr"/>
-      <c r="I66" s="9" t="inlineStr"/>
-      <c r="J66" s="9" t="inlineStr"/>
-      <c r="K66" s="10" t="inlineStr"/>
-      <c r="L66" s="9" t="inlineStr"/>
-      <c r="M66" s="9" t="inlineStr"/>
+          <t>197-15-K-26, 07.08.2026, FHM</t>
+        </is>
+      </c>
+      <c r="G66" s="9" t="inlineStr">
+        <is>
+          <t>Pot.-2</t>
+        </is>
+      </c>
+      <c r="H66" s="9" t="inlineStr">
+        <is>
+          <t>20.00%</t>
+        </is>
+      </c>
+      <c r="I66" s="9" t="inlineStr">
+        <is>
+          <t>± 2.00%</t>
+        </is>
+      </c>
+      <c r="J66" s="9" t="inlineStr">
+        <is>
+          <t>18.00% – 22.00%</t>
+        </is>
+      </c>
+      <c r="K66" s="10" t="inlineStr">
+        <is>
+          <t>Jelly Donuts</t>
+        </is>
+      </c>
+      <c r="L66" s="9" t="inlineStr">
+        <is>
+          <t>CAYN</t>
+        </is>
+      </c>
+      <c r="M66" s="9" t="inlineStr">
+        <is>
+          <t>ДА | YES</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="9" t="n">
@@ -52279,64 +52343,28 @@
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t>SCR112501</t>
-        </is>
-      </c>
-      <c r="C67" s="9" t="inlineStr">
-        <is>
-          <t>P060282</t>
-        </is>
-      </c>
-      <c r="D67" s="10" t="inlineStr">
-        <is>
-          <t>Scrambler</t>
-        </is>
-      </c>
+          <t>JD112501*</t>
+        </is>
+      </c>
+      <c r="C67" s="9" t="inlineStr"/>
+      <c r="D67" s="10" t="inlineStr"/>
       <c r="E67" s="9" t="inlineStr">
         <is>
-          <t>17.13</t>
+          <t>13.93</t>
         </is>
       </c>
       <c r="F67" s="10" t="inlineStr">
         <is>
-          <t>ППК26069, 11.05.2026, CNP</t>
-        </is>
-      </c>
-      <c r="G67" s="9" t="inlineStr">
-        <is>
-          <t>Pot.-1</t>
-        </is>
-      </c>
-      <c r="H67" s="9" t="inlineStr">
-        <is>
-          <t>18.00%</t>
-        </is>
-      </c>
-      <c r="I67" s="9" t="inlineStr">
-        <is>
-          <t>± 1.79%</t>
-        </is>
-      </c>
-      <c r="J67" s="9" t="inlineStr">
-        <is>
-          <t>16.21% – 19.79%</t>
-        </is>
-      </c>
-      <c r="K67" s="10" t="inlineStr">
-        <is>
-          <t>Scrambler</t>
-        </is>
-      </c>
-      <c r="L67" s="9" t="inlineStr">
-        <is>
-          <t>CAYN</t>
-        </is>
-      </c>
-      <c r="M67" s="9" t="inlineStr">
-        <is>
-          <t>ДА | YES</t>
-        </is>
-      </c>
+          <t>ППК26065, 11.05.2026, CNP</t>
+        </is>
+      </c>
+      <c r="G67" s="9" t="inlineStr"/>
+      <c r="H67" s="9" t="inlineStr"/>
+      <c r="I67" s="9" t="inlineStr"/>
+      <c r="J67" s="9" t="inlineStr"/>
+      <c r="K67" s="10" t="inlineStr"/>
+      <c r="L67" s="9" t="inlineStr"/>
+      <c r="M67" s="9" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="9" t="n">
@@ -52344,48 +52372,52 @@
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
-          <t>FB012603</t>
-        </is>
-      </c>
-      <c r="C68" s="9" t="inlineStr"/>
+          <t>SCR112501</t>
+        </is>
+      </c>
+      <c r="C68" s="9" t="inlineStr">
+        <is>
+          <t>P060282</t>
+        </is>
+      </c>
       <c r="D68" s="10" t="inlineStr">
         <is>
-          <t>Fat Bastard</t>
+          <t>Scrambler</t>
         </is>
       </c>
       <c r="E68" s="9" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>17.13</t>
         </is>
       </c>
       <c r="F68" s="10" t="inlineStr">
         <is>
-          <t>ППК26112, 30.06.2026, CNP</t>
+          <t>ППК26069, 11.05.2026, CNP</t>
         </is>
       </c>
       <c r="G68" s="9" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="H68" s="9" t="inlineStr">
         <is>
-          <t>19.50%</t>
+          <t>18.00%</t>
         </is>
       </c>
       <c r="I68" s="9" t="inlineStr">
         <is>
-          <t>± 1.95%</t>
+          <t>± 1.79%</t>
         </is>
       </c>
       <c r="J68" s="9" t="inlineStr">
         <is>
-          <t>17.55% – 21.45%</t>
+          <t>16.21% – 19.79%</t>
         </is>
       </c>
       <c r="K68" s="10" t="inlineStr">
         <is>
-          <t>Daywalker</t>
+          <t>Scrambler</t>
         </is>
       </c>
       <c r="L68" s="9" t="inlineStr">
@@ -52405,14 +52437,10 @@
       </c>
       <c r="B69" s="10" t="inlineStr">
         <is>
-          <t>FB012603V</t>
-        </is>
-      </c>
-      <c r="C69" s="9" t="inlineStr">
-        <is>
-          <t>P060392</t>
-        </is>
-      </c>
+          <t>FB012603</t>
+        </is>
+      </c>
+      <c r="C69" s="9" t="inlineStr"/>
       <c r="D69" s="10" t="inlineStr">
         <is>
           <t>Fat Bastard</t>
@@ -52420,12 +52448,12 @@
       </c>
       <c r="E69" s="9" t="inlineStr">
         <is>
-          <t>18.29</t>
+          <t>20.83</t>
         </is>
       </c>
       <c r="F69" s="10" t="inlineStr">
         <is>
-          <t>ППК26110, 30.06.2026, CNP</t>
+          <t>ППК26112, 30.06.2026, CNP</t>
         </is>
       </c>
       <c r="G69" s="9" t="inlineStr">
@@ -52470,27 +52498,27 @@
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t>GG012603</t>
+          <t>FB012603V</t>
         </is>
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>P060402</t>
+          <t>P060392</t>
         </is>
       </c>
       <c r="D70" s="10" t="inlineStr">
         <is>
-          <t>Gorilla Glue</t>
+          <t>Fat Bastard</t>
         </is>
       </c>
       <c r="E70" s="9" t="inlineStr">
         <is>
-          <t>16.70</t>
+          <t>18.29</t>
         </is>
       </c>
       <c r="F70" s="10" t="inlineStr">
         <is>
-          <t>197-8-K-26, 07.08.2026, FHM</t>
+          <t>ППК26110, 30.06.2026, CNP</t>
         </is>
       </c>
       <c r="G70" s="9" t="inlineStr">
@@ -52500,27 +52528,27 @@
       </c>
       <c r="H70" s="9" t="inlineStr">
         <is>
-          <t>17.50%</t>
+          <t>19.50%</t>
         </is>
       </c>
       <c r="I70" s="9" t="inlineStr">
         <is>
-          <t>± 1.75%</t>
+          <t>± 1.95%</t>
         </is>
       </c>
       <c r="J70" s="9" t="inlineStr">
         <is>
-          <t>15.75% – 19.25%</t>
+          <t>17.55% – 21.45%</t>
         </is>
       </c>
       <c r="K70" s="10" t="inlineStr">
         <is>
-          <t>GG4</t>
+          <t>Daywalker</t>
         </is>
       </c>
       <c r="L70" s="9" t="inlineStr">
         <is>
-          <t>STEADY</t>
+          <t>CAYN</t>
         </is>
       </c>
       <c r="M70" s="9" t="inlineStr">
@@ -52535,23 +52563,27 @@
       </c>
       <c r="B71" s="10" t="inlineStr">
         <is>
-          <t>JD012603_02</t>
-        </is>
-      </c>
-      <c r="C71" s="9" t="inlineStr"/>
+          <t>GG012603</t>
+        </is>
+      </c>
+      <c r="C71" s="9" t="inlineStr">
+        <is>
+          <t>P060402</t>
+        </is>
+      </c>
       <c r="D71" s="10" t="inlineStr">
         <is>
-          <t>JellyDonutz</t>
+          <t>Gorilla Glue</t>
         </is>
       </c>
       <c r="E71" s="9" t="inlineStr">
         <is>
-          <t>20.54</t>
+          <t>16.70</t>
         </is>
       </c>
       <c r="F71" s="10" t="inlineStr">
         <is>
-          <t>ППК26113, 30.06.2026, CNP</t>
+          <t>197-8-K-26, 07.08.2026, FHM</t>
         </is>
       </c>
       <c r="G71" s="9" t="inlineStr">
@@ -52561,27 +52593,27 @@
       </c>
       <c r="H71" s="9" t="inlineStr">
         <is>
-          <t>20.00%</t>
+          <t>17.50%</t>
         </is>
       </c>
       <c r="I71" s="9" t="inlineStr">
         <is>
-          <t>± 2.00%</t>
+          <t>± 1.75%</t>
         </is>
       </c>
       <c r="J71" s="9" t="inlineStr">
         <is>
-          <t>18.00% – 22.00%</t>
+          <t>15.75% – 19.25%</t>
         </is>
       </c>
       <c r="K71" s="10" t="inlineStr">
         <is>
-          <t>Jelly Donuts</t>
+          <t>GG4</t>
         </is>
       </c>
       <c r="L71" s="9" t="inlineStr">
         <is>
-          <t>CAYN</t>
+          <t>STEADY</t>
         </is>
       </c>
       <c r="M71" s="9" t="inlineStr">
@@ -52596,7 +52628,7 @@
       </c>
       <c r="B72" s="10" t="inlineStr">
         <is>
-          <t>JD012603_02V</t>
+          <t>JD012603_02</t>
         </is>
       </c>
       <c r="C72" s="9" t="inlineStr"/>
@@ -52607,32 +52639,32 @@
       </c>
       <c r="E72" s="9" t="inlineStr">
         <is>
-          <t>15.16</t>
+          <t>20.54</t>
         </is>
       </c>
       <c r="F72" s="10" t="inlineStr">
         <is>
-          <t>ППК26111, 30.06.2026, CNP</t>
+          <t>ППК26113, 30.06.2026, CNP</t>
         </is>
       </c>
       <c r="G72" s="9" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="H72" s="9" t="inlineStr">
         <is>
-          <t>16.50%</t>
+          <t>20.00%</t>
         </is>
       </c>
       <c r="I72" s="9" t="inlineStr">
         <is>
-          <t>± 1.49%</t>
+          <t>± 2.00%</t>
         </is>
       </c>
       <c r="J72" s="9" t="inlineStr">
         <is>
-          <t>15.01% – 17.99%</t>
+          <t>18.00% – 22.00%</t>
         </is>
       </c>
       <c r="K72" s="10" t="inlineStr">
@@ -52657,44 +52689,60 @@
       </c>
       <c r="B73" s="10" t="inlineStr">
         <is>
-          <t>JD022601</t>
+          <t>JD012603_02V</t>
         </is>
       </c>
       <c r="C73" s="9" t="inlineStr"/>
       <c r="D73" s="10" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>JellyDonutz</t>
         </is>
       </c>
       <c r="E73" s="9" t="inlineStr">
         <is>
-          <t>18.58</t>
+          <t>15.16</t>
         </is>
       </c>
       <c r="F73" s="10" t="inlineStr">
         <is>
-          <t>ППК26115, 30.06.2026, CNP</t>
+          <t>ППК26111, 30.06.2026, CNP</t>
         </is>
       </c>
       <c r="G73" s="9" t="inlineStr">
         <is>
-          <t>нема | none</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="H73" s="9" t="inlineStr">
         <is>
-          <t>не е во залихата Т1/Т2/Т3 | not in T1/T2/T3 stock</t>
-        </is>
-      </c>
-      <c r="I73" s="9" t="inlineStr"/>
-      <c r="J73" s="9" t="inlineStr"/>
+          <t>16.50%</t>
+        </is>
+      </c>
+      <c r="I73" s="9" t="inlineStr">
+        <is>
+          <t>± 1.49%</t>
+        </is>
+      </c>
+      <c r="J73" s="9" t="inlineStr">
+        <is>
+          <t>15.01% – 17.99%</t>
+        </is>
+      </c>
       <c r="K73" s="10" t="inlineStr">
         <is>
-          <t>— не е во мастерот | not in master</t>
-        </is>
-      </c>
-      <c r="L73" s="9" t="inlineStr"/>
-      <c r="M73" s="9" t="inlineStr"/>
+          <t>Jelly Donuts</t>
+        </is>
+      </c>
+      <c r="L73" s="9" t="inlineStr">
+        <is>
+          <t>CAYN</t>
+        </is>
+      </c>
+      <c r="M73" s="9" t="inlineStr">
+        <is>
+          <t>ДА | YES</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="9" t="n">
@@ -52702,27 +52750,23 @@
       </c>
       <c r="B74" s="10" t="inlineStr">
         <is>
-          <t>P160012</t>
-        </is>
-      </c>
-      <c r="C74" s="9" t="inlineStr">
-        <is>
-          <t>P160012</t>
-        </is>
-      </c>
+          <t>JD022601</t>
+        </is>
+      </c>
+      <c r="C74" s="9" t="inlineStr"/>
       <c r="D74" s="10" t="inlineStr">
         <is>
-          <t>GrapePie</t>
+          <t>Jelly Donutz</t>
         </is>
       </c>
       <c r="E74" s="9" t="inlineStr">
         <is>
-          <t>26.32</t>
+          <t>18.58</t>
         </is>
       </c>
       <c r="F74" s="10" t="inlineStr">
         <is>
-          <t>ППК26117, 06.07.2026, CNP</t>
+          <t>ППК26115, 30.06.2026, CNP</t>
         </is>
       </c>
       <c r="G74" s="9" t="inlineStr">
@@ -52751,12 +52795,12 @@
       </c>
       <c r="B75" s="10" t="inlineStr">
         <is>
-          <t>P160022</t>
+          <t>P160012</t>
         </is>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>P160022</t>
+          <t>P160012</t>
         </is>
       </c>
       <c r="D75" s="10" t="inlineStr">
@@ -52766,12 +52810,12 @@
       </c>
       <c r="E75" s="9" t="inlineStr">
         <is>
-          <t>25.72</t>
+          <t>26.32</t>
         </is>
       </c>
       <c r="F75" s="10" t="inlineStr">
         <is>
-          <t>ППК26118, 06.07.2026, CNP</t>
+          <t>ППК26117, 06.07.2026, CNP</t>
         </is>
       </c>
       <c r="G75" s="9" t="inlineStr">
@@ -52800,12 +52844,12 @@
       </c>
       <c r="B76" s="10" t="inlineStr">
         <is>
-          <t>P160032</t>
+          <t>P160022</t>
         </is>
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>P160032</t>
+          <t>P160022</t>
         </is>
       </c>
       <c r="D76" s="10" t="inlineStr">
@@ -52815,12 +52859,12 @@
       </c>
       <c r="E76" s="9" t="inlineStr">
         <is>
-          <t>24.78</t>
+          <t>25.72</t>
         </is>
       </c>
       <c r="F76" s="10" t="inlineStr">
         <is>
-          <t>ППК26119, 06.07.2026, CNP</t>
+          <t>ППК26118, 06.07.2026, CNP</t>
         </is>
       </c>
       <c r="G76" s="9" t="inlineStr">
@@ -52849,60 +52893,48 @@
       </c>
       <c r="B77" s="10" t="inlineStr">
         <is>
-          <t>SCR022601</t>
-        </is>
-      </c>
-      <c r="C77" s="9" t="inlineStr"/>
+          <t>P160032</t>
+        </is>
+      </c>
+      <c r="C77" s="9" t="inlineStr">
+        <is>
+          <t>P160032</t>
+        </is>
+      </c>
       <c r="D77" s="10" t="inlineStr">
         <is>
-          <t>Scrambler</t>
+          <t>GrapePie</t>
         </is>
       </c>
       <c r="E77" s="9" t="inlineStr">
         <is>
-          <t>21.92</t>
+          <t>24.78</t>
         </is>
       </c>
       <c r="F77" s="10" t="inlineStr">
         <is>
-          <t>ППК26116, 06.07.2026, CNP</t>
+          <t>ППК26119, 06.07.2026, CNP</t>
         </is>
       </c>
       <c r="G77" s="9" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>нема | none</t>
         </is>
       </c>
       <c r="H77" s="9" t="inlineStr">
         <is>
-          <t>22.00%</t>
-        </is>
-      </c>
-      <c r="I77" s="9" t="inlineStr">
-        <is>
-          <t>± 2.20%</t>
-        </is>
-      </c>
-      <c r="J77" s="9" t="inlineStr">
-        <is>
-          <t>19.80% – 24.20%</t>
-        </is>
-      </c>
+          <t>не е во залихата Т1/Т2/Т3 | not in T1/T2/T3 stock</t>
+        </is>
+      </c>
+      <c r="I77" s="9" t="inlineStr"/>
+      <c r="J77" s="9" t="inlineStr"/>
       <c r="K77" s="10" t="inlineStr">
         <is>
-          <t>Rainbow Sherbet</t>
-        </is>
-      </c>
-      <c r="L77" s="9" t="inlineStr">
-        <is>
-          <t>STEADY</t>
-        </is>
-      </c>
-      <c r="M77" s="9" t="inlineStr">
-        <is>
-          <t>ДА | YES</t>
-        </is>
-      </c>
+          <t>— не е во мастерот | not in master</t>
+        </is>
+      </c>
+      <c r="L77" s="9" t="inlineStr"/>
+      <c r="M77" s="9" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="9" t="n">
@@ -52910,44 +52942,60 @@
       </c>
       <c r="B78" s="10" t="inlineStr">
         <is>
-          <t>FB032601</t>
+          <t>SCR022601</t>
         </is>
       </c>
       <c r="C78" s="9" t="inlineStr"/>
       <c r="D78" s="10" t="inlineStr">
         <is>
-          <t>Fat Bastard</t>
+          <t>Scrambler</t>
         </is>
       </c>
       <c r="E78" s="9" t="inlineStr">
         <is>
-          <t>12.39</t>
+          <t>21.92</t>
         </is>
       </c>
       <c r="F78" s="10" t="inlineStr">
         <is>
-          <t>ППК26127, 21.07.2026, CNP</t>
+          <t>ППК26116, 06.07.2026, CNP</t>
         </is>
       </c>
       <c r="G78" s="9" t="inlineStr">
         <is>
-          <t>нема | none</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="H78" s="9" t="inlineStr">
         <is>
-          <t>не е во залихата Т1/Т2/Т3 | not in T1/T2/T3 stock</t>
-        </is>
-      </c>
-      <c r="I78" s="9" t="inlineStr"/>
-      <c r="J78" s="9" t="inlineStr"/>
+          <t>22.00%</t>
+        </is>
+      </c>
+      <c r="I78" s="9" t="inlineStr">
+        <is>
+          <t>± 2.20%</t>
+        </is>
+      </c>
+      <c r="J78" s="9" t="inlineStr">
+        <is>
+          <t>19.80% – 24.20%</t>
+        </is>
+      </c>
       <c r="K78" s="10" t="inlineStr">
         <is>
-          <t>— не е во мастерот | not in master</t>
-        </is>
-      </c>
-      <c r="L78" s="9" t="inlineStr"/>
-      <c r="M78" s="9" t="inlineStr"/>
+          <t>Rainbow Sherbet</t>
+        </is>
+      </c>
+      <c r="L78" s="9" t="inlineStr">
+        <is>
+          <t>STEADY</t>
+        </is>
+      </c>
+      <c r="M78" s="9" t="inlineStr">
+        <is>
+          <t>ДА | YES</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="9" t="n">
@@ -52955,23 +53003,23 @@
       </c>
       <c r="B79" s="10" t="inlineStr">
         <is>
-          <t>GG032601</t>
+          <t>FB032601</t>
         </is>
       </c>
       <c r="C79" s="9" t="inlineStr"/>
       <c r="D79" s="10" t="inlineStr">
         <is>
-          <t>Gorilla Glue</t>
+          <t>Fat Bastard</t>
         </is>
       </c>
       <c r="E79" s="9" t="inlineStr">
         <is>
-          <t>18.98</t>
+          <t>12.39</t>
         </is>
       </c>
       <c r="F79" s="10" t="inlineStr">
         <is>
-          <t>ППК26128, 21.07.2026, CNP</t>
+          <t>ППК26127, 21.07.2026, CNP</t>
         </is>
       </c>
       <c r="G79" s="9" t="inlineStr">
@@ -53000,64 +53048,44 @@
       </c>
       <c r="B80" s="10" t="inlineStr">
         <is>
-          <t>CC012601/1</t>
-        </is>
-      </c>
-      <c r="C80" s="9" t="inlineStr">
-        <is>
-          <t>P060332</t>
-        </is>
-      </c>
+          <t>GG032601</t>
+        </is>
+      </c>
+      <c r="C80" s="9" t="inlineStr"/>
       <c r="D80" s="10" t="inlineStr">
         <is>
-          <t>Cash Cow</t>
+          <t>Gorilla Glue</t>
         </is>
       </c>
       <c r="E80" s="9" t="inlineStr">
         <is>
-          <t>17.67</t>
+          <t>18.98</t>
         </is>
       </c>
       <c r="F80" s="10" t="inlineStr">
         <is>
-          <t>197-6-K-26, 07.08.2026, FHM</t>
+          <t>ППК26128, 21.07.2026, CNP</t>
         </is>
       </c>
       <c r="G80" s="9" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>нема | none</t>
         </is>
       </c>
       <c r="H80" s="9" t="inlineStr">
         <is>
-          <t>16.50%</t>
-        </is>
-      </c>
-      <c r="I80" s="9" t="inlineStr">
-        <is>
-          <t>± 1.65%</t>
-        </is>
-      </c>
-      <c r="J80" s="9" t="inlineStr">
-        <is>
-          <t>14.85% – 18.15%</t>
-        </is>
-      </c>
+          <t>не е во залихата Т1/Т2/Т3 | not in T1/T2/T3 stock</t>
+        </is>
+      </c>
+      <c r="I80" s="9" t="inlineStr"/>
+      <c r="J80" s="9" t="inlineStr"/>
       <c r="K80" s="10" t="inlineStr">
         <is>
-          <t>Payday</t>
-        </is>
-      </c>
-      <c r="L80" s="9" t="inlineStr">
-        <is>
-          <t>STEADY</t>
-        </is>
-      </c>
-      <c r="M80" s="9" t="inlineStr">
-        <is>
-          <t>ДА | YES</t>
-        </is>
-      </c>
+          <t>— не е во мастерот | not in master</t>
+        </is>
+      </c>
+      <c r="L80" s="9" t="inlineStr"/>
+      <c r="M80" s="9" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="9" t="n">
@@ -53065,27 +53093,27 @@
       </c>
       <c r="B81" s="10" t="inlineStr">
         <is>
-          <t>FB012602</t>
+          <t>CC012601/1</t>
         </is>
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>P060352</t>
+          <t>P060332</t>
         </is>
       </c>
       <c r="D81" s="10" t="inlineStr">
         <is>
-          <t>Fat Bastard</t>
+          <t>Cash Cow</t>
         </is>
       </c>
       <c r="E81" s="9" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>17.67</t>
         </is>
       </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
-          <t>197-7-K-26, 07.08.2026, FHM</t>
+          <t>197-6-K-26, 07.08.2026, FHM</t>
         </is>
       </c>
       <c r="G81" s="9" t="inlineStr">
@@ -53095,27 +53123,27 @@
       </c>
       <c r="H81" s="9" t="inlineStr">
         <is>
-          <t>19.50%</t>
+          <t>16.50%</t>
         </is>
       </c>
       <c r="I81" s="9" t="inlineStr">
         <is>
-          <t>± 1.95%</t>
+          <t>± 1.65%</t>
         </is>
       </c>
       <c r="J81" s="9" t="inlineStr">
         <is>
-          <t>17.55% – 21.45%</t>
+          <t>14.85% – 18.15%</t>
         </is>
       </c>
       <c r="K81" s="10" t="inlineStr">
         <is>
-          <t>Fat Sofa</t>
+          <t>Payday</t>
         </is>
       </c>
       <c r="L81" s="9" t="inlineStr">
         <is>
-          <t>CAYN</t>
+          <t>STEADY</t>
         </is>
       </c>
       <c r="M81" s="9" t="inlineStr">
@@ -53130,60 +53158,125 @@
       </c>
       <c r="B82" s="10" t="inlineStr">
         <is>
+          <t>FB012602</t>
+        </is>
+      </c>
+      <c r="C82" s="9" t="inlineStr">
+        <is>
+          <t>P060352</t>
+        </is>
+      </c>
+      <c r="D82" s="10" t="inlineStr">
+        <is>
+          <t>Fat Bastard</t>
+        </is>
+      </c>
+      <c r="E82" s="9" t="inlineStr">
+        <is>
+          <t>18.86</t>
+        </is>
+      </c>
+      <c r="F82" s="10" t="inlineStr">
+        <is>
+          <t>197-7-K-26, 07.08.2026, FHM</t>
+        </is>
+      </c>
+      <c r="G82" s="9" t="inlineStr">
+        <is>
+          <t>Pot.-2</t>
+        </is>
+      </c>
+      <c r="H82" s="9" t="inlineStr">
+        <is>
+          <t>19.50%</t>
+        </is>
+      </c>
+      <c r="I82" s="9" t="inlineStr">
+        <is>
+          <t>± 1.95%</t>
+        </is>
+      </c>
+      <c r="J82" s="9" t="inlineStr">
+        <is>
+          <t>17.55% – 21.45%</t>
+        </is>
+      </c>
+      <c r="K82" s="10" t="inlineStr">
+        <is>
+          <t>Fat Sofa</t>
+        </is>
+      </c>
+      <c r="L82" s="9" t="inlineStr">
+        <is>
+          <t>CAYN</t>
+        </is>
+      </c>
+      <c r="M82" s="9" t="inlineStr">
+        <is>
+          <t>ДА | YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="9" t="n">
+        <v>79</v>
+      </c>
+      <c r="B83" s="10" t="inlineStr">
+        <is>
           <t>SCR012603</t>
         </is>
       </c>
-      <c r="C82" s="9" t="inlineStr">
+      <c r="C83" s="9" t="inlineStr">
         <is>
           <t>P060382</t>
         </is>
       </c>
-      <c r="D82" s="10" t="inlineStr">
+      <c r="D83" s="10" t="inlineStr">
         <is>
           <t>Scrambler</t>
         </is>
       </c>
-      <c r="E82" s="9" t="inlineStr">
+      <c r="E83" s="9" t="inlineStr">
         <is>
           <t>17.84</t>
         </is>
       </c>
-      <c r="F82" s="10" t="inlineStr">
+      <c r="F83" s="10" t="inlineStr">
         <is>
           <t>197-21-K-26, 07.08.2026, FHM</t>
         </is>
       </c>
-      <c r="G82" s="9" t="inlineStr">
+      <c r="G83" s="9" t="inlineStr">
         <is>
           <t>Pot.-1</t>
         </is>
       </c>
-      <c r="H82" s="9" t="inlineStr">
+      <c r="H83" s="9" t="inlineStr">
         <is>
           <t>18.00%</t>
         </is>
       </c>
-      <c r="I82" s="9" t="inlineStr">
+      <c r="I83" s="9" t="inlineStr">
         <is>
           <t>± 1.79%</t>
         </is>
       </c>
-      <c r="J82" s="9" t="inlineStr">
+      <c r="J83" s="9" t="inlineStr">
         <is>
           <t>16.21% – 19.79%</t>
         </is>
       </c>
-      <c r="K82" s="10" t="inlineStr">
+      <c r="K83" s="10" t="inlineStr">
         <is>
           <t>Scrambler</t>
         </is>
       </c>
-      <c r="L82" s="9" t="inlineStr">
+      <c r="L83" s="9" t="inlineStr">
         <is>
           <t>CAYN</t>
         </is>
       </c>
-      <c r="M82" s="9" t="inlineStr">
+      <c r="M83" s="9" t="inlineStr">
         <is>
           <t>ДА | YES</t>
         </is>
@@ -55630,7 +55723,7 @@
       </c>
       <c r="I56" s="10" t="inlineStr">
         <is>
-          <t>J31112501 (?, 20.21%) | J31122501 (2025-12, 19.84%)</t>
+          <t>J31112501 (?, 20.21%) | J31122501 (hand-trimmed) (2025-12, 19.84%) | J31122501 (machine-trimmed) (2025-12, 21.84%)</t>
         </is>
       </c>
     </row>
@@ -58468,7 +58561,7 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>ППК25117 printed THC total 1.58 vs own components 15.38 — VERIFY ON PAPER; ППК25154 printed 1.87 same class; BSS052501 sheet 20.47 — probably the NGP result but the NGP scan parses as garbage, read off paper; GP062501 PP cert prints 24.89 vs tranche sheet 22.89 — QC decision; J31112501 sheet 25.00 = the March 051-5-K-26 result (25.27, CF-77/26), stale — superseded by the April retest 100-1-K-26 (20.21); J31122501 sheet 21.77 ≈ the 100-3-K-26 trimmed-sample result (21.84, CF-153/26) while the register carries the hand-trimmed 100-2-K-26 (19.84, CF-151/26) — same-day dual-preparation results: QC to decide which preparation is CoQ-forming.</t>
+          <t>ППК25117 printed THC total 1.58 vs own components 15.38 — VERIFY ON PAPER; ППК25154 printed 1.87 same class; BSS052501 sheet 20.47 — probably the NGP result but the NGP scan parses as garbage, read off paper; GP062501 PP cert prints 24.89 vs tranche sheet 22.89 — QC decision; J31112501 sheet 25.00 = the March 051-5-K-26 result (25.27, CF-77/26), stale — superseded by the April retest 100-1-K-26 (20.21); J31122501 RESOLVED 27.08.2026: QC designated the trimmed preparation (100-3-K-26, 21.84) as CoQ-forming; hand-trimmed 19.84 (100-2-K-26) kept as experimental processing-mode comparison of the same batch; tranche sheet prints 21.77 — transcription slip of 21.84, correct the sheet.</t>
         </is>
       </c>
     </row>

--- a/deliverables/qc_register/PP_QC_eCoA_Master_Register.xlsx
+++ b/deliverables/qc_register/PP_QC_eCoA_Master_Register.xlsx
@@ -37105,7 +37105,11 @@
           <t>JD112501</t>
         </is>
       </c>
-      <c r="C266" s="7" t="inlineStr"/>
+      <c r="C266" s="7" t="inlineStr">
+        <is>
+          <t>P060212</t>
+        </is>
+      </c>
       <c r="D266" s="8" t="inlineStr">
         <is>
           <t>Jelly Donutz</t>
@@ -39349,7 +39353,11 @@
           <t>JD012603_02</t>
         </is>
       </c>
-      <c r="C282" s="7" t="inlineStr"/>
+      <c r="C282" s="7" t="inlineStr">
+        <is>
+          <t>P060412</t>
+        </is>
+      </c>
       <c r="D282" s="8" t="inlineStr">
         <is>
           <t>JellyDonutz</t>
@@ -39495,7 +39503,11 @@
           <t>JD012603_02V</t>
         </is>
       </c>
-      <c r="C283" s="7" t="inlineStr"/>
+      <c r="C283" s="7" t="inlineStr">
+        <is>
+          <t>P060422</t>
+        </is>
+      </c>
       <c r="D283" s="8" t="inlineStr">
         <is>
           <t>JellyDonutz</t>
@@ -46129,7 +46141,11 @@
           <t>JD112501</t>
         </is>
       </c>
-      <c r="C102" s="9" t="inlineStr"/>
+      <c r="C102" s="9" t="inlineStr">
+        <is>
+          <t>P060212</t>
+        </is>
+      </c>
       <c r="D102" s="9" t="inlineStr">
         <is>
           <t>19.64</t>
@@ -46257,7 +46273,11 @@
           <t>JD012603_02</t>
         </is>
       </c>
-      <c r="C106" s="9" t="inlineStr"/>
+      <c r="C106" s="9" t="inlineStr">
+        <is>
+          <t>P060412</t>
+        </is>
+      </c>
       <c r="D106" s="9" t="inlineStr">
         <is>
           <t>20.54</t>
@@ -46298,7 +46318,11 @@
           <t>JD012603_02V</t>
         </is>
       </c>
-      <c r="C107" s="9" t="inlineStr"/>
+      <c r="C107" s="9" t="inlineStr">
+        <is>
+          <t>P060422</t>
+        </is>
+      </c>
       <c r="D107" s="9" t="inlineStr">
         <is>
           <t>15.16</t>
@@ -52285,7 +52309,11 @@
           <t>JD112501</t>
         </is>
       </c>
-      <c r="C66" s="9" t="inlineStr"/>
+      <c r="C66" s="9" t="inlineStr">
+        <is>
+          <t>P060212</t>
+        </is>
+      </c>
       <c r="D66" s="10" t="inlineStr">
         <is>
           <t>Jelly Donutz</t>
@@ -52631,7 +52659,11 @@
           <t>JD012603_02</t>
         </is>
       </c>
-      <c r="C72" s="9" t="inlineStr"/>
+      <c r="C72" s="9" t="inlineStr">
+        <is>
+          <t>P060412</t>
+        </is>
+      </c>
       <c r="D72" s="10" t="inlineStr">
         <is>
           <t>JellyDonutz</t>
@@ -52692,7 +52724,11 @@
           <t>JD012603_02V</t>
         </is>
       </c>
-      <c r="C73" s="9" t="inlineStr"/>
+      <c r="C73" s="9" t="inlineStr">
+        <is>
+          <t>P060422</t>
+        </is>
+      </c>
       <c r="D73" s="10" t="inlineStr">
         <is>
           <t>JellyDonutz</t>

--- a/deliverables/qc_register/PP_QC_eCoA_Master_Register.xlsx
+++ b/deliverables/qc_register/PP_QC_eCoA_Master_Register.xlsx
@@ -35855,8 +35855,16 @@
           <t>GG012601*</t>
         </is>
       </c>
-      <c r="C257" s="15" t="inlineStr"/>
-      <c r="D257" s="16" t="inlineStr"/>
+      <c r="C257" s="15" t="inlineStr">
+        <is>
+          <t>P060302</t>
+        </is>
+      </c>
+      <c r="D257" s="16" t="inlineStr">
+        <is>
+          <t>Gorilla Glue</t>
+        </is>
+      </c>
       <c r="E257" s="9" t="inlineStr">
         <is>
           <t>/</t>
@@ -36691,8 +36699,16 @@
           <t>JD012601*</t>
         </is>
       </c>
-      <c r="C263" s="15" t="inlineStr"/>
-      <c r="D263" s="16" t="inlineStr"/>
+      <c r="C263" s="15" t="inlineStr">
+        <is>
+          <t>P060312</t>
+        </is>
+      </c>
+      <c r="D263" s="16" t="inlineStr">
+        <is>
+          <t>Jelly Donutz</t>
+        </is>
+      </c>
       <c r="E263" s="9" t="inlineStr">
         <is>
           <t>/</t>
@@ -37800,7 +37816,11 @@
         </is>
       </c>
       <c r="C271" s="15" t="inlineStr"/>
-      <c r="D271" s="16" t="inlineStr"/>
+      <c r="D271" s="16" t="inlineStr">
+        <is>
+          <t>Jelly Donutz</t>
+        </is>
+      </c>
       <c r="E271" s="9" t="inlineStr">
         <is>
           <t>/</t>
@@ -42646,7 +42666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I164"/>
+  <dimension ref="A1:I163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -44371,7 +44391,7 @@
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>Gorilla Glue      6 batch(es)</t>
+          <t>Gorilla Glue      7 batch(es)</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr"/>
@@ -44613,17 +44633,17 @@
       </c>
       <c r="B59" s="12" t="inlineStr">
         <is>
-          <t>GG112501</t>
+          <t>GG012601*</t>
         </is>
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>P060252</t>
+          <t>P060302</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>17.94</t>
+          <t>15.35</t>
         </is>
       </c>
       <c r="E59" s="9" t="inlineStr">
@@ -44633,7 +44653,7 @@
       </c>
       <c r="F59" s="9" t="inlineStr">
         <is>
-          <t>ППК26061</t>
+          <t>ППК26062</t>
         </is>
       </c>
       <c r="G59" s="9" t="inlineStr">
@@ -44658,276 +44678,290 @@
       </c>
       <c r="B60" s="12" t="inlineStr">
         <is>
+          <t>GG112501</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="inlineStr">
+        <is>
+          <t>P060252</t>
+        </is>
+      </c>
+      <c r="D60" s="9" t="inlineStr">
+        <is>
+          <t>17.94</t>
+        </is>
+      </c>
+      <c r="E60" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F60" s="9" t="inlineStr">
+        <is>
+          <t>ППК26061</t>
+        </is>
+      </c>
+      <c r="G60" s="9" t="inlineStr">
+        <is>
+          <t>11.05.2026</t>
+        </is>
+      </c>
+      <c r="H60" s="10" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy — Center for Natural Products</t>
+        </is>
+      </c>
+      <c r="I60" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="B61" s="12" t="inlineStr">
+        <is>
           <t>GG012603</t>
         </is>
       </c>
-      <c r="C60" s="9" t="inlineStr">
+      <c r="C61" s="9" t="inlineStr">
         <is>
           <t>P060402</t>
         </is>
       </c>
-      <c r="D60" s="9" t="inlineStr">
+      <c r="D61" s="9" t="inlineStr">
         <is>
           <t>17.59</t>
         </is>
       </c>
-      <c r="E60" s="9" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="F60" s="9" t="inlineStr">
+      <c r="E61" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F61" s="9" t="inlineStr">
         <is>
           <t>ППК26114</t>
         </is>
       </c>
-      <c r="G60" s="9" t="inlineStr">
+      <c r="G61" s="9" t="inlineStr">
         <is>
           <t>30.06.2026</t>
         </is>
       </c>
-      <c r="H60" s="10" t="inlineStr">
+      <c r="H61" s="10" t="inlineStr">
         <is>
           <t>UKIM Faculty of Pharmacy — Center for Natural Products</t>
         </is>
       </c>
-      <c r="I60" s="11" t="inlineStr">
+      <c r="I61" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="9" t="inlineStr"/>
-      <c r="B61" s="10" t="inlineStr"/>
-      <c r="C61" s="9" t="inlineStr"/>
-      <c r="D61" s="9" t="inlineStr">
-        <is>
-          <t>16.70</t>
-        </is>
-      </c>
-      <c r="E61" s="9" t="inlineStr"/>
-      <c r="F61" s="9" t="inlineStr">
-        <is>
-          <t>197-8-K-26</t>
-        </is>
-      </c>
-      <c r="G61" s="9" t="inlineStr">
-        <is>
-          <t>07.08.2026</t>
-        </is>
-      </c>
-      <c r="H61" s="10" t="inlineStr">
-        <is>
-          <t>Farmahem</t>
-        </is>
-      </c>
-      <c r="I61" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
     <row r="62">
-      <c r="A62" s="9" t="n">
-        <v>29</v>
-      </c>
-      <c r="B62" s="12" t="inlineStr">
-        <is>
-          <t>GG032601</t>
-        </is>
-      </c>
+      <c r="A62" s="9" t="inlineStr"/>
+      <c r="B62" s="10" t="inlineStr"/>
       <c r="C62" s="9" t="inlineStr"/>
       <c r="D62" s="9" t="inlineStr">
         <is>
+          <t>16.70</t>
+        </is>
+      </c>
+      <c r="E62" s="9" t="inlineStr"/>
+      <c r="F62" s="9" t="inlineStr">
+        <is>
+          <t>197-8-K-26</t>
+        </is>
+      </c>
+      <c r="G62" s="9" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="H62" s="10" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I62" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="B63" s="12" t="inlineStr">
+        <is>
+          <t>GG032601</t>
+        </is>
+      </c>
+      <c r="C63" s="9" t="inlineStr"/>
+      <c r="D63" s="9" t="inlineStr">
+        <is>
           <t>18.98</t>
         </is>
       </c>
-      <c r="E62" s="9" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="F62" s="9" t="inlineStr">
+      <c r="E63" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F63" s="9" t="inlineStr">
         <is>
           <t>ППК26128</t>
         </is>
       </c>
-      <c r="G62" s="9" t="inlineStr">
+      <c r="G63" s="9" t="inlineStr">
         <is>
           <t>21.07.2026</t>
         </is>
       </c>
-      <c r="H62" s="10" t="inlineStr">
+      <c r="H63" s="10" t="inlineStr">
         <is>
           <t>UKIM Faculty of Pharmacy — Center for Natural Products</t>
         </is>
       </c>
-      <c r="I62" s="11" t="inlineStr">
+      <c r="I63" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="6" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
         <is>
           <t>Grape Pie      10 batch(es)</t>
         </is>
       </c>
-      <c r="B63" s="7" t="inlineStr"/>
-      <c r="C63" s="7" t="inlineStr"/>
-      <c r="D63" s="7" t="inlineStr"/>
-      <c r="E63" s="7" t="inlineStr"/>
-      <c r="F63" s="7" t="inlineStr"/>
-      <c r="G63" s="7" t="inlineStr"/>
-      <c r="H63" s="7" t="inlineStr"/>
-      <c r="I63" s="7" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="B64" s="12" t="inlineStr">
+      <c r="B64" s="7" t="inlineStr"/>
+      <c r="C64" s="7" t="inlineStr"/>
+      <c r="D64" s="7" t="inlineStr"/>
+      <c r="E64" s="7" t="inlineStr"/>
+      <c r="F64" s="7" t="inlineStr"/>
+      <c r="G64" s="7" t="inlineStr"/>
+      <c r="H64" s="7" t="inlineStr"/>
+      <c r="I64" s="7" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="9" t="n">
+        <v>31</v>
+      </c>
+      <c r="B65" s="12" t="inlineStr">
         <is>
           <t>GP0824_01</t>
         </is>
       </c>
-      <c r="C64" s="9" t="inlineStr">
+      <c r="C65" s="9" t="inlineStr">
         <is>
           <t>P050102</t>
         </is>
       </c>
-      <c r="D64" s="9" t="inlineStr">
+      <c r="D65" s="9" t="inlineStr">
         <is>
           <t>20.79</t>
         </is>
       </c>
-      <c r="E64" s="9" t="inlineStr">
+      <c r="E65" s="9" t="inlineStr">
         <is>
           <t>18.00–22.00%</t>
         </is>
       </c>
-      <c r="F64" s="9" t="inlineStr">
+      <c r="F65" s="9" t="inlineStr">
         <is>
           <t>QCCoA 001</t>
         </is>
       </c>
-      <c r="G64" s="9" t="inlineStr">
+      <c r="G65" s="9" t="inlineStr">
         <is>
           <t>06.08.2025</t>
         </is>
       </c>
-      <c r="H64" s="10" t="inlineStr">
+      <c r="H65" s="10" t="inlineStr">
         <is>
           <t>Purely Plant (in-house)</t>
         </is>
       </c>
-      <c r="I64" s="11" t="inlineStr">
+      <c r="I65" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="9" t="inlineStr"/>
-      <c r="B65" s="10" t="inlineStr"/>
-      <c r="C65" s="9" t="inlineStr"/>
-      <c r="D65" s="9" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="9" t="inlineStr"/>
+      <c r="B66" s="10" t="inlineStr"/>
+      <c r="C66" s="9" t="inlineStr"/>
+      <c r="D66" s="9" t="inlineStr">
         <is>
           <t>20.79</t>
         </is>
       </c>
-      <c r="E65" s="9" t="inlineStr"/>
-      <c r="F65" s="9" t="inlineStr">
+      <c r="E66" s="9" t="inlineStr"/>
+      <c r="F66" s="9" t="inlineStr">
         <is>
           <t>ППК25105</t>
         </is>
       </c>
-      <c r="G65" s="9" t="inlineStr">
+      <c r="G66" s="9" t="inlineStr">
         <is>
           <t>17.04.2025</t>
         </is>
       </c>
-      <c r="H65" s="10" t="inlineStr">
+      <c r="H66" s="10" t="inlineStr">
         <is>
           <t>UKIM Faculty of Pharmacy — Center for Natural Products</t>
         </is>
       </c>
-      <c r="I65" s="11" t="inlineStr">
+      <c r="I66" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="9" t="n">
-        <v>31</v>
-      </c>
-      <c r="B66" s="12" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="9" t="n">
+        <v>32</v>
+      </c>
+      <c r="B67" s="12" t="inlineStr">
         <is>
           <t>GP0824_02</t>
         </is>
       </c>
-      <c r="C66" s="9" t="inlineStr">
+      <c r="C67" s="9" t="inlineStr">
         <is>
           <t>P050022</t>
         </is>
       </c>
-      <c r="D66" s="9" t="inlineStr">
+      <c r="D67" s="9" t="inlineStr">
         <is>
           <t>22.61</t>
         </is>
       </c>
-      <c r="E66" s="9" t="inlineStr">
+      <c r="E67" s="9" t="inlineStr">
         <is>
           <t>22.00–26.00%</t>
         </is>
       </c>
-      <c r="F66" s="9" t="inlineStr">
+      <c r="F67" s="9" t="inlineStr">
         <is>
           <t>197-11-K-26</t>
         </is>
       </c>
-      <c r="G66" s="9" t="inlineStr">
+      <c r="G67" s="9" t="inlineStr">
         <is>
           <t>07.08.2026</t>
         </is>
       </c>
-      <c r="H66" s="10" t="inlineStr">
+      <c r="H67" s="10" t="inlineStr">
         <is>
           <t>Farmahem</t>
-        </is>
-      </c>
-      <c r="I66" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="9" t="inlineStr"/>
-      <c r="B67" s="10" t="inlineStr"/>
-      <c r="C67" s="9" t="inlineStr"/>
-      <c r="D67" s="9" t="inlineStr">
-        <is>
-          <t>23.79</t>
-        </is>
-      </c>
-      <c r="E67" s="9" t="inlineStr"/>
-      <c r="F67" s="9" t="inlineStr">
-        <is>
-          <t>QCCoA 001</t>
-        </is>
-      </c>
-      <c r="G67" s="9" t="inlineStr">
-        <is>
-          <t>10.07.2025</t>
-        </is>
-      </c>
-      <c r="H67" s="10" t="inlineStr">
-        <is>
-          <t>Purely Plant (in-house)</t>
         </is>
       </c>
       <c r="I67" s="11" t="inlineStr">
@@ -44942,7 +44976,7 @@
       <c r="C68" s="9" t="inlineStr"/>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>23.19</t>
+          <t>23.79</t>
         </is>
       </c>
       <c r="E68" s="9" t="inlineStr"/>
@@ -44953,7 +44987,7 @@
       </c>
       <c r="G68" s="9" t="inlineStr">
         <is>
-          <t>17.07.2025</t>
+          <t>10.07.2025</t>
         </is>
       </c>
       <c r="H68" s="10" t="inlineStr">
@@ -44979,17 +45013,17 @@
       <c r="E69" s="9" t="inlineStr"/>
       <c r="F69" s="9" t="inlineStr">
         <is>
-          <t>ППК25174</t>
+          <t>QCCoA 001</t>
         </is>
       </c>
       <c r="G69" s="9" t="inlineStr">
         <is>
-          <t>10.07.2025</t>
+          <t>17.07.2025</t>
         </is>
       </c>
       <c r="H69" s="10" t="inlineStr">
         <is>
-          <t>UKIM Faculty of Pharmacy — Center for Natural Products</t>
+          <t>Purely Plant (in-house)</t>
         </is>
       </c>
       <c r="I69" s="11" t="inlineStr">
@@ -45004,220 +45038,206 @@
       <c r="C70" s="9" t="inlineStr"/>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>23.79</t>
+          <t>23.19</t>
         </is>
       </c>
       <c r="E70" s="9" t="inlineStr"/>
       <c r="F70" s="9" t="inlineStr">
         <is>
+          <t>ППК25174</t>
+        </is>
+      </c>
+      <c r="G70" s="9" t="inlineStr">
+        <is>
+          <t>10.07.2025</t>
+        </is>
+      </c>
+      <c r="H70" s="10" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy — Center for Natural Products</t>
+        </is>
+      </c>
+      <c r="I70" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="9" t="inlineStr"/>
+      <c r="B71" s="10" t="inlineStr"/>
+      <c r="C71" s="9" t="inlineStr"/>
+      <c r="D71" s="9" t="inlineStr">
+        <is>
+          <t>23.79</t>
+        </is>
+      </c>
+      <c r="E71" s="9" t="inlineStr"/>
+      <c r="F71" s="9" t="inlineStr">
+        <is>
           <t>ППК25139</t>
         </is>
       </c>
-      <c r="G70" s="9" t="inlineStr">
+      <c r="G71" s="9" t="inlineStr">
         <is>
           <t>22.05.2025</t>
         </is>
       </c>
-      <c r="H70" s="10" t="inlineStr">
+      <c r="H71" s="10" t="inlineStr">
         <is>
           <t>UKIM Faculty of Pharmacy — Center for Natural Products</t>
         </is>
       </c>
-      <c r="I70" s="11" t="inlineStr">
+      <c r="I71" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="9" t="n">
-        <v>32</v>
-      </c>
-      <c r="B71" s="12" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="9" t="n">
+        <v>33</v>
+      </c>
+      <c r="B72" s="12" t="inlineStr">
         <is>
           <t>GP0824_03</t>
         </is>
       </c>
-      <c r="C71" s="9" t="inlineStr">
+      <c r="C72" s="9" t="inlineStr">
         <is>
           <t>P050072</t>
         </is>
       </c>
-      <c r="D71" s="9" t="inlineStr">
+      <c r="D72" s="9" t="inlineStr">
         <is>
           <t>25.45</t>
         </is>
       </c>
-      <c r="E71" s="9" t="inlineStr">
+      <c r="E72" s="9" t="inlineStr">
         <is>
           <t>22.00–26.00%</t>
         </is>
       </c>
-      <c r="F71" s="9" t="inlineStr">
+      <c r="F72" s="9" t="inlineStr">
         <is>
           <t>QCCoA 001</t>
         </is>
       </c>
-      <c r="G71" s="9" t="inlineStr">
+      <c r="G72" s="9" t="inlineStr">
         <is>
           <t>17.07.2025</t>
         </is>
       </c>
-      <c r="H71" s="10" t="inlineStr">
+      <c r="H72" s="10" t="inlineStr">
         <is>
           <t>Purely Plant (in-house)</t>
         </is>
       </c>
-      <c r="I71" s="11" t="inlineStr">
+      <c r="I72" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="9" t="inlineStr"/>
-      <c r="B72" s="10" t="inlineStr"/>
-      <c r="C72" s="9" t="inlineStr"/>
-      <c r="D72" s="9" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="9" t="inlineStr"/>
+      <c r="B73" s="10" t="inlineStr"/>
+      <c r="C73" s="9" t="inlineStr"/>
+      <c r="D73" s="9" t="inlineStr">
         <is>
           <t>25.45</t>
         </is>
       </c>
-      <c r="E72" s="9" t="inlineStr"/>
-      <c r="F72" s="9" t="inlineStr">
+      <c r="E73" s="9" t="inlineStr"/>
+      <c r="F73" s="9" t="inlineStr">
         <is>
           <t>ППК25175</t>
         </is>
       </c>
-      <c r="G72" s="9" t="inlineStr">
+      <c r="G73" s="9" t="inlineStr">
         <is>
           <t>10.07.2025</t>
         </is>
       </c>
-      <c r="H72" s="10" t="inlineStr">
+      <c r="H73" s="10" t="inlineStr">
         <is>
           <t>UKIM Faculty of Pharmacy — Center for Natural Products</t>
         </is>
       </c>
-      <c r="I72" s="11" t="inlineStr">
+      <c r="I73" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="9" t="n">
-        <v>33</v>
-      </c>
-      <c r="B73" s="12" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="9" t="n">
+        <v>34</v>
+      </c>
+      <c r="B74" s="12" t="inlineStr">
         <is>
           <t>GP052501</t>
         </is>
       </c>
-      <c r="C73" s="9" t="inlineStr">
+      <c r="C74" s="9" t="inlineStr">
         <is>
           <t>P050152</t>
         </is>
       </c>
-      <c r="D73" s="9" t="inlineStr">
+      <c r="D74" s="9" t="inlineStr">
         <is>
           <t>18.98</t>
         </is>
       </c>
-      <c r="E73" s="9" t="inlineStr">
+      <c r="E74" s="9" t="inlineStr">
         <is>
           <t>18.00–22.00%</t>
         </is>
       </c>
-      <c r="F73" s="9" t="inlineStr">
+      <c r="F74" s="9" t="inlineStr">
         <is>
           <t>ППК25279</t>
         </is>
       </c>
-      <c r="G73" s="9" t="inlineStr">
+      <c r="G74" s="9" t="inlineStr">
         <is>
           <t>19.09.2025</t>
         </is>
       </c>
-      <c r="H73" s="10" t="inlineStr">
+      <c r="H74" s="10" t="inlineStr">
         <is>
           <t>UKIM Faculty of Pharmacy — Center for Natural Products</t>
         </is>
       </c>
-      <c r="I73" s="11" t="inlineStr">
+      <c r="I74" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="9" t="inlineStr"/>
-      <c r="B74" s="10" t="inlineStr"/>
-      <c r="C74" s="9" t="inlineStr"/>
-      <c r="D74" s="9" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="9" t="inlineStr"/>
+      <c r="B75" s="10" t="inlineStr"/>
+      <c r="C75" s="9" t="inlineStr"/>
+      <c r="D75" s="9" t="inlineStr">
         <is>
           <t>18.52</t>
         </is>
       </c>
-      <c r="E74" s="9" t="inlineStr"/>
-      <c r="F74" s="9" t="inlineStr">
+      <c r="E75" s="9" t="inlineStr"/>
+      <c r="F75" s="9" t="inlineStr">
         <is>
           <t>197-10-K-26</t>
         </is>
       </c>
-      <c r="G74" s="9" t="inlineStr">
+      <c r="G75" s="9" t="inlineStr">
         <is>
           <t>07.08.2026</t>
         </is>
       </c>
-      <c r="H74" s="10" t="inlineStr">
+      <c r="H75" s="10" t="inlineStr">
         <is>
           <t>Farmahem</t>
-        </is>
-      </c>
-      <c r="I74" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="9" t="n">
-        <v>34</v>
-      </c>
-      <c r="B75" s="12" t="inlineStr">
-        <is>
-          <t>GP062501</t>
-        </is>
-      </c>
-      <c r="C75" s="9" t="inlineStr">
-        <is>
-          <t>P050202</t>
-        </is>
-      </c>
-      <c r="D75" s="9" t="inlineStr">
-        <is>
-          <t>24.89</t>
-        </is>
-      </c>
-      <c r="E75" s="9" t="inlineStr">
-        <is>
-          <t>22.00–26.00%</t>
-        </is>
-      </c>
-      <c r="F75" s="9" t="inlineStr">
-        <is>
-          <t>QCCoA 001v02</t>
-        </is>
-      </c>
-      <c r="G75" s="9" t="inlineStr">
-        <is>
-          <t>04.12.2025</t>
-        </is>
-      </c>
-      <c r="H75" s="10" t="inlineStr">
-        <is>
-          <t>Purely Plant (in-house)</t>
         </is>
       </c>
       <c r="I75" s="11" t="inlineStr">
@@ -45232,296 +45252,310 @@
       </c>
       <c r="B76" s="12" t="inlineStr">
         <is>
+          <t>GP062501</t>
+        </is>
+      </c>
+      <c r="C76" s="9" t="inlineStr">
+        <is>
+          <t>P050202</t>
+        </is>
+      </c>
+      <c r="D76" s="9" t="inlineStr">
+        <is>
+          <t>24.89</t>
+        </is>
+      </c>
+      <c r="E76" s="9" t="inlineStr">
+        <is>
+          <t>22.00–26.00%</t>
+        </is>
+      </c>
+      <c r="F76" s="9" t="inlineStr">
+        <is>
+          <t>QCCoA 001v02</t>
+        </is>
+      </c>
+      <c r="G76" s="9" t="inlineStr">
+        <is>
+          <t>04.12.2025</t>
+        </is>
+      </c>
+      <c r="H76" s="10" t="inlineStr">
+        <is>
+          <t>Purely Plant (in-house)</t>
+        </is>
+      </c>
+      <c r="I76" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="B77" s="12" t="inlineStr">
+        <is>
           <t>GP072501/1</t>
         </is>
       </c>
-      <c r="C76" s="9" t="inlineStr">
+      <c r="C77" s="9" t="inlineStr">
         <is>
           <t>P050292</t>
         </is>
       </c>
-      <c r="D76" s="9" t="inlineStr">
+      <c r="D77" s="9" t="inlineStr">
         <is>
           <t>21.36</t>
         </is>
       </c>
-      <c r="E76" s="9" t="inlineStr">
+      <c r="E77" s="9" t="inlineStr">
         <is>
           <t>18.00–22.00%</t>
         </is>
       </c>
-      <c r="F76" s="9" t="inlineStr">
+      <c r="F77" s="9" t="inlineStr">
         <is>
           <t>QCCoA 001v02</t>
         </is>
       </c>
-      <c r="G76" s="9" t="inlineStr">
+      <c r="G77" s="9" t="inlineStr">
         <is>
           <t>21.01.2026</t>
         </is>
       </c>
-      <c r="H76" s="10" t="inlineStr">
+      <c r="H77" s="10" t="inlineStr">
         <is>
           <t>Purely Plant (in-house)</t>
         </is>
       </c>
-      <c r="I76" s="11" t="inlineStr">
+      <c r="I77" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="9" t="inlineStr"/>
-      <c r="B77" s="10" t="inlineStr"/>
-      <c r="C77" s="9" t="inlineStr"/>
-      <c r="D77" s="9" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="9" t="inlineStr"/>
+      <c r="B78" s="10" t="inlineStr"/>
+      <c r="C78" s="9" t="inlineStr"/>
+      <c r="D78" s="9" t="inlineStr">
         <is>
           <t>21.36</t>
         </is>
       </c>
-      <c r="E77" s="9" t="inlineStr"/>
-      <c r="F77" s="9" t="inlineStr">
+      <c r="E78" s="9" t="inlineStr"/>
+      <c r="F78" s="9" t="inlineStr">
         <is>
           <t>ППК25378</t>
         </is>
       </c>
-      <c r="G77" s="9" t="inlineStr">
+      <c r="G78" s="9" t="inlineStr">
         <is>
           <t>12.12.2025</t>
         </is>
       </c>
-      <c r="H77" s="10" t="inlineStr">
+      <c r="H78" s="10" t="inlineStr">
         <is>
           <t>UKIM Faculty of Pharmacy — Center for Natural Products</t>
         </is>
       </c>
-      <c r="I77" s="11" t="inlineStr">
+      <c r="I78" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="B78" s="12" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="B79" s="12" t="inlineStr">
         <is>
           <t>GP072501/2</t>
         </is>
       </c>
-      <c r="C78" s="9" t="inlineStr">
+      <c r="C79" s="9" t="inlineStr">
         <is>
           <t>P050302</t>
         </is>
       </c>
-      <c r="D78" s="9" t="inlineStr">
+      <c r="D79" s="9" t="inlineStr">
         <is>
           <t>19.81</t>
         </is>
       </c>
-      <c r="E78" s="9" t="inlineStr">
+      <c r="E79" s="9" t="inlineStr">
         <is>
           <t>18.00–22.00%</t>
         </is>
       </c>
-      <c r="F78" s="9" t="inlineStr">
+      <c r="F79" s="9" t="inlineStr">
         <is>
           <t>QCCoA 001v02</t>
         </is>
       </c>
-      <c r="G78" s="9" t="inlineStr">
+      <c r="G79" s="9" t="inlineStr">
         <is>
           <t>21.01.2026</t>
         </is>
       </c>
-      <c r="H78" s="10" t="inlineStr">
+      <c r="H79" s="10" t="inlineStr">
         <is>
           <t>Purely Plant (in-house)</t>
         </is>
       </c>
-      <c r="I78" s="11" t="inlineStr">
+      <c r="I79" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="9" t="inlineStr"/>
-      <c r="B79" s="10" t="inlineStr"/>
-      <c r="C79" s="9" t="inlineStr"/>
-      <c r="D79" s="9" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="9" t="inlineStr"/>
+      <c r="B80" s="10" t="inlineStr"/>
+      <c r="C80" s="9" t="inlineStr"/>
+      <c r="D80" s="9" t="inlineStr">
         <is>
           <t>19.81</t>
         </is>
       </c>
-      <c r="E79" s="9" t="inlineStr"/>
-      <c r="F79" s="9" t="inlineStr">
+      <c r="E80" s="9" t="inlineStr"/>
+      <c r="F80" s="9" t="inlineStr">
         <is>
           <t>ППК25379</t>
         </is>
       </c>
-      <c r="G79" s="9" t="inlineStr">
+      <c r="G80" s="9" t="inlineStr">
         <is>
           <t>12.12.2025</t>
         </is>
       </c>
-      <c r="H79" s="10" t="inlineStr">
+      <c r="H80" s="10" t="inlineStr">
         <is>
           <t>UKIM Faculty of Pharmacy — Center for Natural Products</t>
         </is>
       </c>
-      <c r="I79" s="11" t="inlineStr">
+      <c r="I80" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="B80" s="12" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="9" t="n">
+        <v>38</v>
+      </c>
+      <c r="B81" s="12" t="inlineStr">
         <is>
           <t>GP082501/1</t>
         </is>
       </c>
-      <c r="C80" s="9" t="inlineStr">
+      <c r="C81" s="9" t="inlineStr">
         <is>
           <t>P050312</t>
         </is>
       </c>
-      <c r="D80" s="9" t="inlineStr">
+      <c r="D81" s="9" t="inlineStr">
         <is>
           <t>21.29</t>
         </is>
       </c>
-      <c r="E80" s="9" t="inlineStr">
+      <c r="E81" s="9" t="inlineStr">
         <is>
           <t>18.00–22.00%</t>
         </is>
       </c>
-      <c r="F80" s="9" t="inlineStr">
+      <c r="F81" s="9" t="inlineStr">
         <is>
           <t>QCCoA 001v02</t>
         </is>
       </c>
-      <c r="G80" s="9" t="inlineStr">
+      <c r="G81" s="9" t="inlineStr">
         <is>
           <t>21.01.2026</t>
         </is>
       </c>
-      <c r="H80" s="10" t="inlineStr">
+      <c r="H81" s="10" t="inlineStr">
         <is>
           <t>Purely Plant (in-house)</t>
         </is>
       </c>
-      <c r="I80" s="11" t="inlineStr">
+      <c r="I81" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="9" t="inlineStr"/>
-      <c r="B81" s="10" t="inlineStr"/>
-      <c r="C81" s="9" t="inlineStr"/>
-      <c r="D81" s="9" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="9" t="inlineStr"/>
+      <c r="B82" s="10" t="inlineStr"/>
+      <c r="C82" s="9" t="inlineStr"/>
+      <c r="D82" s="9" t="inlineStr">
         <is>
           <t>21.29</t>
         </is>
       </c>
-      <c r="E81" s="9" t="inlineStr"/>
-      <c r="F81" s="9" t="inlineStr">
+      <c r="E82" s="9" t="inlineStr"/>
+      <c r="F82" s="9" t="inlineStr">
         <is>
           <t>ППК25380</t>
         </is>
       </c>
-      <c r="G81" s="9" t="inlineStr">
+      <c r="G82" s="9" t="inlineStr">
         <is>
           <t>12.12.2025</t>
         </is>
       </c>
-      <c r="H81" s="10" t="inlineStr">
+      <c r="H82" s="10" t="inlineStr">
         <is>
           <t>UKIM Faculty of Pharmacy — Center for Natural Products</t>
         </is>
       </c>
-      <c r="I81" s="11" t="inlineStr">
+      <c r="I82" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="9" t="n">
-        <v>38</v>
-      </c>
-      <c r="B82" s="12" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="9" t="n">
+        <v>39</v>
+      </c>
+      <c r="B83" s="12" t="inlineStr">
         <is>
           <t>GP082501/2</t>
         </is>
       </c>
-      <c r="C82" s="9" t="inlineStr">
+      <c r="C83" s="9" t="inlineStr">
         <is>
           <t>P050322</t>
         </is>
       </c>
-      <c r="D82" s="9" t="inlineStr">
+      <c r="D83" s="9" t="inlineStr">
         <is>
           <t>14.83</t>
         </is>
       </c>
-      <c r="E82" s="9" t="inlineStr">
+      <c r="E83" s="9" t="inlineStr">
         <is>
           <t>13.83–18.00%</t>
         </is>
       </c>
-      <c r="F82" s="9" t="inlineStr">
+      <c r="F83" s="9" t="inlineStr">
         <is>
           <t>QCCoA 001v02</t>
         </is>
       </c>
-      <c r="G82" s="9" t="inlineStr">
+      <c r="G83" s="9" t="inlineStr">
         <is>
           <t>21.01.2026</t>
         </is>
       </c>
-      <c r="H82" s="10" t="inlineStr">
+      <c r="H83" s="10" t="inlineStr">
         <is>
           <t>Purely Plant (in-house)</t>
-        </is>
-      </c>
-      <c r="I82" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="9" t="inlineStr"/>
-      <c r="B83" s="10" t="inlineStr"/>
-      <c r="C83" s="9" t="inlineStr"/>
-      <c r="D83" s="9" t="inlineStr">
-        <is>
-          <t>14.83</t>
-        </is>
-      </c>
-      <c r="E83" s="9" t="inlineStr"/>
-      <c r="F83" s="9" t="inlineStr">
-        <is>
-          <t>ППК25381</t>
-        </is>
-      </c>
-      <c r="G83" s="9" t="inlineStr">
-        <is>
-          <t>12.12.2025</t>
-        </is>
-      </c>
-      <c r="H83" s="10" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy — Center for Natural Products</t>
         </is>
       </c>
       <c r="I83" s="11" t="inlineStr">
@@ -45536,166 +45570,152 @@
       <c r="C84" s="9" t="inlineStr"/>
       <c r="D84" s="9" t="inlineStr">
         <is>
-          <t>15.70</t>
+          <t>14.83</t>
         </is>
       </c>
       <c r="E84" s="9" t="inlineStr"/>
       <c r="F84" s="9" t="inlineStr">
         <is>
+          <t>ППК25381</t>
+        </is>
+      </c>
+      <c r="G84" s="9" t="inlineStr">
+        <is>
+          <t>12.12.2025</t>
+        </is>
+      </c>
+      <c r="H84" s="10" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy — Center for Natural Products</t>
+        </is>
+      </c>
+      <c r="I84" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="9" t="inlineStr"/>
+      <c r="B85" s="10" t="inlineStr"/>
+      <c r="C85" s="9" t="inlineStr"/>
+      <c r="D85" s="9" t="inlineStr">
+        <is>
+          <t>15.70</t>
+        </is>
+      </c>
+      <c r="E85" s="9" t="inlineStr"/>
+      <c r="F85" s="9" t="inlineStr">
+        <is>
           <t>197-12-K-26</t>
         </is>
       </c>
-      <c r="G84" s="9" t="inlineStr">
+      <c r="G85" s="9" t="inlineStr">
         <is>
           <t>07.08.2026</t>
         </is>
       </c>
-      <c r="H84" s="10" t="inlineStr">
+      <c r="H85" s="10" t="inlineStr">
         <is>
           <t>Farmahem</t>
         </is>
       </c>
-      <c r="I84" s="11" t="inlineStr">
+      <c r="I85" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="9" t="n">
-        <v>39</v>
-      </c>
-      <c r="B85" s="12" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="B86" s="12" t="inlineStr">
         <is>
           <t>GP092501</t>
         </is>
       </c>
-      <c r="C85" s="9" t="inlineStr">
+      <c r="C86" s="9" t="inlineStr">
         <is>
           <t>P060092</t>
         </is>
       </c>
-      <c r="D85" s="9" t="inlineStr">
+      <c r="D86" s="9" t="inlineStr">
         <is>
           <t>25.73</t>
         </is>
       </c>
-      <c r="E85" s="9" t="inlineStr">
+      <c r="E86" s="9" t="inlineStr">
         <is>
           <t>22.00–26.00%</t>
         </is>
       </c>
-      <c r="F85" s="9" t="inlineStr">
+      <c r="F86" s="9" t="inlineStr">
         <is>
           <t>QCCoA 001v02</t>
         </is>
       </c>
-      <c r="G85" s="9" t="inlineStr">
+      <c r="G86" s="9" t="inlineStr">
         <is>
           <t>20.02.2026</t>
         </is>
       </c>
-      <c r="H85" s="10" t="inlineStr">
+      <c r="H86" s="10" t="inlineStr">
         <is>
           <t>Purely Plant (in-house)</t>
         </is>
       </c>
-      <c r="I85" s="11" t="inlineStr">
+      <c r="I86" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="9" t="inlineStr"/>
-      <c r="B86" s="10" t="inlineStr"/>
-      <c r="C86" s="9" t="inlineStr"/>
-      <c r="D86" s="9" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="9" t="inlineStr"/>
+      <c r="B87" s="10" t="inlineStr"/>
+      <c r="C87" s="9" t="inlineStr"/>
+      <c r="D87" s="9" t="inlineStr">
         <is>
           <t>25.73</t>
         </is>
       </c>
-      <c r="E86" s="9" t="inlineStr"/>
-      <c r="F86" s="9" t="inlineStr">
+      <c r="E87" s="9" t="inlineStr"/>
+      <c r="F87" s="9" t="inlineStr">
         <is>
           <t>ППК26009</t>
         </is>
       </c>
-      <c r="G86" s="9" t="inlineStr">
+      <c r="G87" s="9" t="inlineStr">
         <is>
           <t>21.01.2026</t>
         </is>
       </c>
-      <c r="H86" s="10" t="inlineStr">
+      <c r="H87" s="10" t="inlineStr">
         <is>
           <t>UKIM Faculty of Pharmacy — Center for Natural Products</t>
         </is>
       </c>
-      <c r="I86" s="11" t="inlineStr">
+      <c r="I87" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="6" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr">
         <is>
           <t>GrapePie      3 batch(es)</t>
         </is>
       </c>
-      <c r="B87" s="7" t="inlineStr"/>
-      <c r="C87" s="7" t="inlineStr"/>
-      <c r="D87" s="7" t="inlineStr"/>
-      <c r="E87" s="7" t="inlineStr"/>
-      <c r="F87" s="7" t="inlineStr"/>
-      <c r="G87" s="7" t="inlineStr"/>
-      <c r="H87" s="7" t="inlineStr"/>
-      <c r="I87" s="7" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="9" t="n">
-        <v>40</v>
-      </c>
-      <c r="B88" s="12" t="inlineStr">
-        <is>
-          <t>P160012</t>
-        </is>
-      </c>
-      <c r="C88" s="9" t="inlineStr">
-        <is>
-          <t>P160012</t>
-        </is>
-      </c>
-      <c r="D88" s="9" t="inlineStr">
-        <is>
-          <t>26.32</t>
-        </is>
-      </c>
-      <c r="E88" s="9" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="F88" s="9" t="inlineStr">
-        <is>
-          <t>ППК26117</t>
-        </is>
-      </c>
-      <c r="G88" s="9" t="inlineStr">
-        <is>
-          <t>06.07.2026</t>
-        </is>
-      </c>
-      <c r="H88" s="10" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy — Center for Natural Products</t>
-        </is>
-      </c>
-      <c r="I88" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B88" s="7" t="inlineStr"/>
+      <c r="C88" s="7" t="inlineStr"/>
+      <c r="D88" s="7" t="inlineStr"/>
+      <c r="E88" s="7" t="inlineStr"/>
+      <c r="F88" s="7" t="inlineStr"/>
+      <c r="G88" s="7" t="inlineStr"/>
+      <c r="H88" s="7" t="inlineStr"/>
+      <c r="I88" s="7" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="9" t="n">
@@ -45703,17 +45723,17 @@
       </c>
       <c r="B89" s="12" t="inlineStr">
         <is>
-          <t>P160022</t>
+          <t>P160012</t>
         </is>
       </c>
       <c r="C89" s="9" t="inlineStr">
         <is>
-          <t>P160022</t>
+          <t>P160012</t>
         </is>
       </c>
       <c r="D89" s="9" t="inlineStr">
         <is>
-          <t>25.72</t>
+          <t>26.32</t>
         </is>
       </c>
       <c r="E89" s="9" t="inlineStr">
@@ -45723,7 +45743,7 @@
       </c>
       <c r="F89" s="9" t="inlineStr">
         <is>
-          <t>ППК26118</t>
+          <t>ППК26117</t>
         </is>
       </c>
       <c r="G89" s="9" t="inlineStr">
@@ -45748,260 +45768,274 @@
       </c>
       <c r="B90" s="12" t="inlineStr">
         <is>
+          <t>P160022</t>
+        </is>
+      </c>
+      <c r="C90" s="9" t="inlineStr">
+        <is>
+          <t>P160022</t>
+        </is>
+      </c>
+      <c r="D90" s="9" t="inlineStr">
+        <is>
+          <t>25.72</t>
+        </is>
+      </c>
+      <c r="E90" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F90" s="9" t="inlineStr">
+        <is>
+          <t>ППК26118</t>
+        </is>
+      </c>
+      <c r="G90" s="9" t="inlineStr">
+        <is>
+          <t>06.07.2026</t>
+        </is>
+      </c>
+      <c r="H90" s="10" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy — Center for Natural Products</t>
+        </is>
+      </c>
+      <c r="I90" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="9" t="n">
+        <v>43</v>
+      </c>
+      <c r="B91" s="12" t="inlineStr">
+        <is>
           <t>P160032</t>
         </is>
       </c>
-      <c r="C90" s="9" t="inlineStr">
+      <c r="C91" s="9" t="inlineStr">
         <is>
           <t>P160032</t>
         </is>
       </c>
-      <c r="D90" s="9" t="inlineStr">
+      <c r="D91" s="9" t="inlineStr">
         <is>
           <t>24.78</t>
         </is>
       </c>
-      <c r="E90" s="9" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="F90" s="9" t="inlineStr">
+      <c r="E91" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F91" s="9" t="inlineStr">
         <is>
           <t>ППК26119</t>
         </is>
       </c>
-      <c r="G90" s="9" t="inlineStr">
+      <c r="G91" s="9" t="inlineStr">
         <is>
           <t>06.07.2026</t>
         </is>
       </c>
-      <c r="H90" s="10" t="inlineStr">
+      <c r="H91" s="10" t="inlineStr">
         <is>
           <t>UKIM Faculty of Pharmacy — Center for Natural Products</t>
         </is>
       </c>
-      <c r="I90" s="11" t="inlineStr">
+      <c r="I91" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="6" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="6" t="inlineStr">
         <is>
           <t>Graps &amp; Creme      1 batch(es)</t>
         </is>
       </c>
-      <c r="B91" s="7" t="inlineStr"/>
-      <c r="C91" s="7" t="inlineStr"/>
-      <c r="D91" s="7" t="inlineStr"/>
-      <c r="E91" s="7" t="inlineStr"/>
-      <c r="F91" s="7" t="inlineStr"/>
-      <c r="G91" s="7" t="inlineStr"/>
-      <c r="H91" s="7" t="inlineStr"/>
-      <c r="I91" s="7" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="9" t="n">
-        <v>43</v>
-      </c>
-      <c r="B92" s="12" t="inlineStr">
+      <c r="B92" s="7" t="inlineStr"/>
+      <c r="C92" s="7" t="inlineStr"/>
+      <c r="D92" s="7" t="inlineStr"/>
+      <c r="E92" s="7" t="inlineStr"/>
+      <c r="F92" s="7" t="inlineStr"/>
+      <c r="G92" s="7" t="inlineStr"/>
+      <c r="H92" s="7" t="inlineStr"/>
+      <c r="I92" s="7" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="9" t="n">
+        <v>44</v>
+      </c>
+      <c r="B93" s="12" t="inlineStr">
         <is>
           <t>GRC102501_2</t>
         </is>
       </c>
-      <c r="C92" s="9" t="inlineStr">
+      <c r="C93" s="9" t="inlineStr">
         <is>
           <t>P060182</t>
         </is>
       </c>
-      <c r="D92" s="9" t="inlineStr">
+      <c r="D93" s="9" t="inlineStr">
         <is>
           <t>11.53</t>
         </is>
       </c>
-      <c r="E92" s="9" t="inlineStr">
+      <c r="E93" s="9" t="inlineStr">
         <is>
           <t>10.53–15.50%</t>
         </is>
       </c>
-      <c r="F92" s="9" t="inlineStr">
+      <c r="F93" s="9" t="inlineStr">
         <is>
           <t>051-6-K-26</t>
         </is>
       </c>
-      <c r="G92" s="9" t="inlineStr">
+      <c r="G93" s="9" t="inlineStr">
         <is>
           <t>04.03.2026</t>
         </is>
       </c>
-      <c r="H92" s="10" t="inlineStr">
+      <c r="H93" s="10" t="inlineStr">
         <is>
           <t>Farmahem</t>
         </is>
       </c>
-      <c r="I92" s="11" t="inlineStr">
+      <c r="I93" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="6" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
         <is>
           <t>High Pro Amnesia      3 batch(es)</t>
         </is>
       </c>
-      <c r="B93" s="7" t="inlineStr"/>
-      <c r="C93" s="7" t="inlineStr"/>
-      <c r="D93" s="7" t="inlineStr"/>
-      <c r="E93" s="7" t="inlineStr"/>
-      <c r="F93" s="7" t="inlineStr"/>
-      <c r="G93" s="7" t="inlineStr"/>
-      <c r="H93" s="7" t="inlineStr"/>
-      <c r="I93" s="7" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="9" t="n">
-        <v>44</v>
-      </c>
-      <c r="B94" s="12" t="inlineStr">
+      <c r="B94" s="7" t="inlineStr"/>
+      <c r="C94" s="7" t="inlineStr"/>
+      <c r="D94" s="7" t="inlineStr"/>
+      <c r="E94" s="7" t="inlineStr"/>
+      <c r="F94" s="7" t="inlineStr"/>
+      <c r="G94" s="7" t="inlineStr"/>
+      <c r="H94" s="7" t="inlineStr"/>
+      <c r="I94" s="7" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="B95" s="12" t="inlineStr">
         <is>
           <t>HPA1024</t>
         </is>
       </c>
-      <c r="C94" s="9" t="inlineStr"/>
-      <c r="D94" s="9" t="inlineStr">
-        <is>
-          <t>14.97</t>
-        </is>
-      </c>
-      <c r="E94" s="9" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="F94" s="9" t="inlineStr">
-        <is>
-          <t>NO-DOC-CODE (Report of Analysis)</t>
-        </is>
-      </c>
-      <c r="G94" s="9" t="inlineStr">
-        <is>
-          <t>23.04.2025</t>
-        </is>
-      </c>
-      <c r="H94" s="10" t="inlineStr">
-        <is>
-          <t>Purely Plant (in-house)</t>
-        </is>
-      </c>
-      <c r="I94" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="9" t="inlineStr"/>
-      <c r="B95" s="10" t="inlineStr"/>
       <c r="C95" s="9" t="inlineStr"/>
       <c r="D95" s="9" t="inlineStr">
         <is>
+          <t>14.97</t>
+        </is>
+      </c>
+      <c r="E95" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F95" s="9" t="inlineStr">
+        <is>
+          <t>NO-DOC-CODE (Report of Analysis)</t>
+        </is>
+      </c>
+      <c r="G95" s="9" t="inlineStr">
+        <is>
+          <t>23.04.2025</t>
+        </is>
+      </c>
+      <c r="H95" s="10" t="inlineStr">
+        <is>
+          <t>Purely Plant (in-house)</t>
+        </is>
+      </c>
+      <c r="I95" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="9" t="inlineStr"/>
+      <c r="B96" s="10" t="inlineStr"/>
+      <c r="C96" s="9" t="inlineStr"/>
+      <c r="D96" s="9" t="inlineStr">
+        <is>
           <t>17.31</t>
         </is>
       </c>
-      <c r="E95" s="9" t="inlineStr"/>
-      <c r="F95" s="9" t="inlineStr">
+      <c r="E96" s="9" t="inlineStr"/>
+      <c r="F96" s="9" t="inlineStr">
         <is>
           <t>197-13-K-26</t>
         </is>
       </c>
-      <c r="G95" s="9" t="inlineStr">
+      <c r="G96" s="9" t="inlineStr">
         <is>
           <t>07.08.2026</t>
         </is>
       </c>
-      <c r="H95" s="10" t="inlineStr">
+      <c r="H96" s="10" t="inlineStr">
         <is>
           <t>Farmahem</t>
         </is>
       </c>
-      <c r="I95" s="11" t="inlineStr">
+      <c r="I96" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="9" t="n">
-        <v>45</v>
-      </c>
-      <c r="B96" s="12" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="9" t="n">
+        <v>46</v>
+      </c>
+      <c r="B97" s="12" t="inlineStr">
         <is>
           <t>HPA1024_01</t>
         </is>
       </c>
-      <c r="C96" s="9" t="inlineStr">
+      <c r="C97" s="9" t="inlineStr">
         <is>
           <t>P050052</t>
         </is>
       </c>
-      <c r="D96" s="9" t="inlineStr">
+      <c r="D97" s="9" t="inlineStr">
         <is>
           <t>22.43</t>
         </is>
       </c>
-      <c r="E96" s="9" t="inlineStr">
+      <c r="E97" s="9" t="inlineStr">
         <is>
           <t>19.39–24.75%</t>
         </is>
       </c>
-      <c r="F96" s="9" t="inlineStr">
+      <c r="F97" s="9" t="inlineStr">
         <is>
           <t>QCCoA 001</t>
         </is>
       </c>
-      <c r="G96" s="9" t="inlineStr">
+      <c r="G97" s="9" t="inlineStr">
         <is>
           <t>17.07.2025</t>
         </is>
       </c>
-      <c r="H96" s="10" t="inlineStr">
+      <c r="H97" s="10" t="inlineStr">
         <is>
           <t>Purely Plant (in-house)</t>
-        </is>
-      </c>
-      <c r="I96" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="9" t="inlineStr"/>
-      <c r="B97" s="10" t="inlineStr"/>
-      <c r="C97" s="9" t="inlineStr"/>
-      <c r="D97" s="9" t="inlineStr">
-        <is>
-          <t>21.61</t>
-        </is>
-      </c>
-      <c r="E97" s="9" t="inlineStr"/>
-      <c r="F97" s="9" t="inlineStr">
-        <is>
-          <t>197-14-K-26</t>
-        </is>
-      </c>
-      <c r="G97" s="9" t="inlineStr">
-        <is>
-          <t>07.08.2026</t>
-        </is>
-      </c>
-      <c r="H97" s="10" t="inlineStr">
-        <is>
-          <t>Farmahem</t>
         </is>
       </c>
       <c r="I97" s="11" t="inlineStr">
@@ -46016,190 +46050,190 @@
       <c r="C98" s="9" t="inlineStr"/>
       <c r="D98" s="9" t="inlineStr">
         <is>
-          <t>22.43</t>
+          <t>21.61</t>
         </is>
       </c>
       <c r="E98" s="9" t="inlineStr"/>
       <c r="F98" s="9" t="inlineStr">
         <is>
+          <t>197-14-K-26</t>
+        </is>
+      </c>
+      <c r="G98" s="9" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="H98" s="10" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I98" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="9" t="inlineStr"/>
+      <c r="B99" s="10" t="inlineStr"/>
+      <c r="C99" s="9" t="inlineStr"/>
+      <c r="D99" s="9" t="inlineStr">
+        <is>
+          <t>22.43</t>
+        </is>
+      </c>
+      <c r="E99" s="9" t="inlineStr"/>
+      <c r="F99" s="9" t="inlineStr">
+        <is>
           <t>ППК25155</t>
         </is>
       </c>
-      <c r="G98" s="9" t="inlineStr">
+      <c r="G99" s="9" t="inlineStr">
         <is>
           <t>24.06.2025</t>
         </is>
       </c>
-      <c r="H98" s="10" t="inlineStr">
+      <c r="H99" s="10" t="inlineStr">
         <is>
           <t>UKIM Faculty of Pharmacy — Center for Natural Products</t>
         </is>
       </c>
-      <c r="I98" s="11" t="inlineStr">
+      <c r="I99" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="9" t="n">
-        <v>46</v>
-      </c>
-      <c r="B99" s="12" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="9" t="n">
+        <v>47</v>
+      </c>
+      <c r="B100" s="12" t="inlineStr">
         <is>
           <t>HPA052501</t>
         </is>
       </c>
-      <c r="C99" s="9" t="inlineStr">
+      <c r="C100" s="9" t="inlineStr">
         <is>
           <t>P050182</t>
         </is>
       </c>
-      <c r="D99" s="9" t="inlineStr">
+      <c r="D100" s="9" t="inlineStr">
         <is>
           <t>20.39</t>
         </is>
       </c>
-      <c r="E99" s="9" t="inlineStr">
+      <c r="E100" s="9" t="inlineStr">
         <is>
           <t>19.39–24.75%</t>
         </is>
       </c>
-      <c r="F99" s="9" t="inlineStr">
+      <c r="F100" s="9" t="inlineStr">
         <is>
           <t>ППК25278</t>
         </is>
       </c>
-      <c r="G99" s="9" t="inlineStr">
+      <c r="G100" s="9" t="inlineStr">
         <is>
           <t>19.09.2025</t>
         </is>
       </c>
-      <c r="H99" s="10" t="inlineStr">
+      <c r="H100" s="10" t="inlineStr">
         <is>
           <t>UKIM Faculty of Pharmacy — Center for Natural Products</t>
         </is>
       </c>
-      <c r="I99" s="11" t="inlineStr">
+      <c r="I100" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="9" t="inlineStr"/>
-      <c r="B100" s="10" t="inlineStr"/>
-      <c r="C100" s="9" t="inlineStr"/>
-      <c r="D100" s="9" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="9" t="inlineStr"/>
+      <c r="B101" s="10" t="inlineStr"/>
+      <c r="C101" s="9" t="inlineStr"/>
+      <c r="D101" s="9" t="inlineStr">
         <is>
           <t>20.39</t>
         </is>
       </c>
-      <c r="E100" s="9" t="inlineStr"/>
-      <c r="F100" s="9" t="inlineStr">
+      <c r="E101" s="9" t="inlineStr"/>
+      <c r="F101" s="9" t="inlineStr">
         <is>
           <t>QCCoA 001</t>
         </is>
       </c>
-      <c r="G100" s="9" t="inlineStr">
+      <c r="G101" s="9" t="inlineStr">
         <is>
           <t>22.09.2025</t>
         </is>
       </c>
-      <c r="H100" s="10" t="inlineStr">
+      <c r="H101" s="10" t="inlineStr">
         <is>
           <t>Purely Plant (in-house)</t>
         </is>
       </c>
-      <c r="I100" s="11" t="inlineStr">
+      <c r="I101" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="6" t="inlineStr">
-        <is>
-          <t>Jelly Donutz      2 batch(es)</t>
-        </is>
-      </c>
-      <c r="B101" s="7" t="inlineStr"/>
-      <c r="C101" s="7" t="inlineStr"/>
-      <c r="D101" s="7" t="inlineStr"/>
-      <c r="E101" s="7" t="inlineStr"/>
-      <c r="F101" s="7" t="inlineStr"/>
-      <c r="G101" s="7" t="inlineStr"/>
-      <c r="H101" s="7" t="inlineStr"/>
-      <c r="I101" s="7" t="inlineStr"/>
-    </row>
     <row r="102">
-      <c r="A102" s="9" t="n">
-        <v>47</v>
-      </c>
-      <c r="B102" s="12" t="inlineStr">
-        <is>
-          <t>JD112501</t>
-        </is>
-      </c>
-      <c r="C102" s="9" t="inlineStr">
-        <is>
-          <t>P060212</t>
-        </is>
-      </c>
-      <c r="D102" s="9" t="inlineStr">
-        <is>
-          <t>19.64</t>
-        </is>
-      </c>
-      <c r="E102" s="9" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="F102" s="9" t="inlineStr">
-        <is>
-          <t>ППК26063</t>
-        </is>
-      </c>
-      <c r="G102" s="9" t="inlineStr">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>Jelly Donutz      4 batch(es)</t>
+        </is>
+      </c>
+      <c r="B102" s="7" t="inlineStr"/>
+      <c r="C102" s="7" t="inlineStr"/>
+      <c r="D102" s="7" t="inlineStr"/>
+      <c r="E102" s="7" t="inlineStr"/>
+      <c r="F102" s="7" t="inlineStr"/>
+      <c r="G102" s="7" t="inlineStr"/>
+      <c r="H102" s="7" t="inlineStr"/>
+      <c r="I102" s="7" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="9" t="n">
+        <v>48</v>
+      </c>
+      <c r="B103" s="12" t="inlineStr">
+        <is>
+          <t>JD012601*</t>
+        </is>
+      </c>
+      <c r="C103" s="9" t="inlineStr">
+        <is>
+          <t>P060312</t>
+        </is>
+      </c>
+      <c r="D103" s="9" t="inlineStr">
+        <is>
+          <t>18.16</t>
+        </is>
+      </c>
+      <c r="E103" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F103" s="9" t="inlineStr">
+        <is>
+          <t>ППК26064</t>
+        </is>
+      </c>
+      <c r="G103" s="9" t="inlineStr">
         <is>
           <t>11.05.2026</t>
         </is>
       </c>
-      <c r="H102" s="10" t="inlineStr">
+      <c r="H103" s="10" t="inlineStr">
         <is>
           <t>UKIM Faculty of Pharmacy — Center for Natural Products</t>
-        </is>
-      </c>
-      <c r="I102" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="9" t="inlineStr"/>
-      <c r="B103" s="10" t="inlineStr"/>
-      <c r="C103" s="9" t="inlineStr"/>
-      <c r="D103" s="9" t="inlineStr">
-        <is>
-          <t>20.32</t>
-        </is>
-      </c>
-      <c r="E103" s="9" t="inlineStr"/>
-      <c r="F103" s="9" t="inlineStr">
-        <is>
-          <t>197-15-K-26</t>
-        </is>
-      </c>
-      <c r="G103" s="9" t="inlineStr">
-        <is>
-          <t>07.08.2026</t>
-        </is>
-      </c>
-      <c r="H103" s="10" t="inlineStr">
-        <is>
-          <t>Farmahem</t>
         </is>
       </c>
       <c r="I103" s="11" t="inlineStr">
@@ -46210,17 +46244,21 @@
     </row>
     <row r="104">
       <c r="A104" s="9" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B104" s="12" t="inlineStr">
         <is>
-          <t>JD022601</t>
-        </is>
-      </c>
-      <c r="C104" s="9" t="inlineStr"/>
+          <t>JD112501</t>
+        </is>
+      </c>
+      <c r="C104" s="9" t="inlineStr">
+        <is>
+          <t>P060212</t>
+        </is>
+      </c>
       <c r="D104" s="9" t="inlineStr">
         <is>
-          <t>18.58</t>
+          <t>19.64</t>
         </is>
       </c>
       <c r="E104" s="9" t="inlineStr">
@@ -46230,12 +46268,12 @@
       </c>
       <c r="F104" s="9" t="inlineStr">
         <is>
-          <t>ППК26115</t>
+          <t>ППК26063</t>
         </is>
       </c>
       <c r="G104" s="9" t="inlineStr">
         <is>
-          <t>30.06.2026</t>
+          <t>11.05.2026</t>
         </is>
       </c>
       <c r="H104" s="10" t="inlineStr">
@@ -46250,37 +46288,49 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="6" t="inlineStr">
-        <is>
-          <t>JellyDonutz      2 batch(es)</t>
-        </is>
-      </c>
-      <c r="B105" s="7" t="inlineStr"/>
-      <c r="C105" s="7" t="inlineStr"/>
-      <c r="D105" s="7" t="inlineStr"/>
-      <c r="E105" s="7" t="inlineStr"/>
-      <c r="F105" s="7" t="inlineStr"/>
-      <c r="G105" s="7" t="inlineStr"/>
-      <c r="H105" s="7" t="inlineStr"/>
-      <c r="I105" s="7" t="inlineStr"/>
+      <c r="A105" s="9" t="inlineStr"/>
+      <c r="B105" s="10" t="inlineStr"/>
+      <c r="C105" s="9" t="inlineStr"/>
+      <c r="D105" s="9" t="inlineStr">
+        <is>
+          <t>20.32</t>
+        </is>
+      </c>
+      <c r="E105" s="9" t="inlineStr"/>
+      <c r="F105" s="9" t="inlineStr">
+        <is>
+          <t>197-15-K-26</t>
+        </is>
+      </c>
+      <c r="G105" s="9" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="H105" s="10" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I105" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="9" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B106" s="12" t="inlineStr">
         <is>
-          <t>JD012603_02</t>
-        </is>
-      </c>
-      <c r="C106" s="9" t="inlineStr">
-        <is>
-          <t>P060412</t>
-        </is>
-      </c>
+          <t>JD112501*</t>
+        </is>
+      </c>
+      <c r="C106" s="9" t="inlineStr"/>
       <c r="D106" s="9" t="inlineStr">
         <is>
-          <t>20.54</t>
+          <t>13.93</t>
         </is>
       </c>
       <c r="E106" s="9" t="inlineStr">
@@ -46290,12 +46340,12 @@
       </c>
       <c r="F106" s="9" t="inlineStr">
         <is>
-          <t>ППК26113</t>
+          <t>ППК26065</t>
         </is>
       </c>
       <c r="G106" s="9" t="inlineStr">
         <is>
-          <t>30.06.2026</t>
+          <t>11.05.2026</t>
         </is>
       </c>
       <c r="H106" s="10" t="inlineStr">
@@ -46311,21 +46361,17 @@
     </row>
     <row r="107">
       <c r="A107" s="9" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B107" s="12" t="inlineStr">
         <is>
-          <t>JD012603_02V</t>
-        </is>
-      </c>
-      <c r="C107" s="9" t="inlineStr">
-        <is>
-          <t>P060422</t>
-        </is>
-      </c>
+          <t>JD022601</t>
+        </is>
+      </c>
+      <c r="C107" s="9" t="inlineStr"/>
       <c r="D107" s="9" t="inlineStr">
         <is>
-          <t>15.16</t>
+          <t>18.58</t>
         </is>
       </c>
       <c r="E107" s="9" t="inlineStr">
@@ -46335,7 +46381,7 @@
       </c>
       <c r="F107" s="9" t="inlineStr">
         <is>
-          <t>ППК26111</t>
+          <t>ППК26115</t>
         </is>
       </c>
       <c r="G107" s="9" t="inlineStr">
@@ -46357,7 +46403,7 @@
     <row r="108">
       <c r="A108" s="6" t="inlineStr">
         <is>
-          <t>Jokerz 31      4 batch(es)</t>
+          <t>JellyDonutz      2 batch(es)</t>
         </is>
       </c>
       <c r="B108" s="7" t="inlineStr"/>
@@ -46371,21 +46417,21 @@
     </row>
     <row r="109">
       <c r="A109" s="9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B109" s="12" t="inlineStr">
         <is>
-          <t>J31102501</t>
+          <t>JD012603_02</t>
         </is>
       </c>
       <c r="C109" s="9" t="inlineStr">
         <is>
-          <t>P060152</t>
+          <t>P060412</t>
         </is>
       </c>
       <c r="D109" s="9" t="inlineStr">
         <is>
-          <t>19.14</t>
+          <t>20.54</t>
         </is>
       </c>
       <c r="E109" s="9" t="inlineStr">
@@ -46395,17 +46441,17 @@
       </c>
       <c r="F109" s="9" t="inlineStr">
         <is>
-          <t>051-1-K-26</t>
+          <t>ППК26113</t>
         </is>
       </c>
       <c r="G109" s="9" t="inlineStr">
         <is>
-          <t>04.03.2026</t>
+          <t>30.06.2026</t>
         </is>
       </c>
       <c r="H109" s="10" t="inlineStr">
         <is>
-          <t>Farmahem</t>
+          <t>UKIM Faculty of Pharmacy — Center for Natural Products</t>
         </is>
       </c>
       <c r="I109" s="11" t="inlineStr">
@@ -46415,28 +46461,42 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="9" t="inlineStr"/>
-      <c r="B110" s="10" t="inlineStr"/>
-      <c r="C110" s="9" t="inlineStr"/>
+      <c r="A110" s="9" t="n">
+        <v>53</v>
+      </c>
+      <c r="B110" s="12" t="inlineStr">
+        <is>
+          <t>JD012603_02V</t>
+        </is>
+      </c>
+      <c r="C110" s="9" t="inlineStr">
+        <is>
+          <t>P060422</t>
+        </is>
+      </c>
       <c r="D110" s="9" t="inlineStr">
         <is>
-          <t>17.32</t>
-        </is>
-      </c>
-      <c r="E110" s="9" t="inlineStr"/>
+          <t>15.16</t>
+        </is>
+      </c>
+      <c r="E110" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="F110" s="9" t="inlineStr">
         <is>
-          <t>197-16-K-26</t>
+          <t>ППК26111</t>
         </is>
       </c>
       <c r="G110" s="9" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>30.06.2026</t>
         </is>
       </c>
       <c r="H110" s="10" t="inlineStr">
         <is>
-          <t>Farmahem</t>
+          <t>UKIM Faculty of Pharmacy — Center for Natural Products</t>
         </is>
       </c>
       <c r="I110" s="11" t="inlineStr">
@@ -46446,49 +46506,37 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="9" t="inlineStr"/>
-      <c r="B111" s="10" t="inlineStr"/>
-      <c r="C111" s="9" t="inlineStr"/>
-      <c r="D111" s="9" t="inlineStr">
-        <is>
-          <t>17.32</t>
-        </is>
-      </c>
-      <c r="E111" s="9" t="inlineStr"/>
-      <c r="F111" s="9" t="inlineStr">
-        <is>
-          <t>197-16-M-26</t>
-        </is>
-      </c>
-      <c r="G111" s="9" t="inlineStr">
-        <is>
-          <t>10.08.2026</t>
-        </is>
-      </c>
-      <c r="H111" s="10" t="inlineStr">
-        <is>
-          <t>Farmahem</t>
-        </is>
-      </c>
-      <c r="I111" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="A111" s="6" t="inlineStr">
+        <is>
+          <t>Jokerz 31      4 batch(es)</t>
+        </is>
+      </c>
+      <c r="B111" s="7" t="inlineStr"/>
+      <c r="C111" s="7" t="inlineStr"/>
+      <c r="D111" s="7" t="inlineStr"/>
+      <c r="E111" s="7" t="inlineStr"/>
+      <c r="F111" s="7" t="inlineStr"/>
+      <c r="G111" s="7" t="inlineStr"/>
+      <c r="H111" s="7" t="inlineStr"/>
+      <c r="I111" s="7" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="9" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B112" s="12" t="inlineStr">
         <is>
-          <t>J31112501</t>
-        </is>
-      </c>
-      <c r="C112" s="9" t="inlineStr"/>
+          <t>J31102501</t>
+        </is>
+      </c>
+      <c r="C112" s="9" t="inlineStr">
+        <is>
+          <t>P060152</t>
+        </is>
+      </c>
       <c r="D112" s="9" t="inlineStr">
         <is>
-          <t>20.21</t>
+          <t>19.14</t>
         </is>
       </c>
       <c r="E112" s="9" t="inlineStr">
@@ -46498,12 +46546,12 @@
       </c>
       <c r="F112" s="9" t="inlineStr">
         <is>
-          <t>100-1-K-26</t>
+          <t>051-1-K-26</t>
         </is>
       </c>
       <c r="G112" s="9" t="inlineStr">
         <is>
-          <t>09.04.2026</t>
+          <t>04.03.2026</t>
         </is>
       </c>
       <c r="H112" s="10" t="inlineStr">
@@ -46523,18 +46571,18 @@
       <c r="C113" s="9" t="inlineStr"/>
       <c r="D113" s="9" t="inlineStr">
         <is>
-          <t>25.27</t>
+          <t>17.32</t>
         </is>
       </c>
       <c r="E113" s="9" t="inlineStr"/>
       <c r="F113" s="9" t="inlineStr">
         <is>
-          <t>051-5-K-26</t>
+          <t>197-16-K-26</t>
         </is>
       </c>
       <c r="G113" s="9" t="inlineStr">
         <is>
-          <t>04.03.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="H113" s="10" t="inlineStr">
@@ -46549,37 +46597,23 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="9" t="n">
-        <v>53</v>
-      </c>
-      <c r="B114" s="12" t="inlineStr">
-        <is>
-          <t>J31122501 (hand-trimmed)</t>
-        </is>
-      </c>
-      <c r="C114" s="9" t="inlineStr">
-        <is>
-          <t>P060262</t>
-        </is>
-      </c>
+      <c r="A114" s="9" t="inlineStr"/>
+      <c r="B114" s="10" t="inlineStr"/>
+      <c r="C114" s="9" t="inlineStr"/>
       <c r="D114" s="9" t="inlineStr">
         <is>
-          <t>19.84</t>
-        </is>
-      </c>
-      <c r="E114" s="9" t="inlineStr">
-        <is>
-          <t>18.84–24.25%</t>
-        </is>
-      </c>
+          <t>17.32</t>
+        </is>
+      </c>
+      <c r="E114" s="9" t="inlineStr"/>
       <c r="F114" s="9" t="inlineStr">
         <is>
-          <t>100-2-K-26</t>
+          <t>197-16-M-26</t>
         </is>
       </c>
       <c r="G114" s="9" t="inlineStr">
         <is>
-          <t>09.04.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="H114" s="10" t="inlineStr">
@@ -46595,31 +46629,27 @@
     </row>
     <row r="115">
       <c r="A115" s="9" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B115" s="12" t="inlineStr">
         <is>
-          <t>J31122501 (machine-trimmed)</t>
-        </is>
-      </c>
-      <c r="C115" s="9" t="inlineStr">
-        <is>
-          <t>P060262</t>
-        </is>
-      </c>
+          <t>J31112501</t>
+        </is>
+      </c>
+      <c r="C115" s="9" t="inlineStr"/>
       <c r="D115" s="9" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>20.21</t>
         </is>
       </c>
       <c r="E115" s="9" t="inlineStr">
         <is>
-          <t>18.84–24.25%</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F115" s="9" t="inlineStr">
         <is>
-          <t>100-3-K-26</t>
+          <t>100-1-K-26</t>
         </is>
       </c>
       <c r="G115" s="9" t="inlineStr">
@@ -46639,280 +46669,314 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="6" t="inlineStr">
-        <is>
-          <t>Kush Crasher      1 batch(es)</t>
-        </is>
-      </c>
-      <c r="B116" s="7" t="inlineStr"/>
-      <c r="C116" s="7" t="inlineStr"/>
-      <c r="D116" s="7" t="inlineStr"/>
-      <c r="E116" s="7" t="inlineStr"/>
-      <c r="F116" s="7" t="inlineStr"/>
-      <c r="G116" s="7" t="inlineStr"/>
-      <c r="H116" s="7" t="inlineStr"/>
-      <c r="I116" s="7" t="inlineStr"/>
+      <c r="A116" s="9" t="inlineStr"/>
+      <c r="B116" s="10" t="inlineStr"/>
+      <c r="C116" s="9" t="inlineStr"/>
+      <c r="D116" s="9" t="inlineStr">
+        <is>
+          <t>25.27</t>
+        </is>
+      </c>
+      <c r="E116" s="9" t="inlineStr"/>
+      <c r="F116" s="9" t="inlineStr">
+        <is>
+          <t>051-5-K-26</t>
+        </is>
+      </c>
+      <c r="G116" s="9" t="inlineStr">
+        <is>
+          <t>04.03.2026</t>
+        </is>
+      </c>
+      <c r="H116" s="10" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I116" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="9" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B117" s="12" t="inlineStr">
         <is>
+          <t>J31122501 (hand-trimmed)</t>
+        </is>
+      </c>
+      <c r="C117" s="9" t="inlineStr">
+        <is>
+          <t>P060262</t>
+        </is>
+      </c>
+      <c r="D117" s="9" t="inlineStr">
+        <is>
+          <t>19.84</t>
+        </is>
+      </c>
+      <c r="E117" s="9" t="inlineStr">
+        <is>
+          <t>18.84–24.25%</t>
+        </is>
+      </c>
+      <c r="F117" s="9" t="inlineStr">
+        <is>
+          <t>100-2-K-26</t>
+        </is>
+      </c>
+      <c r="G117" s="9" t="inlineStr">
+        <is>
+          <t>09.04.2026</t>
+        </is>
+      </c>
+      <c r="H117" s="10" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I117" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="9" t="n">
+        <v>57</v>
+      </c>
+      <c r="B118" s="12" t="inlineStr">
+        <is>
+          <t>J31122501 (machine-trimmed)</t>
+        </is>
+      </c>
+      <c r="C118" s="9" t="inlineStr">
+        <is>
+          <t>P060262</t>
+        </is>
+      </c>
+      <c r="D118" s="9" t="inlineStr">
+        <is>
+          <t>21.84</t>
+        </is>
+      </c>
+      <c r="E118" s="9" t="inlineStr">
+        <is>
+          <t>18.84–24.25%</t>
+        </is>
+      </c>
+      <c r="F118" s="9" t="inlineStr">
+        <is>
+          <t>100-3-K-26</t>
+        </is>
+      </c>
+      <c r="G118" s="9" t="inlineStr">
+        <is>
+          <t>09.04.2026</t>
+        </is>
+      </c>
+      <c r="H118" s="10" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I118" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="6" t="inlineStr">
+        <is>
+          <t>Kush Crasher      1 batch(es)</t>
+        </is>
+      </c>
+      <c r="B119" s="7" t="inlineStr"/>
+      <c r="C119" s="7" t="inlineStr"/>
+      <c r="D119" s="7" t="inlineStr"/>
+      <c r="E119" s="7" t="inlineStr"/>
+      <c r="F119" s="7" t="inlineStr"/>
+      <c r="G119" s="7" t="inlineStr"/>
+      <c r="H119" s="7" t="inlineStr"/>
+      <c r="I119" s="7" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="9" t="n">
+        <v>58</v>
+      </c>
+      <c r="B120" s="12" t="inlineStr">
+        <is>
           <t>KC102501</t>
         </is>
       </c>
-      <c r="C117" s="9" t="inlineStr">
+      <c r="C120" s="9" t="inlineStr">
         <is>
           <t>P060172</t>
         </is>
       </c>
-      <c r="D117" s="9" t="inlineStr">
+      <c r="D120" s="9" t="inlineStr">
         <is>
           <t>17.04</t>
         </is>
       </c>
-      <c r="E117" s="9" t="inlineStr">
+      <c r="E120" s="9" t="inlineStr">
         <is>
           <t>16.04–20.75%</t>
         </is>
       </c>
-      <c r="F117" s="9" t="inlineStr">
+      <c r="F120" s="9" t="inlineStr">
         <is>
           <t>051-4-K-26</t>
         </is>
       </c>
-      <c r="G117" s="9" t="inlineStr">
+      <c r="G120" s="9" t="inlineStr">
         <is>
           <t>04.03.2026</t>
         </is>
       </c>
-      <c r="H117" s="10" t="inlineStr">
+      <c r="H120" s="10" t="inlineStr">
         <is>
           <t>Farmahem</t>
         </is>
       </c>
-      <c r="I117" s="11" t="inlineStr">
+      <c r="I120" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="6" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="6" t="inlineStr">
         <is>
           <t>Motor Breath      2 batch(es)</t>
         </is>
       </c>
-      <c r="B118" s="7" t="inlineStr"/>
-      <c r="C118" s="7" t="inlineStr"/>
-      <c r="D118" s="7" t="inlineStr"/>
-      <c r="E118" s="7" t="inlineStr"/>
-      <c r="F118" s="7" t="inlineStr"/>
-      <c r="G118" s="7" t="inlineStr"/>
-      <c r="H118" s="7" t="inlineStr"/>
-      <c r="I118" s="7" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="9" t="n">
-        <v>56</v>
-      </c>
-      <c r="B119" s="12" t="inlineStr">
+      <c r="B121" s="7" t="inlineStr"/>
+      <c r="C121" s="7" t="inlineStr"/>
+      <c r="D121" s="7" t="inlineStr"/>
+      <c r="E121" s="7" t="inlineStr"/>
+      <c r="F121" s="7" t="inlineStr"/>
+      <c r="G121" s="7" t="inlineStr"/>
+      <c r="H121" s="7" t="inlineStr"/>
+      <c r="I121" s="7" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="9" t="n">
+        <v>59</v>
+      </c>
+      <c r="B122" s="12" t="inlineStr">
         <is>
           <t>MB0824_04</t>
         </is>
       </c>
-      <c r="C119" s="9" t="inlineStr">
+      <c r="C122" s="9" t="inlineStr">
         <is>
           <t>P050032</t>
         </is>
       </c>
-      <c r="D119" s="9" t="inlineStr">
+      <c r="D122" s="9" t="inlineStr">
         <is>
           <t>18.67</t>
         </is>
       </c>
-      <c r="E119" s="9" t="inlineStr">
+      <c r="E122" s="9" t="inlineStr">
         <is>
           <t>15.82–20.75%</t>
         </is>
       </c>
-      <c r="F119" s="9" t="inlineStr">
+      <c r="F122" s="9" t="inlineStr">
         <is>
           <t>ППК25118</t>
         </is>
       </c>
-      <c r="G119" s="9" t="inlineStr">
+      <c r="G122" s="9" t="inlineStr">
         <is>
           <t>06.05.2025</t>
         </is>
       </c>
-      <c r="H119" s="10" t="inlineStr">
+      <c r="H122" s="10" t="inlineStr">
         <is>
           <t>UKIM Faculty of Pharmacy — Center for Natural Products</t>
         </is>
       </c>
-      <c r="I119" s="11" t="inlineStr">
+      <c r="I122" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="9" t="inlineStr"/>
-      <c r="B120" s="10" t="inlineStr"/>
-      <c r="C120" s="9" t="inlineStr"/>
-      <c r="D120" s="9" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="9" t="inlineStr"/>
+      <c r="B123" s="10" t="inlineStr"/>
+      <c r="C123" s="9" t="inlineStr"/>
+      <c r="D123" s="9" t="inlineStr">
         <is>
           <t>18.67</t>
         </is>
       </c>
-      <c r="E120" s="9" t="inlineStr"/>
-      <c r="F120" s="9" t="inlineStr">
+      <c r="E123" s="9" t="inlineStr"/>
+      <c r="F123" s="9" t="inlineStr">
         <is>
           <t>QCCoA 001</t>
         </is>
       </c>
-      <c r="G120" s="9" t="inlineStr">
+      <c r="G123" s="9" t="inlineStr">
         <is>
           <t>15.05.2025</t>
         </is>
       </c>
-      <c r="H120" s="10" t="inlineStr">
+      <c r="H123" s="10" t="inlineStr">
         <is>
           <t>Purely Plant (in-house)</t>
         </is>
       </c>
-      <c r="I120" s="11" t="inlineStr">
+      <c r="I123" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="9" t="n">
-        <v>57</v>
-      </c>
-      <c r="B121" s="12" t="inlineStr">
-        <is>
-          <t>MB0824_05</t>
-        </is>
-      </c>
-      <c r="C121" s="9" t="inlineStr">
-        <is>
-          <t>P050112</t>
-        </is>
-      </c>
-      <c r="D121" s="9" t="inlineStr">
-        <is>
-          <t>16.82</t>
-        </is>
-      </c>
-      <c r="E121" s="9" t="inlineStr">
-        <is>
-          <t>15.82–20.75%</t>
-        </is>
-      </c>
-      <c r="F121" s="9" t="inlineStr">
-        <is>
-          <t>QCCoA 001v02</t>
-        </is>
-      </c>
-      <c r="G121" s="9" t="inlineStr">
-        <is>
-          <t>21.01.2026</t>
-        </is>
-      </c>
-      <c r="H121" s="10" t="inlineStr">
-        <is>
-          <t>Purely Plant (in-house)</t>
-        </is>
-      </c>
-      <c r="I121" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="9" t="inlineStr"/>
-      <c r="B122" s="10" t="inlineStr"/>
-      <c r="C122" s="9" t="inlineStr"/>
-      <c r="D122" s="9" t="inlineStr">
-        <is>
-          <t>16.82</t>
-        </is>
-      </c>
-      <c r="E122" s="9" t="inlineStr"/>
-      <c r="F122" s="9" t="inlineStr">
-        <is>
-          <t>ППК25211</t>
-        </is>
-      </c>
-      <c r="G122" s="9" t="inlineStr">
-        <is>
-          <t>28.07.2025</t>
-        </is>
-      </c>
-      <c r="H122" s="10" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy — Center for Natural Products</t>
-        </is>
-      </c>
-      <c r="I122" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="6" t="inlineStr">
-        <is>
-          <t>Orange Punch Mimosa      8 batch(es)</t>
-        </is>
-      </c>
-      <c r="B123" s="7" t="inlineStr"/>
-      <c r="C123" s="7" t="inlineStr"/>
-      <c r="D123" s="7" t="inlineStr"/>
-      <c r="E123" s="7" t="inlineStr"/>
-      <c r="F123" s="7" t="inlineStr"/>
-      <c r="G123" s="7" t="inlineStr"/>
-      <c r="H123" s="7" t="inlineStr"/>
-      <c r="I123" s="7" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="9" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B124" s="12" t="inlineStr">
         <is>
-          <t>OPM1024</t>
-        </is>
-      </c>
-      <c r="C124" s="9" t="inlineStr"/>
+          <t>MB0824_05</t>
+        </is>
+      </c>
+      <c r="C124" s="9" t="inlineStr">
+        <is>
+          <t>P050112</t>
+        </is>
+      </c>
       <c r="D124" s="9" t="inlineStr">
         <is>
-          <t>20.03</t>
+          <t>16.82</t>
         </is>
       </c>
       <c r="E124" s="9" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>15.82–20.75%</t>
         </is>
       </c>
       <c r="F124" s="9" t="inlineStr">
         <is>
-          <t>197-17-K-26</t>
+          <t>QCCoA 001v02</t>
         </is>
       </c>
       <c r="G124" s="9" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>21.01.2026</t>
         </is>
       </c>
       <c r="H124" s="10" t="inlineStr">
         <is>
-          <t>Farmahem</t>
+          <t>Purely Plant (in-house)</t>
         </is>
       </c>
       <c r="I124" s="11" t="inlineStr">
@@ -46927,23 +46991,23 @@
       <c r="C125" s="9" t="inlineStr"/>
       <c r="D125" s="9" t="inlineStr">
         <is>
-          <t>19.96</t>
+          <t>16.82</t>
         </is>
       </c>
       <c r="E125" s="9" t="inlineStr"/>
       <c r="F125" s="9" t="inlineStr">
         <is>
-          <t>NO-DOC-CODE (Report of Analysis)</t>
+          <t>ППК25211</t>
         </is>
       </c>
       <c r="G125" s="9" t="inlineStr">
         <is>
-          <t>23.04.2025</t>
+          <t>28.07.2025</t>
         </is>
       </c>
       <c r="H125" s="10" t="inlineStr">
         <is>
-          <t>Purely Plant (in-house)</t>
+          <t>UKIM Faculty of Pharmacy — Center for Natural Products</t>
         </is>
       </c>
       <c r="I125" s="11" t="inlineStr">
@@ -46953,149 +47017,129 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="9" t="n">
-        <v>59</v>
-      </c>
-      <c r="B126" s="12" t="inlineStr">
-        <is>
-          <t>OMP1024_01</t>
-        </is>
-      </c>
-      <c r="C126" s="9" t="inlineStr">
-        <is>
-          <t>P050042</t>
-        </is>
-      </c>
-      <c r="D126" s="9" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
-      <c r="E126" s="9" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="F126" s="9" t="inlineStr">
-        <is>
-          <t>ППК25117</t>
-        </is>
-      </c>
-      <c r="G126" s="9" t="inlineStr">
-        <is>
-          <t>06.05.2025</t>
-        </is>
-      </c>
-      <c r="H126" s="10" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy — Center for Natural Products</t>
-        </is>
-      </c>
-      <c r="I126" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="A126" s="6" t="inlineStr">
+        <is>
+          <t>Orange Punch Mimosa      8 batch(es)</t>
+        </is>
+      </c>
+      <c r="B126" s="7" t="inlineStr"/>
+      <c r="C126" s="7" t="inlineStr"/>
+      <c r="D126" s="7" t="inlineStr"/>
+      <c r="E126" s="7" t="inlineStr"/>
+      <c r="F126" s="7" t="inlineStr"/>
+      <c r="G126" s="7" t="inlineStr"/>
+      <c r="H126" s="7" t="inlineStr"/>
+      <c r="I126" s="7" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" s="9" t="inlineStr"/>
-      <c r="B127" s="10" t="inlineStr"/>
+      <c r="A127" s="9" t="n">
+        <v>61</v>
+      </c>
+      <c r="B127" s="12" t="inlineStr">
+        <is>
+          <t>OPM1024</t>
+        </is>
+      </c>
       <c r="C127" s="9" t="inlineStr"/>
       <c r="D127" s="9" t="inlineStr">
         <is>
-          <t>15.38</t>
-        </is>
-      </c>
-      <c r="E127" s="9" t="inlineStr"/>
+          <t>20.03</t>
+        </is>
+      </c>
+      <c r="E127" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="F127" s="9" t="inlineStr">
         <is>
-          <t>QCCoA 001</t>
+          <t>197-17-K-26</t>
         </is>
       </c>
       <c r="G127" s="9" t="inlineStr">
         <is>
-          <t>15.05.2025</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="H127" s="10" t="inlineStr">
         <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I127" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="9" t="inlineStr"/>
+      <c r="B128" s="10" t="inlineStr"/>
+      <c r="C128" s="9" t="inlineStr"/>
+      <c r="D128" s="9" t="inlineStr">
+        <is>
+          <t>19.96</t>
+        </is>
+      </c>
+      <c r="E128" s="9" t="inlineStr"/>
+      <c r="F128" s="9" t="inlineStr">
+        <is>
+          <t>NO-DOC-CODE (Report of Analysis)</t>
+        </is>
+      </c>
+      <c r="G128" s="9" t="inlineStr">
+        <is>
+          <t>23.04.2025</t>
+        </is>
+      </c>
+      <c r="H128" s="10" t="inlineStr">
+        <is>
           <t>Purely Plant (in-house)</t>
         </is>
       </c>
-      <c r="I127" s="11" t="inlineStr">
+      <c r="I128" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="9" t="n">
-        <v>60</v>
-      </c>
-      <c r="B128" s="12" t="inlineStr">
-        <is>
-          <t>OPM1024_02</t>
-        </is>
-      </c>
-      <c r="C128" s="9" t="inlineStr">
-        <is>
-          <t>P050062</t>
-        </is>
-      </c>
-      <c r="D128" s="9" t="inlineStr">
-        <is>
-          <t>18.27</t>
-        </is>
-      </c>
-      <c r="E128" s="9" t="inlineStr">
-        <is>
-          <t>13.00–19.00%</t>
-        </is>
-      </c>
-      <c r="F128" s="9" t="inlineStr">
-        <is>
-          <t>QCCoA 001</t>
-        </is>
-      </c>
-      <c r="G128" s="9" t="inlineStr">
-        <is>
-          <t>17.07.2025</t>
-        </is>
-      </c>
-      <c r="H128" s="10" t="inlineStr">
-        <is>
-          <t>Purely Plant (in-house)</t>
-        </is>
-      </c>
-      <c r="I128" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
     <row r="129">
-      <c r="A129" s="9" t="inlineStr"/>
-      <c r="B129" s="10" t="inlineStr"/>
-      <c r="C129" s="9" t="inlineStr"/>
+      <c r="A129" s="9" t="n">
+        <v>62</v>
+      </c>
+      <c r="B129" s="12" t="inlineStr">
+        <is>
+          <t>OMP1024_01</t>
+        </is>
+      </c>
+      <c r="C129" s="9" t="inlineStr">
+        <is>
+          <t>P050042</t>
+        </is>
+      </c>
       <c r="D129" s="9" t="inlineStr">
         <is>
-          <t>18.04</t>
-        </is>
-      </c>
-      <c r="E129" s="9" t="inlineStr"/>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="E129" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="F129" s="9" t="inlineStr">
         <is>
-          <t>197-18-K-26</t>
+          <t>ППК25117</t>
         </is>
       </c>
       <c r="G129" s="9" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>06.05.2025</t>
         </is>
       </c>
       <c r="H129" s="10" t="inlineStr">
         <is>
-          <t>Farmahem</t>
+          <t>UKIM Faculty of Pharmacy — Center for Natural Products</t>
         </is>
       </c>
       <c r="I129" s="11" t="inlineStr">
@@ -47110,23 +47154,23 @@
       <c r="C130" s="9" t="inlineStr"/>
       <c r="D130" s="9" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>15.38</t>
         </is>
       </c>
       <c r="E130" s="9" t="inlineStr"/>
       <c r="F130" s="9" t="inlineStr">
         <is>
-          <t>ППК25154</t>
+          <t>QCCoA 001</t>
         </is>
       </c>
       <c r="G130" s="9" t="inlineStr">
         <is>
-          <t>24.06.2025</t>
+          <t>15.05.2025</t>
         </is>
       </c>
       <c r="H130" s="10" t="inlineStr">
         <is>
-          <t>UKIM Faculty of Pharmacy — Center for Natural Products</t>
+          <t>Purely Plant (in-house)</t>
         </is>
       </c>
       <c r="I130" s="11" t="inlineStr">
@@ -47137,21 +47181,21 @@
     </row>
     <row r="131">
       <c r="A131" s="9" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B131" s="12" t="inlineStr">
         <is>
-          <t>OPM1024_03</t>
+          <t>OPM1024_02</t>
         </is>
       </c>
       <c r="C131" s="9" t="inlineStr">
         <is>
-          <t>P050082</t>
+          <t>P050062</t>
         </is>
       </c>
       <c r="D131" s="9" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>18.27</t>
         </is>
       </c>
       <c r="E131" s="9" t="inlineStr">
@@ -47161,12 +47205,12 @@
       </c>
       <c r="F131" s="9" t="inlineStr">
         <is>
-          <t>QCCoA 001v02</t>
+          <t>QCCoA 001</t>
         </is>
       </c>
       <c r="G131" s="9" t="inlineStr">
         <is>
-          <t>21.01.2026</t>
+          <t>17.07.2025</t>
         </is>
       </c>
       <c r="H131" s="10" t="inlineStr">
@@ -47186,215 +47230,201 @@
       <c r="C132" s="9" t="inlineStr"/>
       <c r="D132" s="9" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>18.04</t>
         </is>
       </c>
       <c r="E132" s="9" t="inlineStr"/>
       <c r="F132" s="9" t="inlineStr">
         <is>
+          <t>197-18-K-26</t>
+        </is>
+      </c>
+      <c r="G132" s="9" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="H132" s="10" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I132" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="9" t="inlineStr"/>
+      <c r="B133" s="10" t="inlineStr"/>
+      <c r="C133" s="9" t="inlineStr"/>
+      <c r="D133" s="9" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="E133" s="9" t="inlineStr"/>
+      <c r="F133" s="9" t="inlineStr">
+        <is>
+          <t>ППК25154</t>
+        </is>
+      </c>
+      <c r="G133" s="9" t="inlineStr">
+        <is>
+          <t>24.06.2025</t>
+        </is>
+      </c>
+      <c r="H133" s="10" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy — Center for Natural Products</t>
+        </is>
+      </c>
+      <c r="I133" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="9" t="n">
+        <v>64</v>
+      </c>
+      <c r="B134" s="12" t="inlineStr">
+        <is>
+          <t>OPM1024_03</t>
+        </is>
+      </c>
+      <c r="C134" s="9" t="inlineStr">
+        <is>
+          <t>P050082</t>
+        </is>
+      </c>
+      <c r="D134" s="9" t="inlineStr">
+        <is>
+          <t>16.55</t>
+        </is>
+      </c>
+      <c r="E134" s="9" t="inlineStr">
+        <is>
+          <t>13.00–19.00%</t>
+        </is>
+      </c>
+      <c r="F134" s="9" t="inlineStr">
+        <is>
+          <t>QCCoA 001v02</t>
+        </is>
+      </c>
+      <c r="G134" s="9" t="inlineStr">
+        <is>
+          <t>21.01.2026</t>
+        </is>
+      </c>
+      <c r="H134" s="10" t="inlineStr">
+        <is>
+          <t>Purely Plant (in-house)</t>
+        </is>
+      </c>
+      <c r="I134" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="9" t="inlineStr"/>
+      <c r="B135" s="10" t="inlineStr"/>
+      <c r="C135" s="9" t="inlineStr"/>
+      <c r="D135" s="9" t="inlineStr">
+        <is>
+          <t>16.55</t>
+        </is>
+      </c>
+      <c r="E135" s="9" t="inlineStr"/>
+      <c r="F135" s="9" t="inlineStr">
+        <is>
           <t>ППК25210</t>
         </is>
       </c>
-      <c r="G132" s="9" t="inlineStr">
+      <c r="G135" s="9" t="inlineStr">
         <is>
           <t>28.07.2025</t>
         </is>
       </c>
-      <c r="H132" s="10" t="inlineStr">
+      <c r="H135" s="10" t="inlineStr">
         <is>
           <t>UKIM Faculty of Pharmacy — Center for Natural Products</t>
         </is>
       </c>
-      <c r="I132" s="11" t="inlineStr">
+      <c r="I135" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="9" t="n">
-        <v>62</v>
-      </c>
-      <c r="B133" s="12" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="9" t="n">
+        <v>65</v>
+      </c>
+      <c r="B136" s="12" t="inlineStr">
         <is>
           <t>OPM052501</t>
         </is>
       </c>
-      <c r="C133" s="9" t="inlineStr">
+      <c r="C136" s="9" t="inlineStr">
         <is>
           <t>P050132</t>
         </is>
       </c>
-      <c r="D133" s="9" t="inlineStr">
+      <c r="D136" s="9" t="inlineStr">
         <is>
           <t>14.16</t>
         </is>
       </c>
-      <c r="E133" s="9" t="inlineStr">
+      <c r="E136" s="9" t="inlineStr">
         <is>
           <t>13.00–19.00%</t>
         </is>
       </c>
-      <c r="F133" s="9" t="inlineStr">
+      <c r="F136" s="9" t="inlineStr">
         <is>
           <t>QCCoA 001v02</t>
         </is>
       </c>
-      <c r="G133" s="9" t="inlineStr">
+      <c r="G136" s="9" t="inlineStr">
         <is>
           <t>21.01.2026</t>
         </is>
       </c>
-      <c r="H133" s="10" t="inlineStr">
+      <c r="H136" s="10" t="inlineStr">
         <is>
           <t>Purely Plant (in-house)</t>
         </is>
       </c>
-      <c r="I133" s="11" t="inlineStr">
+      <c r="I136" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="9" t="inlineStr"/>
-      <c r="B134" s="10" t="inlineStr"/>
-      <c r="C134" s="9" t="inlineStr"/>
-      <c r="D134" s="9" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="9" t="inlineStr"/>
+      <c r="B137" s="10" t="inlineStr"/>
+      <c r="C137" s="9" t="inlineStr"/>
+      <c r="D137" s="9" t="inlineStr">
         <is>
           <t>14.16</t>
         </is>
       </c>
-      <c r="E134" s="9" t="inlineStr"/>
-      <c r="F134" s="9" t="inlineStr">
+      <c r="E137" s="9" t="inlineStr"/>
+      <c r="F137" s="9" t="inlineStr">
         <is>
           <t>ППК25257</t>
         </is>
       </c>
-      <c r="G134" s="9" t="inlineStr">
+      <c r="G137" s="9" t="inlineStr">
         <is>
           <t>05.09.2025</t>
-        </is>
-      </c>
-      <c r="H134" s="10" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy — Center for Natural Products</t>
-        </is>
-      </c>
-      <c r="I134" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="9" t="n">
-        <v>63</v>
-      </c>
-      <c r="B135" s="12" t="inlineStr">
-        <is>
-          <t>OPM092501</t>
-        </is>
-      </c>
-      <c r="C135" s="9" t="inlineStr">
-        <is>
-          <t>P060042</t>
-        </is>
-      </c>
-      <c r="D135" s="9" t="inlineStr">
-        <is>
-          <t>9.43</t>
-        </is>
-      </c>
-      <c r="E135" s="9" t="inlineStr">
-        <is>
-          <t>7.09–13.00%</t>
-        </is>
-      </c>
-      <c r="F135" s="9" t="inlineStr">
-        <is>
-          <t>QCCoA 001v02</t>
-        </is>
-      </c>
-      <c r="G135" s="9" t="inlineStr">
-        <is>
-          <t>20.02.2026</t>
-        </is>
-      </c>
-      <c r="H135" s="10" t="inlineStr">
-        <is>
-          <t>Purely Plant (in-house)</t>
-        </is>
-      </c>
-      <c r="I135" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="9" t="inlineStr"/>
-      <c r="B136" s="10" t="inlineStr"/>
-      <c r="C136" s="9" t="inlineStr"/>
-      <c r="D136" s="9" t="inlineStr">
-        <is>
-          <t>9.43</t>
-        </is>
-      </c>
-      <c r="E136" s="9" t="inlineStr"/>
-      <c r="F136" s="9" t="inlineStr">
-        <is>
-          <t>ППК26008</t>
-        </is>
-      </c>
-      <c r="G136" s="9" t="inlineStr">
-        <is>
-          <t>21.01.2026</t>
-        </is>
-      </c>
-      <c r="H136" s="10" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy — Center for Natural Products</t>
-        </is>
-      </c>
-      <c r="I136" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="9" t="n">
-        <v>64</v>
-      </c>
-      <c r="B137" s="12" t="inlineStr">
-        <is>
-          <t>OPM112501</t>
-        </is>
-      </c>
-      <c r="C137" s="9" t="inlineStr">
-        <is>
-          <t>P060222</t>
-        </is>
-      </c>
-      <c r="D137" s="9" t="inlineStr">
-        <is>
-          <t>8.00</t>
-        </is>
-      </c>
-      <c r="E137" s="9" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="F137" s="9" t="inlineStr">
-        <is>
-          <t>ППК26031</t>
-        </is>
-      </c>
-      <c r="G137" s="9" t="inlineStr">
-        <is>
-          <t>05.03.2026</t>
         </is>
       </c>
       <c r="H137" s="10" t="inlineStr">
@@ -47410,21 +47440,21 @@
     </row>
     <row r="138">
       <c r="A138" s="9" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B138" s="12" t="inlineStr">
         <is>
-          <t>OPM122501</t>
+          <t>OPM092501</t>
         </is>
       </c>
       <c r="C138" s="9" t="inlineStr">
         <is>
-          <t>P060242</t>
+          <t>P060042</t>
         </is>
       </c>
       <c r="D138" s="9" t="inlineStr">
         <is>
-          <t>8.09</t>
+          <t>9.43</t>
         </is>
       </c>
       <c r="E138" s="9" t="inlineStr">
@@ -47434,17 +47464,17 @@
       </c>
       <c r="F138" s="9" t="inlineStr">
         <is>
-          <t>100-4-K-26</t>
+          <t>QCCoA 001v02</t>
         </is>
       </c>
       <c r="G138" s="9" t="inlineStr">
         <is>
-          <t>09.04.2026</t>
+          <t>20.02.2026</t>
         </is>
       </c>
       <c r="H138" s="10" t="inlineStr">
         <is>
-          <t>Farmahem</t>
+          <t>Purely Plant (in-house)</t>
         </is>
       </c>
       <c r="I138" s="11" t="inlineStr">
@@ -47459,23 +47489,23 @@
       <c r="C139" s="9" t="inlineStr"/>
       <c r="D139" s="9" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>9.43</t>
         </is>
       </c>
       <c r="E139" s="9" t="inlineStr"/>
       <c r="F139" s="9" t="inlineStr">
         <is>
-          <t>197-19-K-26</t>
+          <t>ППК26008</t>
         </is>
       </c>
       <c r="G139" s="9" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>21.01.2026</t>
         </is>
       </c>
       <c r="H139" s="10" t="inlineStr">
         <is>
-          <t>Farmahem</t>
+          <t>UKIM Faculty of Pharmacy — Center for Natural Products</t>
         </is>
       </c>
       <c r="I139" s="11" t="inlineStr">
@@ -47485,57 +47515,87 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="6" t="inlineStr">
-        <is>
-          <t>Permanent Marker      2 batch(es)</t>
-        </is>
-      </c>
-      <c r="B140" s="7" t="inlineStr"/>
-      <c r="C140" s="7" t="inlineStr"/>
-      <c r="D140" s="7" t="inlineStr"/>
-      <c r="E140" s="7" t="inlineStr"/>
-      <c r="F140" s="7" t="inlineStr"/>
-      <c r="G140" s="7" t="inlineStr"/>
-      <c r="H140" s="7" t="inlineStr"/>
-      <c r="I140" s="7" t="inlineStr"/>
+      <c r="A140" s="9" t="n">
+        <v>67</v>
+      </c>
+      <c r="B140" s="12" t="inlineStr">
+        <is>
+          <t>OPM112501</t>
+        </is>
+      </c>
+      <c r="C140" s="9" t="inlineStr">
+        <is>
+          <t>P060222</t>
+        </is>
+      </c>
+      <c r="D140" s="9" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+      <c r="E140" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F140" s="9" t="inlineStr">
+        <is>
+          <t>ППК26031</t>
+        </is>
+      </c>
+      <c r="G140" s="9" t="inlineStr">
+        <is>
+          <t>05.03.2026</t>
+        </is>
+      </c>
+      <c r="H140" s="10" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy — Center for Natural Products</t>
+        </is>
+      </c>
+      <c r="I140" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="9" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B141" s="12" t="inlineStr">
         <is>
-          <t>PM072501</t>
+          <t>OPM122501</t>
         </is>
       </c>
       <c r="C141" s="9" t="inlineStr">
         <is>
-          <t>P050272</t>
+          <t>P060242</t>
         </is>
       </c>
       <c r="D141" s="9" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t>8.09</t>
         </is>
       </c>
       <c r="E141" s="9" t="inlineStr">
         <is>
-          <t>9.01–14.00%</t>
+          <t>7.09–13.00%</t>
         </is>
       </c>
       <c r="F141" s="9" t="inlineStr">
         <is>
-          <t>QCCoA 001v02</t>
+          <t>100-4-K-26</t>
         </is>
       </c>
       <c r="G141" s="9" t="inlineStr">
         <is>
-          <t>21.01.2026</t>
+          <t>09.04.2026</t>
         </is>
       </c>
       <c r="H141" s="10" t="inlineStr">
         <is>
-          <t>Purely Plant (in-house)</t>
+          <t>Farmahem</t>
         </is>
       </c>
       <c r="I141" s="11" t="inlineStr">
@@ -47550,286 +47610,276 @@
       <c r="C142" s="9" t="inlineStr"/>
       <c r="D142" s="9" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="E142" s="9" t="inlineStr"/>
       <c r="F142" s="9" t="inlineStr">
         <is>
+          <t>197-19-K-26</t>
+        </is>
+      </c>
+      <c r="G142" s="9" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="H142" s="10" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I142" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="6" t="inlineStr">
+        <is>
+          <t>Permanent Marker      2 batch(es)</t>
+        </is>
+      </c>
+      <c r="B143" s="7" t="inlineStr"/>
+      <c r="C143" s="7" t="inlineStr"/>
+      <c r="D143" s="7" t="inlineStr"/>
+      <c r="E143" s="7" t="inlineStr"/>
+      <c r="F143" s="7" t="inlineStr"/>
+      <c r="G143" s="7" t="inlineStr"/>
+      <c r="H143" s="7" t="inlineStr"/>
+      <c r="I143" s="7" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="9" t="n">
+        <v>69</v>
+      </c>
+      <c r="B144" s="12" t="inlineStr">
+        <is>
+          <t>PM072501</t>
+        </is>
+      </c>
+      <c r="C144" s="9" t="inlineStr">
+        <is>
+          <t>P050272</t>
+        </is>
+      </c>
+      <c r="D144" s="9" t="inlineStr">
+        <is>
+          <t>10.01</t>
+        </is>
+      </c>
+      <c r="E144" s="9" t="inlineStr">
+        <is>
+          <t>9.01–14.00%</t>
+        </is>
+      </c>
+      <c r="F144" s="9" t="inlineStr">
+        <is>
+          <t>QCCoA 001v02</t>
+        </is>
+      </c>
+      <c r="G144" s="9" t="inlineStr">
+        <is>
+          <t>21.01.2026</t>
+        </is>
+      </c>
+      <c r="H144" s="10" t="inlineStr">
+        <is>
+          <t>Purely Plant (in-house)</t>
+        </is>
+      </c>
+      <c r="I144" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="9" t="inlineStr"/>
+      <c r="B145" s="10" t="inlineStr"/>
+      <c r="C145" s="9" t="inlineStr"/>
+      <c r="D145" s="9" t="inlineStr">
+        <is>
+          <t>10.01</t>
+        </is>
+      </c>
+      <c r="E145" s="9" t="inlineStr"/>
+      <c r="F145" s="9" t="inlineStr">
+        <is>
           <t>ППК25368</t>
         </is>
       </c>
-      <c r="G142" s="9" t="inlineStr">
+      <c r="G145" s="9" t="inlineStr">
         <is>
           <t>28.11.2025</t>
         </is>
       </c>
-      <c r="H142" s="10" t="inlineStr">
+      <c r="H145" s="10" t="inlineStr">
         <is>
           <t>UKIM Faculty of Pharmacy — Center for Natural Products</t>
         </is>
       </c>
-      <c r="I142" s="11" t="inlineStr">
+      <c r="I145" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="9" t="n">
-        <v>67</v>
-      </c>
-      <c r="B143" s="12" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="9" t="n">
+        <v>70</v>
+      </c>
+      <c r="B146" s="12" t="inlineStr">
         <is>
           <t>PM112501</t>
         </is>
       </c>
-      <c r="C143" s="9" t="inlineStr">
+      <c r="C146" s="9" t="inlineStr">
         <is>
           <t>P060232</t>
         </is>
       </c>
-      <c r="D143" s="9" t="inlineStr">
+      <c r="D146" s="9" t="inlineStr">
         <is>
           <t>13.33</t>
         </is>
       </c>
-      <c r="E143" s="9" t="inlineStr">
+      <c r="E146" s="9" t="inlineStr">
         <is>
           <t>9.01–14.00%</t>
         </is>
       </c>
-      <c r="F143" s="9" t="inlineStr">
+      <c r="F146" s="9" t="inlineStr">
         <is>
           <t>ППК26030</t>
         </is>
       </c>
-      <c r="G143" s="9" t="inlineStr">
+      <c r="G146" s="9" t="inlineStr">
         <is>
           <t>05.03.2026</t>
         </is>
       </c>
-      <c r="H143" s="10" t="inlineStr">
+      <c r="H146" s="10" t="inlineStr">
         <is>
           <t>UKIM Faculty of Pharmacy — Center for Natural Products</t>
         </is>
       </c>
-      <c r="I143" s="11" t="inlineStr">
+      <c r="I146" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="6" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="6" t="inlineStr">
         <is>
           <t>Permanent Market      1 batch(es)</t>
         </is>
       </c>
-      <c r="B144" s="7" t="inlineStr"/>
-      <c r="C144" s="7" t="inlineStr"/>
-      <c r="D144" s="7" t="inlineStr"/>
-      <c r="E144" s="7" t="inlineStr"/>
-      <c r="F144" s="7" t="inlineStr"/>
-      <c r="G144" s="7" t="inlineStr"/>
-      <c r="H144" s="7" t="inlineStr"/>
-      <c r="I144" s="7" t="inlineStr"/>
-    </row>
-    <row r="145">
-      <c r="A145" s="9" t="n">
-        <v>68</v>
-      </c>
-      <c r="B145" s="12" t="inlineStr">
+      <c r="B147" s="7" t="inlineStr"/>
+      <c r="C147" s="7" t="inlineStr"/>
+      <c r="D147" s="7" t="inlineStr"/>
+      <c r="E147" s="7" t="inlineStr"/>
+      <c r="F147" s="7" t="inlineStr"/>
+      <c r="G147" s="7" t="inlineStr"/>
+      <c r="H147" s="7" t="inlineStr"/>
+      <c r="I147" s="7" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="9" t="n">
+        <v>71</v>
+      </c>
+      <c r="B148" s="12" t="inlineStr">
         <is>
           <t>PM092501</t>
         </is>
       </c>
-      <c r="C145" s="9" t="inlineStr">
+      <c r="C148" s="9" t="inlineStr">
         <is>
           <t>P060062</t>
         </is>
       </c>
-      <c r="D145" s="9" t="inlineStr">
+      <c r="D148" s="9" t="inlineStr">
         <is>
           <t>14.06</t>
         </is>
       </c>
-      <c r="E145" s="9" t="inlineStr">
+      <c r="E148" s="9" t="inlineStr">
         <is>
           <t>14.00–19.00%</t>
         </is>
       </c>
-      <c r="F145" s="9" t="inlineStr">
+      <c r="F148" s="9" t="inlineStr">
         <is>
           <t>QCCoA 001v02</t>
         </is>
       </c>
-      <c r="G145" s="9" t="inlineStr">
+      <c r="G148" s="9" t="inlineStr">
         <is>
           <t>20.02.2026</t>
         </is>
       </c>
-      <c r="H145" s="10" t="inlineStr">
+      <c r="H148" s="10" t="inlineStr">
         <is>
           <t>Purely Plant (in-house)</t>
         </is>
       </c>
-      <c r="I145" s="11" t="inlineStr">
+      <c r="I148" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="9" t="inlineStr"/>
-      <c r="B146" s="10" t="inlineStr"/>
-      <c r="C146" s="9" t="inlineStr"/>
-      <c r="D146" s="9" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="9" t="inlineStr"/>
+      <c r="B149" s="10" t="inlineStr"/>
+      <c r="C149" s="9" t="inlineStr"/>
+      <c r="D149" s="9" t="inlineStr">
         <is>
           <t>12.25</t>
         </is>
       </c>
-      <c r="E146" s="9" t="inlineStr"/>
-      <c r="F146" s="9" t="inlineStr">
+      <c r="E149" s="9" t="inlineStr"/>
+      <c r="F149" s="9" t="inlineStr">
         <is>
           <t>197-20-K-26</t>
         </is>
       </c>
-      <c r="G146" s="9" t="inlineStr">
+      <c r="G149" s="9" t="inlineStr">
         <is>
           <t>07.08.2026</t>
         </is>
       </c>
-      <c r="H146" s="10" t="inlineStr">
+      <c r="H149" s="10" t="inlineStr">
         <is>
           <t>Farmahem</t>
         </is>
       </c>
-      <c r="I146" s="11" t="inlineStr">
+      <c r="I149" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="9" t="inlineStr"/>
-      <c r="B147" s="10" t="inlineStr"/>
-      <c r="C147" s="9" t="inlineStr"/>
-      <c r="D147" s="9" t="inlineStr">
-        <is>
-          <t>14.06</t>
-        </is>
-      </c>
-      <c r="E147" s="9" t="inlineStr"/>
-      <c r="F147" s="9" t="inlineStr">
-        <is>
-          <t>ППК26004</t>
-        </is>
-      </c>
-      <c r="G147" s="9" t="inlineStr">
-        <is>
-          <t>21.01.2026</t>
-        </is>
-      </c>
-      <c r="H147" s="10" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy — Center for Natural Products</t>
-        </is>
-      </c>
-      <c r="I147" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="6" t="inlineStr">
-        <is>
-          <t>Scrambler      3 batch(es)</t>
-        </is>
-      </c>
-      <c r="B148" s="7" t="inlineStr"/>
-      <c r="C148" s="7" t="inlineStr"/>
-      <c r="D148" s="7" t="inlineStr"/>
-      <c r="E148" s="7" t="inlineStr"/>
-      <c r="F148" s="7" t="inlineStr"/>
-      <c r="G148" s="7" t="inlineStr"/>
-      <c r="H148" s="7" t="inlineStr"/>
-      <c r="I148" s="7" t="inlineStr"/>
-    </row>
-    <row r="149">
-      <c r="A149" s="9" t="n">
-        <v>69</v>
-      </c>
-      <c r="B149" s="12" t="inlineStr">
-        <is>
-          <t>SCR112501</t>
-        </is>
-      </c>
-      <c r="C149" s="9" t="inlineStr">
-        <is>
-          <t>P060282</t>
-        </is>
-      </c>
-      <c r="D149" s="9" t="inlineStr">
-        <is>
-          <t>17.13</t>
-        </is>
-      </c>
-      <c r="E149" s="9" t="inlineStr">
-        <is>
-          <t>16.13–20.75%</t>
-        </is>
-      </c>
-      <c r="F149" s="9" t="inlineStr">
-        <is>
-          <t>ППК26069</t>
-        </is>
-      </c>
-      <c r="G149" s="9" t="inlineStr">
-        <is>
-          <t>11.05.2026</t>
-        </is>
-      </c>
-      <c r="H149" s="10" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy — Center for Natural Products</t>
-        </is>
-      </c>
-      <c r="I149" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
     <row r="150">
-      <c r="A150" s="9" t="n">
-        <v>70</v>
-      </c>
-      <c r="B150" s="12" t="inlineStr">
-        <is>
-          <t>SCR022601</t>
-        </is>
-      </c>
+      <c r="A150" s="9" t="inlineStr"/>
+      <c r="B150" s="10" t="inlineStr"/>
       <c r="C150" s="9" t="inlineStr"/>
       <c r="D150" s="9" t="inlineStr">
         <is>
-          <t>21.92</t>
-        </is>
-      </c>
-      <c r="E150" s="9" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>14.06</t>
+        </is>
+      </c>
+      <c r="E150" s="9" t="inlineStr"/>
       <c r="F150" s="9" t="inlineStr">
         <is>
-          <t>ППК26116</t>
+          <t>ППК26004</t>
         </is>
       </c>
       <c r="G150" s="9" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>21.01.2026</t>
         </is>
       </c>
       <c r="H150" s="10" t="inlineStr">
@@ -47844,102 +47894,98 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="9" t="n">
-        <v>71</v>
-      </c>
-      <c r="B151" s="12" t="inlineStr">
-        <is>
-          <t>SCR012603</t>
-        </is>
-      </c>
-      <c r="C151" s="9" t="inlineStr">
-        <is>
-          <t>P060382</t>
-        </is>
-      </c>
-      <c r="D151" s="9" t="inlineStr">
-        <is>
-          <t>17.84</t>
-        </is>
-      </c>
-      <c r="E151" s="9" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="F151" s="9" t="inlineStr">
-        <is>
-          <t>197-21-K-26</t>
-        </is>
-      </c>
-      <c r="G151" s="9" t="inlineStr">
-        <is>
-          <t>07.08.2026</t>
-        </is>
-      </c>
-      <c r="H151" s="10" t="inlineStr">
-        <is>
-          <t>Farmahem</t>
-        </is>
-      </c>
-      <c r="I151" s="11" t="inlineStr">
+      <c r="A151" s="6" t="inlineStr">
+        <is>
+          <t>Scrambler      3 batch(es)</t>
+        </is>
+      </c>
+      <c r="B151" s="7" t="inlineStr"/>
+      <c r="C151" s="7" t="inlineStr"/>
+      <c r="D151" s="7" t="inlineStr"/>
+      <c r="E151" s="7" t="inlineStr"/>
+      <c r="F151" s="7" t="inlineStr"/>
+      <c r="G151" s="7" t="inlineStr"/>
+      <c r="H151" s="7" t="inlineStr"/>
+      <c r="I151" s="7" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="9" t="n">
+        <v>72</v>
+      </c>
+      <c r="B152" s="12" t="inlineStr">
+        <is>
+          <t>SCR112501</t>
+        </is>
+      </c>
+      <c r="C152" s="9" t="inlineStr">
+        <is>
+          <t>P060282</t>
+        </is>
+      </c>
+      <c r="D152" s="9" t="inlineStr">
+        <is>
+          <t>17.13</t>
+        </is>
+      </c>
+      <c r="E152" s="9" t="inlineStr">
+        <is>
+          <t>16.13–20.75%</t>
+        </is>
+      </c>
+      <c r="F152" s="9" t="inlineStr">
+        <is>
+          <t>ППК26069</t>
+        </is>
+      </c>
+      <c r="G152" s="9" t="inlineStr">
+        <is>
+          <t>11.05.2026</t>
+        </is>
+      </c>
+      <c r="H152" s="10" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy — Center for Natural Products</t>
+        </is>
+      </c>
+      <c r="I152" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="6" t="inlineStr">
-        <is>
-          <t>Sleepy Joy      3 batch(es)</t>
-        </is>
-      </c>
-      <c r="B152" s="7" t="inlineStr"/>
-      <c r="C152" s="7" t="inlineStr"/>
-      <c r="D152" s="7" t="inlineStr"/>
-      <c r="E152" s="7" t="inlineStr"/>
-      <c r="F152" s="7" t="inlineStr"/>
-      <c r="G152" s="7" t="inlineStr"/>
-      <c r="H152" s="7" t="inlineStr"/>
-      <c r="I152" s="7" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="9" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B153" s="12" t="inlineStr">
         <is>
-          <t>SJ092501</t>
-        </is>
-      </c>
-      <c r="C153" s="9" t="inlineStr">
-        <is>
-          <t>P060082</t>
-        </is>
-      </c>
+          <t>SCR022601</t>
+        </is>
+      </c>
+      <c r="C153" s="9" t="inlineStr"/>
       <c r="D153" s="9" t="inlineStr">
         <is>
-          <t>10.96</t>
+          <t>21.92</t>
         </is>
       </c>
       <c r="E153" s="9" t="inlineStr">
         <is>
-          <t>9.96–15.00%</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F153" s="9" t="inlineStr">
         <is>
-          <t>QCCoA 001v02</t>
+          <t>ППК26116</t>
         </is>
       </c>
       <c r="G153" s="9" t="inlineStr">
         <is>
-          <t>20.02.2026</t>
+          <t>06.07.2026</t>
         </is>
       </c>
       <c r="H153" s="10" t="inlineStr">
         <is>
-          <t>Purely Plant (in-house)</t>
+          <t>UKIM Faculty of Pharmacy — Center for Natural Products</t>
         </is>
       </c>
       <c r="I153" s="11" t="inlineStr">
@@ -47949,28 +47995,42 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="9" t="inlineStr"/>
-      <c r="B154" s="10" t="inlineStr"/>
-      <c r="C154" s="9" t="inlineStr"/>
+      <c r="A154" s="9" t="n">
+        <v>74</v>
+      </c>
+      <c r="B154" s="12" t="inlineStr">
+        <is>
+          <t>SCR012603</t>
+        </is>
+      </c>
+      <c r="C154" s="9" t="inlineStr">
+        <is>
+          <t>P060382</t>
+        </is>
+      </c>
       <c r="D154" s="9" t="inlineStr">
         <is>
-          <t>10.96</t>
-        </is>
-      </c>
-      <c r="E154" s="9" t="inlineStr"/>
+          <t>17.84</t>
+        </is>
+      </c>
+      <c r="E154" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="F154" s="9" t="inlineStr">
         <is>
-          <t>ППК26006</t>
+          <t>197-21-K-26</t>
         </is>
       </c>
       <c r="G154" s="9" t="inlineStr">
         <is>
-          <t>21.01.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="H154" s="10" t="inlineStr">
         <is>
-          <t>UKIM Faculty of Pharmacy — Center for Natural Products</t>
+          <t>Farmahem</t>
         </is>
       </c>
       <c r="I154" s="11" t="inlineStr">
@@ -47980,87 +48040,57 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="9" t="n">
-        <v>73</v>
-      </c>
-      <c r="B155" s="12" t="inlineStr">
-        <is>
-          <t>SJ102501</t>
-        </is>
-      </c>
-      <c r="C155" s="9" t="inlineStr">
-        <is>
-          <t>P060162</t>
-        </is>
-      </c>
-      <c r="D155" s="9" t="inlineStr">
-        <is>
-          <t>11.20</t>
-        </is>
-      </c>
-      <c r="E155" s="9" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="F155" s="9" t="inlineStr">
-        <is>
-          <t>051-3-K-26</t>
-        </is>
-      </c>
-      <c r="G155" s="9" t="inlineStr">
-        <is>
-          <t>04.03.2026</t>
-        </is>
-      </c>
-      <c r="H155" s="10" t="inlineStr">
-        <is>
-          <t>Farmahem</t>
-        </is>
-      </c>
-      <c r="I155" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="A155" s="6" t="inlineStr">
+        <is>
+          <t>Sleepy Joy      3 batch(es)</t>
+        </is>
+      </c>
+      <c r="B155" s="7" t="inlineStr"/>
+      <c r="C155" s="7" t="inlineStr"/>
+      <c r="D155" s="7" t="inlineStr"/>
+      <c r="E155" s="7" t="inlineStr"/>
+      <c r="F155" s="7" t="inlineStr"/>
+      <c r="G155" s="7" t="inlineStr"/>
+      <c r="H155" s="7" t="inlineStr"/>
+      <c r="I155" s="7" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="9" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B156" s="12" t="inlineStr">
         <is>
-          <t>SJ112501</t>
+          <t>SJ092501</t>
         </is>
       </c>
       <c r="C156" s="9" t="inlineStr">
         <is>
-          <t>P060192</t>
+          <t>P060082</t>
         </is>
       </c>
       <c r="D156" s="9" t="inlineStr">
         <is>
-          <t>9.20</t>
+          <t>10.96</t>
         </is>
       </c>
       <c r="E156" s="9" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>9.96–15.00%</t>
         </is>
       </c>
       <c r="F156" s="9" t="inlineStr">
         <is>
-          <t>051-2-K-26</t>
+          <t>QCCoA 001v02</t>
         </is>
       </c>
       <c r="G156" s="9" t="inlineStr">
         <is>
-          <t>04.03.2026</t>
+          <t>20.02.2026</t>
         </is>
       </c>
       <c r="H156" s="10" t="inlineStr">
         <is>
-          <t>Farmahem</t>
+          <t>Purely Plant (in-house)</t>
         </is>
       </c>
       <c r="I156" s="11" t="inlineStr">
@@ -48070,57 +48100,73 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="6" t="inlineStr">
-        <is>
-          <t>Wedding Crasher      2 batch(es)</t>
-        </is>
-      </c>
-      <c r="B157" s="7" t="inlineStr"/>
-      <c r="C157" s="7" t="inlineStr"/>
-      <c r="D157" s="7" t="inlineStr"/>
-      <c r="E157" s="7" t="inlineStr"/>
-      <c r="F157" s="7" t="inlineStr"/>
-      <c r="G157" s="7" t="inlineStr"/>
-      <c r="H157" s="7" t="inlineStr"/>
-      <c r="I157" s="7" t="inlineStr"/>
+      <c r="A157" s="9" t="inlineStr"/>
+      <c r="B157" s="10" t="inlineStr"/>
+      <c r="C157" s="9" t="inlineStr"/>
+      <c r="D157" s="9" t="inlineStr">
+        <is>
+          <t>10.96</t>
+        </is>
+      </c>
+      <c r="E157" s="9" t="inlineStr"/>
+      <c r="F157" s="9" t="inlineStr">
+        <is>
+          <t>ППК26006</t>
+        </is>
+      </c>
+      <c r="G157" s="9" t="inlineStr">
+        <is>
+          <t>21.01.2026</t>
+        </is>
+      </c>
+      <c r="H157" s="10" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy — Center for Natural Products</t>
+        </is>
+      </c>
+      <c r="I157" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="9" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B158" s="12" t="inlineStr">
         <is>
-          <t>WC072501</t>
+          <t>SJ102501</t>
         </is>
       </c>
       <c r="C158" s="9" t="inlineStr">
         <is>
-          <t>P050262</t>
+          <t>P060162</t>
         </is>
       </c>
       <c r="D158" s="9" t="inlineStr">
         <is>
-          <t>22.11</t>
+          <t>11.20</t>
         </is>
       </c>
       <c r="E158" s="9" t="inlineStr">
         <is>
-          <t>20.67–25.25%</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F158" s="9" t="inlineStr">
         <is>
-          <t>ППК25369</t>
+          <t>051-3-K-26</t>
         </is>
       </c>
       <c r="G158" s="9" t="inlineStr">
         <is>
-          <t>28.11.2025</t>
+          <t>04.03.2026</t>
         </is>
       </c>
       <c r="H158" s="10" t="inlineStr">
         <is>
-          <t>UKIM Faculty of Pharmacy — Center for Natural Products</t>
+          <t>Farmahem</t>
         </is>
       </c>
       <c r="I158" s="11" t="inlineStr">
@@ -48131,128 +48177,146 @@
     </row>
     <row r="159">
       <c r="A159" s="9" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B159" s="12" t="inlineStr">
         <is>
-          <t>WC082501</t>
+          <t>SJ112501</t>
         </is>
       </c>
       <c r="C159" s="9" t="inlineStr">
         <is>
-          <t>P060012</t>
+          <t>P060192</t>
         </is>
       </c>
       <c r="D159" s="9" t="inlineStr">
         <is>
-          <t>21.67</t>
+          <t>9.20</t>
         </is>
       </c>
       <c r="E159" s="9" t="inlineStr">
         <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F159" s="9" t="inlineStr">
+        <is>
+          <t>051-2-K-26</t>
+        </is>
+      </c>
+      <c r="G159" s="9" t="inlineStr">
+        <is>
+          <t>04.03.2026</t>
+        </is>
+      </c>
+      <c r="H159" s="10" t="inlineStr">
+        <is>
+          <t>Farmahem</t>
+        </is>
+      </c>
+      <c r="I159" s="11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="6" t="inlineStr">
+        <is>
+          <t>Wedding Crasher      2 batch(es)</t>
+        </is>
+      </c>
+      <c r="B160" s="7" t="inlineStr"/>
+      <c r="C160" s="7" t="inlineStr"/>
+      <c r="D160" s="7" t="inlineStr"/>
+      <c r="E160" s="7" t="inlineStr"/>
+      <c r="F160" s="7" t="inlineStr"/>
+      <c r="G160" s="7" t="inlineStr"/>
+      <c r="H160" s="7" t="inlineStr"/>
+      <c r="I160" s="7" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="9" t="n">
+        <v>78</v>
+      </c>
+      <c r="B161" s="12" t="inlineStr">
+        <is>
+          <t>WC072501</t>
+        </is>
+      </c>
+      <c r="C161" s="9" t="inlineStr">
+        <is>
+          <t>P050262</t>
+        </is>
+      </c>
+      <c r="D161" s="9" t="inlineStr">
+        <is>
+          <t>22.11</t>
+        </is>
+      </c>
+      <c r="E161" s="9" t="inlineStr">
+        <is>
           <t>20.67–25.25%</t>
         </is>
       </c>
-      <c r="F159" s="9" t="inlineStr">
-        <is>
-          <t>QCCoA 001v02</t>
-        </is>
-      </c>
-      <c r="G159" s="9" t="inlineStr">
-        <is>
-          <t>20.02.2026</t>
-        </is>
-      </c>
-      <c r="H159" s="10" t="inlineStr">
-        <is>
-          <t>Purely Plant (in-house)</t>
-        </is>
-      </c>
-      <c r="I159" s="11" t="inlineStr">
+      <c r="F161" s="9" t="inlineStr">
+        <is>
+          <t>ППК25369</t>
+        </is>
+      </c>
+      <c r="G161" s="9" t="inlineStr">
+        <is>
+          <t>28.11.2025</t>
+        </is>
+      </c>
+      <c r="H161" s="10" t="inlineStr">
+        <is>
+          <t>UKIM Faculty of Pharmacy — Center for Natural Products</t>
+        </is>
+      </c>
+      <c r="I161" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="9" t="inlineStr"/>
-      <c r="B160" s="10" t="inlineStr"/>
-      <c r="C160" s="9" t="inlineStr"/>
-      <c r="D160" s="9" t="inlineStr">
-        <is>
-          <t>21.67</t>
-        </is>
-      </c>
-      <c r="E160" s="9" t="inlineStr"/>
-      <c r="F160" s="9" t="inlineStr">
-        <is>
-          <t>ППК26001</t>
-        </is>
-      </c>
-      <c r="G160" s="9" t="inlineStr">
-        <is>
-          <t>21.01.2026</t>
-        </is>
-      </c>
-      <c r="H160" s="10" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy — Center for Natural Products</t>
-        </is>
-      </c>
-      <c r="I160" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="6" t="inlineStr">
-        <is>
-          <t>— strain not identified —      3 batch(es)</t>
-        </is>
-      </c>
-      <c r="B161" s="7" t="inlineStr"/>
-      <c r="C161" s="7" t="inlineStr"/>
-      <c r="D161" s="7" t="inlineStr"/>
-      <c r="E161" s="7" t="inlineStr"/>
-      <c r="F161" s="7" t="inlineStr"/>
-      <c r="G161" s="7" t="inlineStr"/>
-      <c r="H161" s="7" t="inlineStr"/>
-      <c r="I161" s="7" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="9" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B162" s="12" t="inlineStr">
         <is>
-          <t>GG012601*</t>
-        </is>
-      </c>
-      <c r="C162" s="9" t="inlineStr"/>
+          <t>WC082501</t>
+        </is>
+      </c>
+      <c r="C162" s="9" t="inlineStr">
+        <is>
+          <t>P060012</t>
+        </is>
+      </c>
       <c r="D162" s="9" t="inlineStr">
         <is>
-          <t>15.35</t>
+          <t>21.67</t>
         </is>
       </c>
       <c r="E162" s="9" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>20.67–25.25%</t>
         </is>
       </c>
       <c r="F162" s="9" t="inlineStr">
         <is>
-          <t>ППК26062</t>
+          <t>QCCoA 001v02</t>
         </is>
       </c>
       <c r="G162" s="9" t="inlineStr">
         <is>
-          <t>11.05.2026</t>
+          <t>20.02.2026</t>
         </is>
       </c>
       <c r="H162" s="10" t="inlineStr">
         <is>
-          <t>UKIM Faculty of Pharmacy — Center for Natural Products</t>
+          <t>Purely Plant (in-house)</t>
         </is>
       </c>
       <c r="I162" s="11" t="inlineStr">
@@ -48262,33 +48326,23 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="9" t="n">
-        <v>78</v>
-      </c>
-      <c r="B163" s="12" t="inlineStr">
-        <is>
-          <t>JD012601*</t>
-        </is>
-      </c>
+      <c r="A163" s="9" t="inlineStr"/>
+      <c r="B163" s="10" t="inlineStr"/>
       <c r="C163" s="9" t="inlineStr"/>
       <c r="D163" s="9" t="inlineStr">
         <is>
-          <t>18.16</t>
-        </is>
-      </c>
-      <c r="E163" s="9" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+          <t>21.67</t>
+        </is>
+      </c>
+      <c r="E163" s="9" t="inlineStr"/>
       <c r="F163" s="9" t="inlineStr">
         <is>
-          <t>ППК26064</t>
+          <t>ППК26001</t>
         </is>
       </c>
       <c r="G163" s="9" t="inlineStr">
         <is>
-          <t>11.05.2026</t>
+          <t>21.01.2026</t>
         </is>
       </c>
       <c r="H163" s="10" t="inlineStr">
@@ -48297,47 +48351,6 @@
         </is>
       </c>
       <c r="I163" s="11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="9" t="n">
-        <v>79</v>
-      </c>
-      <c r="B164" s="12" t="inlineStr">
-        <is>
-          <t>JD112501*</t>
-        </is>
-      </c>
-      <c r="C164" s="9" t="inlineStr"/>
-      <c r="D164" s="9" t="inlineStr">
-        <is>
-          <t>13.93</t>
-        </is>
-      </c>
-      <c r="E164" s="9" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="F164" s="9" t="inlineStr">
-        <is>
-          <t>ППК26065</t>
-        </is>
-      </c>
-      <c r="G164" s="9" t="inlineStr">
-        <is>
-          <t>11.05.2026</t>
-        </is>
-      </c>
-      <c r="H164" s="10" t="inlineStr">
-        <is>
-          <t>UKIM Faculty of Pharmacy — Center for Natural Products</t>
-        </is>
-      </c>
-      <c r="I164" s="11" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -48395,7 +48408,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId54"/>
@@ -48418,37 +48431,37 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId71"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I86" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I87" r:id="rId74"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I89" r:id="rId75"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I90" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I92" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I94" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I93" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I95" r:id="rId79"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I96" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I97" r:id="rId81"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I98" r:id="rId82"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I99" r:id="rId83"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I100" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I102" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I101" r:id="rId85"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I103" r:id="rId86"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I104" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I106" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I107" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I109" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I110" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I111" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I105" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I106" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I107" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I109" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I110" r:id="rId92"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I112" r:id="rId93"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I113" r:id="rId94"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I114" r:id="rId95"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I115" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I117" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I119" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I120" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I121" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I116" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I117" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I118" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I120" r:id="rId100"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I122" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I124" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I125" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I126" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I123" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I124" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I125" r:id="rId104"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I127" r:id="rId105"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I128" r:id="rId106"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I129" r:id="rId107"/>
@@ -48462,25 +48475,25 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I137" r:id="rId115"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I138" r:id="rId116"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I139" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I141" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I142" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I143" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I145" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I146" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I147" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I149" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I150" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I151" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I153" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I154" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I155" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I140" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I141" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I142" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I144" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I145" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I146" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I148" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I149" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I150" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I152" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I153" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I154" r:id="rId129"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I156" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I158" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I159" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I160" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I162" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I163" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I164" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I157" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I158" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I159" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I161" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I162" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I163" r:id="rId136"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -52186,8 +52199,16 @@
           <t>GG012601*</t>
         </is>
       </c>
-      <c r="C63" s="9" t="inlineStr"/>
-      <c r="D63" s="10" t="inlineStr"/>
+      <c r="C63" s="9" t="inlineStr">
+        <is>
+          <t>P060302</t>
+        </is>
+      </c>
+      <c r="D63" s="10" t="inlineStr">
+        <is>
+          <t>Gorilla Glue</t>
+        </is>
+      </c>
       <c r="E63" s="9" t="inlineStr">
         <is>
           <t>15.35</t>
@@ -52280,8 +52301,16 @@
           <t>JD012601*</t>
         </is>
       </c>
-      <c r="C65" s="9" t="inlineStr"/>
-      <c r="D65" s="10" t="inlineStr"/>
+      <c r="C65" s="9" t="inlineStr">
+        <is>
+          <t>P060312</t>
+        </is>
+      </c>
+      <c r="D65" s="10" t="inlineStr">
+        <is>
+          <t>Jelly Donutz</t>
+        </is>
+      </c>
       <c r="E65" s="9" t="inlineStr">
         <is>
           <t>18.16</t>
@@ -52375,7 +52404,11 @@
         </is>
       </c>
       <c r="C67" s="9" t="inlineStr"/>
-      <c r="D67" s="10" t="inlineStr"/>
+      <c r="D67" s="10" t="inlineStr">
+        <is>
+          <t>Jelly Donutz</t>
+        </is>
+      </c>
       <c r="E67" s="9" t="inlineStr">
         <is>
           <t>13.93</t>
@@ -54520,7 +54553,7 @@
       </c>
       <c r="I21" s="10" t="inlineStr">
         <is>
-          <t>GG1024 (2024-10, 13.34%) | GG1024_02 (2024-10, 15.95%) | GG112501 (2025-11, 17.94%) | GG012603 (2026-01, 16.70%)</t>
+          <t>GG1024 (2024-10, 13.34%) | GG1024_02 (2024-10, 15.95%) | GG012601* (?, 15.35%) | GG112501 (2025-11, 17.94%) | GG012603 (2026-01, 16.70%)</t>
         </is>
       </c>
     </row>
